--- a/artfynd/A 48568-2023 artfynd.xlsx
+++ b/artfynd/A 48568-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129759350</v>
+        <v>129759341</v>
       </c>
       <c r="B2" t="n">
-        <v>57735</v>
+        <v>91588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583877</v>
+        <v>583643</v>
       </c>
       <c r="R2" t="n">
-        <v>6911708</v>
+        <v>6911972</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129759361</v>
+        <v>129759398</v>
       </c>
       <c r="B3" t="n">
-        <v>57735</v>
+        <v>80209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583916</v>
+        <v>583824</v>
       </c>
       <c r="R3" t="n">
-        <v>6911778</v>
+        <v>6911829</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129759341</v>
+        <v>129759415</v>
       </c>
       <c r="B4" t="n">
-        <v>91587</v>
+        <v>98769</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583643</v>
+        <v>583723</v>
       </c>
       <c r="R4" t="n">
-        <v>6911972</v>
+        <v>6911832</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -950,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129759359</v>
+        <v>129759399</v>
       </c>
       <c r="B5" t="n">
-        <v>57735</v>
+        <v>75112</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>229651</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglavsknapp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Plectocarpon lichenum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583686</v>
+        <v>583550</v>
       </c>
       <c r="R5" t="n">
-        <v>6911969</v>
+        <v>6911932</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1047,11 +1042,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129759415</v>
+        <v>129759401</v>
       </c>
       <c r="B6" t="n">
-        <v>98768</v>
+        <v>80181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583723</v>
+        <v>583559</v>
       </c>
       <c r="R6" t="n">
-        <v>6911832</v>
+        <v>6911967</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,11 +1139,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129759398</v>
+        <v>129759381</v>
       </c>
       <c r="B7" t="n">
-        <v>80208</v>
+        <v>80085</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6461</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583824</v>
+        <v>583783</v>
       </c>
       <c r="R7" t="n">
-        <v>6911829</v>
+        <v>6911895</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129759399</v>
+        <v>129759379</v>
       </c>
       <c r="B8" t="n">
-        <v>75111</v>
+        <v>57733</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229651</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglavsknapp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Plectocarpon lichenum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Sommerf.) D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583550</v>
+        <v>583930</v>
       </c>
       <c r="R8" t="n">
-        <v>6911932</v>
+        <v>6911711</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1348,6 +1333,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1 ex, födosökande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1374,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129759401</v>
+        <v>129759413</v>
       </c>
       <c r="B9" t="n">
-        <v>80180</v>
+        <v>98769</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583559</v>
+        <v>583755</v>
       </c>
       <c r="R9" t="n">
-        <v>6911967</v>
+        <v>6911734</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1445,6 +1435,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1471,10 +1466,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129759379</v>
+        <v>129759430</v>
       </c>
       <c r="B10" t="n">
-        <v>57732</v>
+        <v>91608</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,23 +1477,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1506,10 +1497,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583930</v>
+        <v>584005</v>
       </c>
       <c r="R10" t="n">
-        <v>6911711</v>
+        <v>6911803</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1542,11 +1533,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>1 ex, födosökande</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1573,32 +1559,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129759352</v>
+        <v>129759436</v>
       </c>
       <c r="B11" t="n">
-        <v>57735</v>
+        <v>80216</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1608,10 +1594,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583778</v>
+        <v>583792</v>
       </c>
       <c r="R11" t="n">
-        <v>6911699</v>
+        <v>6911886</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1644,11 +1630,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1675,32 +1656,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129759381</v>
+        <v>129759429</v>
       </c>
       <c r="B12" t="n">
-        <v>80084</v>
+        <v>91602</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1710,10 +1691,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583783</v>
+        <v>583810</v>
       </c>
       <c r="R12" t="n">
-        <v>6911895</v>
+        <v>6911860</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1772,10 +1753,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129759430</v>
+        <v>129759392</v>
       </c>
       <c r="B13" t="n">
-        <v>91607</v>
+        <v>91886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1783,19 +1764,23 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1803,10 +1788,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584005</v>
+        <v>583799</v>
       </c>
       <c r="R13" t="n">
-        <v>6911803</v>
+        <v>6911903</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1865,32 +1850,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129759354</v>
+        <v>129759397</v>
       </c>
       <c r="B14" t="n">
-        <v>57735</v>
+        <v>80209</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1900,10 +1885,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>583724</v>
+        <v>583679</v>
       </c>
       <c r="R14" t="n">
-        <v>6911836</v>
+        <v>6911975</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,11 +1921,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1967,32 +1947,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129759436</v>
+        <v>129759424</v>
       </c>
       <c r="B15" t="n">
-        <v>80215</v>
+        <v>98769</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2002,10 +1982,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583792</v>
+        <v>583956</v>
       </c>
       <c r="R15" t="n">
-        <v>6911886</v>
+        <v>6911817</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2038,6 +2018,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>90 ex runt en tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2064,32 +2049,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129759413</v>
+        <v>129759427</v>
       </c>
       <c r="B16" t="n">
-        <v>98768</v>
+        <v>105835</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2099,10 +2084,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583755</v>
+        <v>584003</v>
       </c>
       <c r="R16" t="n">
-        <v>6911734</v>
+        <v>6911804</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2135,11 +2120,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>45 ex</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2166,32 +2146,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129759397</v>
+        <v>129759434</v>
       </c>
       <c r="B17" t="n">
-        <v>80208</v>
+        <v>79076</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2201,10 +2181,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583679</v>
+        <v>583999</v>
       </c>
       <c r="R17" t="n">
-        <v>6911975</v>
+        <v>6911809</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2263,32 +2243,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129759348</v>
+        <v>129759425</v>
       </c>
       <c r="B18" t="n">
-        <v>57735</v>
+        <v>98769</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2298,10 +2278,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584041</v>
+        <v>583999</v>
       </c>
       <c r="R18" t="n">
-        <v>6911763</v>
+        <v>6911781</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2338,7 +2318,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2365,32 +2345,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129759429</v>
+        <v>129759423</v>
       </c>
       <c r="B19" t="n">
-        <v>91601</v>
+        <v>98769</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2400,10 +2380,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583810</v>
+        <v>583836</v>
       </c>
       <c r="R19" t="n">
-        <v>6911860</v>
+        <v>6911810</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2436,6 +2416,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2462,10 +2447,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129759392</v>
+        <v>129759432</v>
       </c>
       <c r="B20" t="n">
-        <v>91885</v>
+        <v>79076</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2473,21 +2458,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2497,10 +2482,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583799</v>
+        <v>583940</v>
       </c>
       <c r="R20" t="n">
-        <v>6911903</v>
+        <v>6911767</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2559,32 +2544,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129759434</v>
+        <v>129759437</v>
       </c>
       <c r="B21" t="n">
-        <v>79075</v>
+        <v>100958</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2594,10 +2579,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583999</v>
+        <v>583826</v>
       </c>
       <c r="R21" t="n">
-        <v>6911809</v>
+        <v>6911855</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2656,32 +2641,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129759363</v>
+        <v>129759406</v>
       </c>
       <c r="B22" t="n">
-        <v>57735</v>
+        <v>80141</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2691,10 +2676,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>583939</v>
+        <v>583688</v>
       </c>
       <c r="R22" t="n">
-        <v>6911760</v>
+        <v>6911990</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2727,11 +2712,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2758,32 +2738,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129759427</v>
+        <v>129759339</v>
       </c>
       <c r="B23" t="n">
-        <v>105834</v>
+        <v>91588</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2793,10 +2773,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584003</v>
+        <v>584025</v>
       </c>
       <c r="R23" t="n">
-        <v>6911804</v>
+        <v>6911724</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2855,10 +2835,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129759424</v>
+        <v>129759384</v>
       </c>
       <c r="B24" t="n">
-        <v>98768</v>
+        <v>92041</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2866,21 +2846,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2890,10 +2870,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583956</v>
+        <v>584021</v>
       </c>
       <c r="R24" t="n">
-        <v>6911817</v>
+        <v>6911731</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2926,11 +2906,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>90 ex runt en tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2957,10 +2932,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129759370</v>
+        <v>129759380</v>
       </c>
       <c r="B25" t="n">
-        <v>57735</v>
+        <v>57733</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2968,16 +2943,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2992,10 +2967,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584063</v>
+        <v>583963</v>
       </c>
       <c r="R25" t="n">
-        <v>6911870</v>
+        <v>6911801</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3032,7 +3007,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska hackspår i liggande gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3059,10 +3034,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129759357</v>
+        <v>129759404</v>
       </c>
       <c r="B26" t="n">
-        <v>57735</v>
+        <v>92007</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3070,34 +3045,32 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stor-Oxögeberget, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583586</v>
+        <v>583819</v>
       </c>
       <c r="R26" t="n">
-        <v>6911868</v>
+        <v>6911717</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3132,17 +3105,13 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3161,32 +3130,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129759425</v>
+        <v>129759375</v>
       </c>
       <c r="B27" t="n">
-        <v>98768</v>
+        <v>57896</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3196,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>583999</v>
+        <v>583977</v>
       </c>
       <c r="R27" t="n">
-        <v>6911781</v>
+        <v>6911791</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3236,7 +3205,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>15 ex</t>
+          <t>Flera hördes varna</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3263,32 +3232,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129759432</v>
+        <v>129759411</v>
       </c>
       <c r="B28" t="n">
-        <v>79075</v>
+        <v>98769</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3298,10 +3267,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>583940</v>
+        <v>583966</v>
       </c>
       <c r="R28" t="n">
-        <v>6911767</v>
+        <v>6911716</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3334,6 +3303,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>29 ex</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3360,32 +3334,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129759437</v>
+        <v>129759385</v>
       </c>
       <c r="B29" t="n">
-        <v>100957</v>
+        <v>92041</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3395,10 +3369,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>583826</v>
+        <v>583791</v>
       </c>
       <c r="R29" t="n">
-        <v>6911855</v>
+        <v>6911899</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3457,32 +3431,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129759423</v>
+        <v>129759388</v>
       </c>
       <c r="B30" t="n">
-        <v>98768</v>
+        <v>91886</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3492,10 +3466,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>583836</v>
+        <v>584025</v>
       </c>
       <c r="R30" t="n">
-        <v>6911810</v>
+        <v>6911728</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3528,11 +3502,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>10 ex</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3559,32 +3528,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129759339</v>
+        <v>129759410</v>
       </c>
       <c r="B31" t="n">
-        <v>91587</v>
+        <v>80141</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3594,10 +3563,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584025</v>
+        <v>583794</v>
       </c>
       <c r="R31" t="n">
-        <v>6911724</v>
+        <v>6911885</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3656,43 +3625,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129759404</v>
+        <v>129759422</v>
       </c>
       <c r="B32" t="n">
-        <v>92006</v>
+        <v>98769</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6040186</v>
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stor-Oxögeberget, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>583819</v>
+        <v>583932</v>
       </c>
       <c r="R32" t="n">
-        <v>6911717</v>
+        <v>6911706</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3727,13 +3698,17 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>6 ex</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3752,32 +3727,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129759384</v>
+        <v>129759343</v>
       </c>
       <c r="B33" t="n">
-        <v>92040</v>
+        <v>91588</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3787,10 +3762,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584021</v>
+        <v>583805</v>
       </c>
       <c r="R33" t="n">
-        <v>6911731</v>
+        <v>6911905</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3849,10 +3824,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129759380</v>
+        <v>129759393</v>
       </c>
       <c r="B34" t="n">
-        <v>57732</v>
+        <v>91886</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3860,21 +3835,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3884,10 +3859,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>583963</v>
+        <v>583944</v>
       </c>
       <c r="R34" t="n">
-        <v>6911801</v>
+        <v>6911825</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3920,11 +3895,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Färska hackspår i liggande gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3951,10 +3921,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129759406</v>
+        <v>129759409</v>
       </c>
       <c r="B35" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3986,10 +3956,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>583688</v>
+        <v>583771</v>
       </c>
       <c r="R35" t="n">
-        <v>6911990</v>
+        <v>6911948</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4048,32 +4018,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129759372</v>
+        <v>129759407</v>
       </c>
       <c r="B36" t="n">
-        <v>57735</v>
+        <v>80141</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4083,10 +4053,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>584065</v>
+        <v>583767</v>
       </c>
       <c r="R36" t="n">
-        <v>6911918</v>
+        <v>6911956</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4119,11 +4089,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4150,32 +4115,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129759411</v>
+        <v>129759389</v>
       </c>
       <c r="B37" t="n">
-        <v>98768</v>
+        <v>91886</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4185,10 +4150,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>583966</v>
+        <v>583704</v>
       </c>
       <c r="R37" t="n">
-        <v>6911716</v>
+        <v>6911854</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4221,11 +4186,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>29 ex</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4252,32 +4212,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129759375</v>
+        <v>129759421</v>
       </c>
       <c r="B38" t="n">
-        <v>57895</v>
+        <v>98769</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4287,10 +4247,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>583977</v>
+        <v>583940</v>
       </c>
       <c r="R38" t="n">
-        <v>6911791</v>
+        <v>6911780</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4327,7 +4287,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Flera hördes varna</t>
+          <t>7 ex</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4354,10 +4314,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129759422</v>
+        <v>129759414</v>
       </c>
       <c r="B39" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4389,10 +4349,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>583932</v>
+        <v>583765</v>
       </c>
       <c r="R39" t="n">
-        <v>6911706</v>
+        <v>6911752</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4429,7 +4389,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>6 ex</t>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4456,10 +4416,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129759388</v>
+        <v>129759400</v>
       </c>
       <c r="B40" t="n">
-        <v>91885</v>
+        <v>80181</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4467,21 +4427,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4491,10 +4451,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584025</v>
+        <v>583551</v>
       </c>
       <c r="R40" t="n">
-        <v>6911728</v>
+        <v>6911946</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4527,6 +4487,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4553,32 +4518,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129759385</v>
+        <v>129759435</v>
       </c>
       <c r="B41" t="n">
-        <v>92040</v>
+        <v>80216</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1209</v>
+        <v>6463</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4588,10 +4553,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>583791</v>
+        <v>583790</v>
       </c>
       <c r="R41" t="n">
-        <v>6911899</v>
+        <v>6911897</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4650,10 +4615,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129759410</v>
+        <v>129759396</v>
       </c>
       <c r="B42" t="n">
-        <v>80140</v>
+        <v>97640</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4661,21 +4626,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229497</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4685,10 +4650,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>583794</v>
+        <v>583804</v>
       </c>
       <c r="R42" t="n">
-        <v>6911885</v>
+        <v>6911895</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4747,10 +4712,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129759367</v>
+        <v>129759428</v>
       </c>
       <c r="B43" t="n">
-        <v>57735</v>
+        <v>91602</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4758,21 +4723,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4782,10 +4747,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584025</v>
+        <v>583782</v>
       </c>
       <c r="R43" t="n">
-        <v>6911875</v>
+        <v>6911933</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4818,11 +4783,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4849,10 +4809,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129759366</v>
+        <v>129759345</v>
       </c>
       <c r="B44" t="n">
-        <v>57735</v>
+        <v>91588</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4860,21 +4820,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4884,10 +4844,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>583996</v>
+        <v>584070</v>
       </c>
       <c r="R44" t="n">
-        <v>6911823</v>
+        <v>6911921</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4920,11 +4880,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4951,10 +4906,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129759343</v>
+        <v>129759395</v>
       </c>
       <c r="B45" t="n">
-        <v>91587</v>
+        <v>91886</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4962,21 +4917,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4986,10 +4941,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>583805</v>
+        <v>584070</v>
       </c>
       <c r="R45" t="n">
-        <v>6911905</v>
+        <v>6911923</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5048,32 +5003,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129759393</v>
+        <v>129759378</v>
       </c>
       <c r="B46" t="n">
-        <v>91885</v>
+        <v>80210</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5083,10 +5038,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>583944</v>
+        <v>583791</v>
       </c>
       <c r="R46" t="n">
-        <v>6911825</v>
+        <v>6911883</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5145,10 +5100,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129759364</v>
+        <v>129759402</v>
       </c>
       <c r="B47" t="n">
-        <v>57735</v>
+        <v>80181</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5156,21 +5111,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5180,10 +5135,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>583922</v>
+        <v>583797</v>
       </c>
       <c r="R47" t="n">
-        <v>6911801</v>
+        <v>6911899</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5216,11 +5171,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5247,32 +5197,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129759358</v>
+        <v>129759382</v>
       </c>
       <c r="B48" t="n">
-        <v>57735</v>
+        <v>80085</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5282,10 +5232,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>583672</v>
+        <v>583791</v>
       </c>
       <c r="R48" t="n">
-        <v>6911978</v>
+        <v>6911884</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5318,11 +5268,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5349,10 +5294,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129759409</v>
+        <v>129759403</v>
       </c>
       <c r="B49" t="n">
-        <v>80140</v>
+        <v>80217</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5360,21 +5305,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229497</v>
+        <v>6464</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5384,10 +5329,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>583771</v>
+        <v>583755</v>
       </c>
       <c r="R49" t="n">
-        <v>6911948</v>
+        <v>6911971</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5446,10 +5391,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129759407</v>
+        <v>129759405</v>
       </c>
       <c r="B50" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5481,10 +5426,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>583767</v>
+        <v>583549</v>
       </c>
       <c r="R50" t="n">
-        <v>6911956</v>
+        <v>6911932</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5543,10 +5488,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129759421</v>
+        <v>129759419</v>
       </c>
       <c r="B51" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5578,10 +5523,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>583940</v>
+        <v>583745</v>
       </c>
       <c r="R51" t="n">
-        <v>6911780</v>
+        <v>6911935</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5618,7 +5563,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>7 ex</t>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5645,32 +5590,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129759389</v>
+        <v>129759412</v>
       </c>
       <c r="B52" t="n">
-        <v>91885</v>
+        <v>98769</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5680,10 +5625,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>583704</v>
+        <v>583781</v>
       </c>
       <c r="R52" t="n">
-        <v>6911854</v>
+        <v>6911695</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5716,6 +5661,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>70 ex</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5742,32 +5692,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129759355</v>
+        <v>129759420</v>
       </c>
       <c r="B53" t="n">
-        <v>57735</v>
+        <v>98769</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5777,10 +5727,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>583717</v>
+        <v>583927</v>
       </c>
       <c r="R53" t="n">
-        <v>6911847</v>
+        <v>6911779</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5817,7 +5767,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>1 ex, födosökande</t>
+          <t>22 ex</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5844,32 +5794,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129759414</v>
+        <v>129759391</v>
       </c>
       <c r="B54" t="n">
-        <v>98768</v>
+        <v>91886</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5879,10 +5829,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>583765</v>
+        <v>583565</v>
       </c>
       <c r="R54" t="n">
-        <v>6911752</v>
+        <v>6911984</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5915,11 +5865,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>15 ex</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5946,32 +5891,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129759400</v>
+        <v>129759377</v>
       </c>
       <c r="B55" t="n">
-        <v>80180</v>
+        <v>80210</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5981,10 +5926,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>583551</v>
+        <v>583809</v>
       </c>
       <c r="R55" t="n">
-        <v>6911946</v>
+        <v>6911875</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6017,11 +5962,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6048,10 +5988,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129759395</v>
+        <v>129759431</v>
       </c>
       <c r="B56" t="n">
-        <v>91885</v>
+        <v>79076</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6059,21 +5999,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6083,10 +6023,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>584070</v>
+        <v>583549</v>
       </c>
       <c r="R56" t="n">
-        <v>6911923</v>
+        <v>6911806</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6145,32 +6085,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129759435</v>
+        <v>129759394</v>
       </c>
       <c r="B57" t="n">
-        <v>80215</v>
+        <v>91886</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6180,10 +6120,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>583790</v>
+        <v>584057</v>
       </c>
       <c r="R57" t="n">
-        <v>6911897</v>
+        <v>6911892</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6242,32 +6182,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129759353</v>
+        <v>129759383</v>
       </c>
       <c r="B58" t="n">
-        <v>57735</v>
+        <v>80085</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6277,10 +6217,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>583756</v>
+        <v>584065</v>
       </c>
       <c r="R58" t="n">
-        <v>6911811</v>
+        <v>6911889</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6313,11 +6253,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6344,32 +6279,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129759428</v>
+        <v>129759376</v>
       </c>
       <c r="B59" t="n">
-        <v>91601</v>
+        <v>80210</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1204</v>
+        <v>6462</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6379,10 +6314,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>583782</v>
+        <v>583790</v>
       </c>
       <c r="R59" t="n">
-        <v>6911933</v>
+        <v>6911899</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6441,10 +6376,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129759362</v>
+        <v>129759433</v>
       </c>
       <c r="B60" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6452,21 +6387,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6476,10 +6411,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>583925</v>
+        <v>583652</v>
       </c>
       <c r="R60" t="n">
-        <v>6911784</v>
+        <v>6911949</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6512,11 +6447,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6543,32 +6473,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129759396</v>
+        <v>129759418</v>
       </c>
       <c r="B61" t="n">
-        <v>97639</v>
+        <v>98769</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6578,10 +6508,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>583804</v>
+        <v>583629</v>
       </c>
       <c r="R61" t="n">
-        <v>6911895</v>
+        <v>6911831</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6614,6 +6544,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6640,32 +6575,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129759345</v>
+        <v>129759416</v>
       </c>
       <c r="B62" t="n">
-        <v>91587</v>
+        <v>98769</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6675,10 +6610,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>584070</v>
+        <v>583627</v>
       </c>
       <c r="R62" t="n">
-        <v>6911921</v>
+        <v>6911841</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6711,6 +6646,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6737,32 +6677,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129759405</v>
+        <v>129759387</v>
       </c>
       <c r="B63" t="n">
-        <v>80140</v>
+        <v>91886</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>229497</v>
+        <v>658</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6772,10 +6712,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>583549</v>
+        <v>584029</v>
       </c>
       <c r="R63" t="n">
-        <v>6911932</v>
+        <v>6911718</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6834,32 +6774,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129759378</v>
+        <v>129759350</v>
       </c>
       <c r="B64" t="n">
-        <v>80209</v>
+        <v>57736</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6869,10 +6809,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>583791</v>
+        <v>583877</v>
       </c>
       <c r="R64" t="n">
-        <v>6911883</v>
+        <v>6911708</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6905,6 +6845,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6931,10 +6876,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129759402</v>
+        <v>129759361</v>
       </c>
       <c r="B65" t="n">
-        <v>80180</v>
+        <v>57736</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6942,21 +6887,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6966,10 +6911,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>583797</v>
+        <v>583916</v>
       </c>
       <c r="R65" t="n">
-        <v>6911899</v>
+        <v>6911778</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7002,6 +6947,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7028,32 +6978,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129759382</v>
+        <v>129759359</v>
       </c>
       <c r="B66" t="n">
-        <v>80084</v>
+        <v>57736</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7063,10 +7013,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>583791</v>
+        <v>583686</v>
       </c>
       <c r="R66" t="n">
-        <v>6911884</v>
+        <v>6911969</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7099,6 +7049,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7125,32 +7080,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129759403</v>
+        <v>129759352</v>
       </c>
       <c r="B67" t="n">
-        <v>80216</v>
+        <v>57736</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7160,10 +7115,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>583755</v>
+        <v>583778</v>
       </c>
       <c r="R67" t="n">
-        <v>6911971</v>
+        <v>6911699</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7196,6 +7151,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7222,10 +7182,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129759349</v>
+        <v>129759354</v>
       </c>
       <c r="B68" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7257,10 +7217,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>583883</v>
+        <v>583724</v>
       </c>
       <c r="R68" t="n">
-        <v>6911711</v>
+        <v>6911836</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7324,32 +7284,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129759419</v>
+        <v>129759348</v>
       </c>
       <c r="B69" t="n">
-        <v>98768</v>
+        <v>57736</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7359,10 +7319,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>583745</v>
+        <v>584041</v>
       </c>
       <c r="R69" t="n">
-        <v>6911935</v>
+        <v>6911763</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7399,7 +7359,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>100 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7426,10 +7386,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129759365</v>
+        <v>129759363</v>
       </c>
       <c r="B70" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7461,10 +7421,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>583989</v>
+        <v>583939</v>
       </c>
       <c r="R70" t="n">
-        <v>6911806</v>
+        <v>6911760</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7501,7 +7461,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>1 ex födosökande</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7528,32 +7488,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129759412</v>
+        <v>129759370</v>
       </c>
       <c r="B71" t="n">
-        <v>98768</v>
+        <v>57736</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7563,10 +7523,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>583781</v>
+        <v>584063</v>
       </c>
       <c r="R71" t="n">
-        <v>6911695</v>
+        <v>6911870</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7603,7 +7563,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>70 ex</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7630,32 +7590,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129759420</v>
+        <v>129759357</v>
       </c>
       <c r="B72" t="n">
-        <v>98768</v>
+        <v>57736</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7665,10 +7625,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>583927</v>
+        <v>583586</v>
       </c>
       <c r="R72" t="n">
-        <v>6911779</v>
+        <v>6911868</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7705,7 +7665,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>22 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7732,32 +7692,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129759377</v>
+        <v>129759372</v>
       </c>
       <c r="B73" t="n">
-        <v>80209</v>
+        <v>57736</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7767,10 +7727,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>583809</v>
+        <v>584065</v>
       </c>
       <c r="R73" t="n">
-        <v>6911875</v>
+        <v>6911918</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7803,6 +7763,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7829,10 +7794,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129759360</v>
+        <v>129759367</v>
       </c>
       <c r="B74" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7864,10 +7829,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>583915</v>
+        <v>584025</v>
       </c>
       <c r="R74" t="n">
-        <v>6911784</v>
+        <v>6911875</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7931,10 +7896,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129759391</v>
+        <v>129759366</v>
       </c>
       <c r="B75" t="n">
-        <v>91885</v>
+        <v>57736</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7942,21 +7907,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7966,10 +7931,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>583565</v>
+        <v>583996</v>
       </c>
       <c r="R75" t="n">
-        <v>6911984</v>
+        <v>6911823</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8002,6 +7967,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8028,10 +7998,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129759431</v>
+        <v>129759364</v>
       </c>
       <c r="B76" t="n">
-        <v>79075</v>
+        <v>57736</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8039,21 +8009,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8063,10 +8033,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>583549</v>
+        <v>583922</v>
       </c>
       <c r="R76" t="n">
-        <v>6911806</v>
+        <v>6911801</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8099,6 +8069,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8125,10 +8100,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129759394</v>
+        <v>129759358</v>
       </c>
       <c r="B77" t="n">
-        <v>91885</v>
+        <v>57736</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8136,21 +8111,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8160,10 +8135,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>584057</v>
+        <v>583672</v>
       </c>
       <c r="R77" t="n">
-        <v>6911892</v>
+        <v>6911978</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8196,6 +8171,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8222,32 +8202,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129759418</v>
+        <v>129759355</v>
       </c>
       <c r="B78" t="n">
-        <v>98768</v>
+        <v>57736</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8257,10 +8237,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>583629</v>
+        <v>583717</v>
       </c>
       <c r="R78" t="n">
-        <v>6911831</v>
+        <v>6911847</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8297,7 +8277,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>35 ex</t>
+          <t>1 ex, födosökande</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8324,32 +8304,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129759416</v>
+        <v>129759353</v>
       </c>
       <c r="B79" t="n">
-        <v>98768</v>
+        <v>57736</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8359,10 +8339,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>583627</v>
+        <v>583756</v>
       </c>
       <c r="R79" t="n">
-        <v>6911841</v>
+        <v>6911811</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8399,7 +8379,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>45 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8426,32 +8406,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129759383</v>
+        <v>129759362</v>
       </c>
       <c r="B80" t="n">
-        <v>80084</v>
+        <v>57736</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8461,10 +8441,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>584065</v>
+        <v>583925</v>
       </c>
       <c r="R80" t="n">
-        <v>6911889</v>
+        <v>6911784</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8497,6 +8477,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8523,32 +8508,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129759376</v>
+        <v>129759349</v>
       </c>
       <c r="B81" t="n">
-        <v>80209</v>
+        <v>57736</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8558,10 +8543,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>583790</v>
+        <v>583883</v>
       </c>
       <c r="R81" t="n">
-        <v>6911899</v>
+        <v>6911711</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8594,6 +8579,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8620,10 +8610,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129759433</v>
+        <v>129759365</v>
       </c>
       <c r="B82" t="n">
-        <v>79075</v>
+        <v>57736</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8631,21 +8621,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8655,10 +8645,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>583652</v>
+        <v>583989</v>
       </c>
       <c r="R82" t="n">
-        <v>6911949</v>
+        <v>6911806</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8691,6 +8681,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>1 ex födosökande</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8717,10 +8712,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129759351</v>
+        <v>129759360</v>
       </c>
       <c r="B83" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8752,10 +8747,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>583868</v>
+        <v>583915</v>
       </c>
       <c r="R83" t="n">
-        <v>6911718</v>
+        <v>6911784</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8819,10 +8814,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129759369</v>
+        <v>129759351</v>
       </c>
       <c r="B84" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8854,10 +8849,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>584039</v>
+        <v>583868</v>
       </c>
       <c r="R84" t="n">
-        <v>6911888</v>
+        <v>6911718</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8921,10 +8916,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129759387</v>
+        <v>129759369</v>
       </c>
       <c r="B85" t="n">
-        <v>91885</v>
+        <v>57736</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8932,21 +8927,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8956,10 +8951,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>584029</v>
+        <v>584039</v>
       </c>
       <c r="R85" t="n">
-        <v>6911718</v>
+        <v>6911888</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8992,6 +8987,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9021,7 +9021,7 @@
         <v>129759356</v>
       </c>
       <c r="B86" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 48568-2023 artfynd.xlsx
+++ b/artfynd/A 48568-2023 artfynd.xlsx
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129759399</v>
+        <v>129759401</v>
       </c>
       <c r="B5" t="n">
-        <v>75112</v>
+        <v>80181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229651</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglavsknapp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Plectocarpon lichenum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Sommerf.) D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583550</v>
+        <v>583559</v>
       </c>
       <c r="R5" t="n">
-        <v>6911932</v>
+        <v>6911967</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129759401</v>
+        <v>129759399</v>
       </c>
       <c r="B6" t="n">
-        <v>80181</v>
+        <v>75112</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>229651</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lunglavsknapp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Plectocarpon lichenum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583559</v>
+        <v>583550</v>
       </c>
       <c r="R6" t="n">
-        <v>6911967</v>
+        <v>6911932</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1947,32 +1947,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129759424</v>
+        <v>129759434</v>
       </c>
       <c r="B15" t="n">
-        <v>98769</v>
+        <v>79076</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1982,10 +1982,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583956</v>
+        <v>583999</v>
       </c>
       <c r="R15" t="n">
-        <v>6911817</v>
+        <v>6911809</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2018,11 +2018,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>90 ex runt en tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2049,32 +2044,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129759427</v>
+        <v>129759424</v>
       </c>
       <c r="B16" t="n">
-        <v>105835</v>
+        <v>98769</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2084,10 +2079,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584003</v>
+        <v>583956</v>
       </c>
       <c r="R16" t="n">
-        <v>6911804</v>
+        <v>6911817</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2120,6 +2115,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>90 ex runt en tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2146,32 +2146,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129759434</v>
+        <v>129759427</v>
       </c>
       <c r="B17" t="n">
-        <v>79076</v>
+        <v>105835</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583999</v>
+        <v>584003</v>
       </c>
       <c r="R17" t="n">
-        <v>6911809</v>
+        <v>6911804</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2243,32 +2243,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129759425</v>
+        <v>129759432</v>
       </c>
       <c r="B18" t="n">
-        <v>98769</v>
+        <v>79076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583999</v>
+        <v>583940</v>
       </c>
       <c r="R18" t="n">
-        <v>6911781</v>
+        <v>6911767</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2314,11 +2314,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>15 ex</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2345,7 +2340,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129759423</v>
+        <v>129759425</v>
       </c>
       <c r="B19" t="n">
         <v>98769</v>
@@ -2380,10 +2375,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583836</v>
+        <v>583999</v>
       </c>
       <c r="R19" t="n">
-        <v>6911810</v>
+        <v>6911781</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2420,7 +2415,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>10 ex</t>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2447,32 +2442,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129759432</v>
+        <v>129759423</v>
       </c>
       <c r="B20" t="n">
-        <v>79076</v>
+        <v>98769</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2482,10 +2477,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583940</v>
+        <v>583836</v>
       </c>
       <c r="R20" t="n">
-        <v>6911767</v>
+        <v>6911810</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2518,6 +2513,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -4115,32 +4115,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129759389</v>
+        <v>129759421</v>
       </c>
       <c r="B37" t="n">
-        <v>91886</v>
+        <v>98769</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>583704</v>
+        <v>583940</v>
       </c>
       <c r="R37" t="n">
-        <v>6911854</v>
+        <v>6911780</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4186,6 +4186,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>7 ex</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4212,7 +4217,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129759421</v>
+        <v>129759414</v>
       </c>
       <c r="B38" t="n">
         <v>98769</v>
@@ -4247,10 +4252,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>583940</v>
+        <v>583765</v>
       </c>
       <c r="R38" t="n">
-        <v>6911780</v>
+        <v>6911752</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4287,7 +4292,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>7 ex</t>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4314,32 +4319,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129759414</v>
+        <v>129759389</v>
       </c>
       <c r="B39" t="n">
-        <v>98769</v>
+        <v>91886</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4349,10 +4354,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>583765</v>
+        <v>583704</v>
       </c>
       <c r="R39" t="n">
-        <v>6911752</v>
+        <v>6911854</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4385,11 +4390,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>15 ex</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -6085,32 +6085,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129759394</v>
+        <v>129759383</v>
       </c>
       <c r="B57" t="n">
-        <v>91886</v>
+        <v>80085</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6120,10 +6120,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>584057</v>
+        <v>584065</v>
       </c>
       <c r="R57" t="n">
-        <v>6911892</v>
+        <v>6911889</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6182,10 +6182,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129759383</v>
+        <v>129759376</v>
       </c>
       <c r="B58" t="n">
-        <v>80085</v>
+        <v>80210</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6193,21 +6193,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6217,10 +6217,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>584065</v>
+        <v>583790</v>
       </c>
       <c r="R58" t="n">
-        <v>6911889</v>
+        <v>6911899</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6279,32 +6279,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129759376</v>
+        <v>129759433</v>
       </c>
       <c r="B59" t="n">
-        <v>80210</v>
+        <v>79076</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6314,10 +6314,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>583790</v>
+        <v>583652</v>
       </c>
       <c r="R59" t="n">
-        <v>6911899</v>
+        <v>6911949</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6376,32 +6376,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129759433</v>
+        <v>129759418</v>
       </c>
       <c r="B60" t="n">
-        <v>79076</v>
+        <v>98769</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6411,10 +6411,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>583652</v>
+        <v>583629</v>
       </c>
       <c r="R60" t="n">
-        <v>6911949</v>
+        <v>6911831</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6447,6 +6447,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6473,7 +6478,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129759418</v>
+        <v>129759416</v>
       </c>
       <c r="B61" t="n">
         <v>98769</v>
@@ -6508,10 +6513,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>583629</v>
+        <v>583627</v>
       </c>
       <c r="R61" t="n">
-        <v>6911831</v>
+        <v>6911841</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6548,7 +6553,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>35 ex</t>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6575,32 +6580,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129759416</v>
+        <v>129759394</v>
       </c>
       <c r="B62" t="n">
-        <v>98769</v>
+        <v>91886</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6610,10 +6615,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>583627</v>
+        <v>584057</v>
       </c>
       <c r="R62" t="n">
-        <v>6911841</v>
+        <v>6911892</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6646,11 +6651,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>45 ex</t>
         </is>
       </c>
       <c r="AD62" t="b">

--- a/artfynd/A 48568-2023 artfynd.xlsx
+++ b/artfynd/A 48568-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129759341</v>
       </c>
       <c r="B2" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129759398</v>
       </c>
       <c r="B3" t="n">
-        <v>80209</v>
+        <v>80214</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129759415</v>
       </c>
       <c r="B4" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>129759401</v>
       </c>
       <c r="B5" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>129759399</v>
       </c>
       <c r="B6" t="n">
-        <v>75112</v>
+        <v>75117</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>129759381</v>
       </c>
       <c r="B7" t="n">
-        <v>80085</v>
+        <v>80090</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129759413</v>
+        <v>129759436</v>
       </c>
       <c r="B9" t="n">
-        <v>98769</v>
+        <v>80221</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583755</v>
+        <v>583792</v>
       </c>
       <c r="R9" t="n">
-        <v>6911734</v>
+        <v>6911886</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1435,11 +1435,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>45 ex</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1466,30 +1461,34 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129759430</v>
+        <v>129759413</v>
       </c>
       <c r="B10" t="n">
-        <v>91608</v>
+        <v>98774</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1497,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584005</v>
+        <v>583755</v>
       </c>
       <c r="R10" t="n">
-        <v>6911803</v>
+        <v>6911734</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1533,6 +1532,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1559,34 +1563,30 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129759436</v>
+        <v>129759430</v>
       </c>
       <c r="B11" t="n">
-        <v>80216</v>
+        <v>91613</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1594,10 +1594,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583792</v>
+        <v>584005</v>
       </c>
       <c r="R11" t="n">
-        <v>6911886</v>
+        <v>6911803</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1659,7 +1659,7 @@
         <v>129759429</v>
       </c>
       <c r="B12" t="n">
-        <v>91602</v>
+        <v>91607</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>129759392</v>
       </c>
       <c r="B13" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>129759397</v>
       </c>
       <c r="B14" t="n">
-        <v>80209</v>
+        <v>80214</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>129759434</v>
       </c>
       <c r="B15" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2044,32 +2044,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129759424</v>
+        <v>129759427</v>
       </c>
       <c r="B16" t="n">
-        <v>98769</v>
+        <v>105840</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583956</v>
+        <v>584003</v>
       </c>
       <c r="R16" t="n">
-        <v>6911817</v>
+        <v>6911804</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2115,11 +2115,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>90 ex runt en tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2146,32 +2141,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129759427</v>
+        <v>129759424</v>
       </c>
       <c r="B17" t="n">
-        <v>105835</v>
+        <v>98774</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2181,10 +2176,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584003</v>
+        <v>583956</v>
       </c>
       <c r="R17" t="n">
-        <v>6911804</v>
+        <v>6911817</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2217,6 +2212,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>90 ex runt en tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2246,7 +2246,7 @@
         <v>129759432</v>
       </c>
       <c r="B18" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2340,32 +2340,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129759425</v>
+        <v>129759437</v>
       </c>
       <c r="B19" t="n">
-        <v>98769</v>
+        <v>100963</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583999</v>
+        <v>583826</v>
       </c>
       <c r="R19" t="n">
-        <v>6911781</v>
+        <v>6911855</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2411,11 +2411,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>15 ex</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2442,10 +2437,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129759423</v>
+        <v>129759425</v>
       </c>
       <c r="B20" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2477,10 +2472,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583836</v>
+        <v>583999</v>
       </c>
       <c r="R20" t="n">
-        <v>6911810</v>
+        <v>6911781</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2517,7 +2512,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>10 ex</t>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2544,32 +2539,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129759437</v>
+        <v>129759423</v>
       </c>
       <c r="B21" t="n">
-        <v>100958</v>
+        <v>98774</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2579,10 +2574,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583826</v>
+        <v>583836</v>
       </c>
       <c r="R21" t="n">
-        <v>6911855</v>
+        <v>6911810</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2615,6 +2610,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2644,7 +2644,7 @@
         <v>129759406</v>
       </c>
       <c r="B22" t="n">
-        <v>80141</v>
+        <v>80146</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>129759339</v>
       </c>
       <c r="B23" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>129759384</v>
       </c>
       <c r="B24" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>129759404</v>
       </c>
       <c r="B26" t="n">
-        <v>92007</v>
+        <v>92012</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>129759411</v>
       </c>
       <c r="B28" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3334,32 +3334,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129759385</v>
+        <v>129759388</v>
       </c>
       <c r="B29" t="n">
-        <v>92041</v>
+        <v>91891</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>583791</v>
+        <v>584025</v>
       </c>
       <c r="R29" t="n">
-        <v>6911899</v>
+        <v>6911728</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3431,32 +3431,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129759388</v>
+        <v>129759385</v>
       </c>
       <c r="B30" t="n">
-        <v>91886</v>
+        <v>92046</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584025</v>
+        <v>583791</v>
       </c>
       <c r="R30" t="n">
-        <v>6911728</v>
+        <v>6911899</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3528,32 +3528,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129759410</v>
+        <v>129759422</v>
       </c>
       <c r="B31" t="n">
-        <v>80141</v>
+        <v>98774</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3563,10 +3563,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>583794</v>
+        <v>583932</v>
       </c>
       <c r="R31" t="n">
-        <v>6911885</v>
+        <v>6911706</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3599,6 +3599,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>6 ex</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3625,32 +3630,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129759422</v>
+        <v>129759410</v>
       </c>
       <c r="B32" t="n">
-        <v>98769</v>
+        <v>80146</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3660,10 +3665,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>583932</v>
+        <v>583794</v>
       </c>
       <c r="R32" t="n">
-        <v>6911706</v>
+        <v>6911885</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3696,11 +3701,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>6 ex</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3730,7 +3730,7 @@
         <v>129759343</v>
       </c>
       <c r="B33" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>129759393</v>
       </c>
       <c r="B34" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3921,10 +3921,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129759409</v>
+        <v>129759407</v>
       </c>
       <c r="B35" t="n">
-        <v>80141</v>
+        <v>80146</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3956,10 +3956,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>583771</v>
+        <v>583767</v>
       </c>
       <c r="R35" t="n">
-        <v>6911948</v>
+        <v>6911956</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4018,10 +4018,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129759407</v>
+        <v>129759409</v>
       </c>
       <c r="B36" t="n">
-        <v>80141</v>
+        <v>80146</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>583767</v>
+        <v>583771</v>
       </c>
       <c r="R36" t="n">
-        <v>6911956</v>
+        <v>6911948</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4118,7 +4118,7 @@
         <v>129759421</v>
       </c>
       <c r="B37" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         <v>129759414</v>
       </c>
       <c r="B38" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>129759389</v>
       </c>
       <c r="B39" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4416,10 +4416,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129759400</v>
+        <v>129759395</v>
       </c>
       <c r="B40" t="n">
-        <v>80181</v>
+        <v>91891</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4427,21 +4427,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4451,10 +4451,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>583551</v>
+        <v>584070</v>
       </c>
       <c r="R40" t="n">
-        <v>6911946</v>
+        <v>6911923</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4487,11 +4487,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4518,32 +4513,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129759435</v>
+        <v>129759428</v>
       </c>
       <c r="B41" t="n">
-        <v>80216</v>
+        <v>91607</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6463</v>
+        <v>1204</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4553,10 +4548,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>583790</v>
+        <v>583782</v>
       </c>
       <c r="R41" t="n">
-        <v>6911897</v>
+        <v>6911933</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4615,32 +4610,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129759396</v>
+        <v>129759345</v>
       </c>
       <c r="B42" t="n">
-        <v>97640</v>
+        <v>91593</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4650,10 +4645,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>583804</v>
+        <v>584070</v>
       </c>
       <c r="R42" t="n">
-        <v>6911895</v>
+        <v>6911921</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4712,10 +4707,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129759428</v>
+        <v>129759400</v>
       </c>
       <c r="B43" t="n">
-        <v>91602</v>
+        <v>80186</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4723,21 +4718,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4747,10 +4742,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>583782</v>
+        <v>583551</v>
       </c>
       <c r="R43" t="n">
-        <v>6911933</v>
+        <v>6911946</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4783,6 +4778,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4809,32 +4809,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129759345</v>
+        <v>129759435</v>
       </c>
       <c r="B44" t="n">
-        <v>91588</v>
+        <v>80221</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4844,10 +4844,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584070</v>
+        <v>583790</v>
       </c>
       <c r="R44" t="n">
-        <v>6911921</v>
+        <v>6911897</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4906,32 +4906,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129759395</v>
+        <v>129759396</v>
       </c>
       <c r="B45" t="n">
-        <v>91886</v>
+        <v>97645</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584070</v>
+        <v>583804</v>
       </c>
       <c r="R45" t="n">
-        <v>6911923</v>
+        <v>6911895</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5006,7 +5006,7 @@
         <v>129759378</v>
       </c>
       <c r="B46" t="n">
-        <v>80210</v>
+        <v>80215</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>129759402</v>
       </c>
       <c r="B47" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         <v>129759382</v>
       </c>
       <c r="B48" t="n">
-        <v>80085</v>
+        <v>80090</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>129759403</v>
       </c>
       <c r="B49" t="n">
-        <v>80217</v>
+        <v>80222</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>129759405</v>
       </c>
       <c r="B50" t="n">
-        <v>80141</v>
+        <v>80146</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>129759419</v>
       </c>
       <c r="B51" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>129759412</v>
       </c>
       <c r="B52" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>129759420</v>
       </c>
       <c r="B53" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>129759391</v>
       </c>
       <c r="B54" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>129759377</v>
       </c>
       <c r="B55" t="n">
-        <v>80210</v>
+        <v>80215</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>129759431</v>
       </c>
       <c r="B56" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>129759383</v>
       </c>
       <c r="B57" t="n">
-        <v>80085</v>
+        <v>80090</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         <v>129759376</v>
       </c>
       <c r="B58" t="n">
-        <v>80210</v>
+        <v>80215</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>129759433</v>
       </c>
       <c r="B59" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6379,7 +6379,7 @@
         <v>129759418</v>
       </c>
       <c r="B60" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>129759416</v>
       </c>
       <c r="B61" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>129759394</v>
       </c>
       <c r="B62" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>129759387</v>
       </c>
       <c r="B63" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 48568-2023 artfynd.xlsx
+++ b/artfynd/A 48568-2023 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129759398</v>
+        <v>129759415</v>
       </c>
       <c r="B3" t="n">
-        <v>80214</v>
+        <v>98774</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583824</v>
+        <v>583723</v>
       </c>
       <c r="R3" t="n">
-        <v>6911829</v>
+        <v>6911832</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129759415</v>
+        <v>129759398</v>
       </c>
       <c r="B4" t="n">
-        <v>98774</v>
+        <v>80214</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583723</v>
+        <v>583824</v>
       </c>
       <c r="R4" t="n">
-        <v>6911832</v>
+        <v>6911829</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129759381</v>
+        <v>129759379</v>
       </c>
       <c r="B7" t="n">
-        <v>80090</v>
+        <v>57733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583783</v>
+        <v>583930</v>
       </c>
       <c r="R7" t="n">
-        <v>6911895</v>
+        <v>6911711</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,6 +1236,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>1 ex, födosökande</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1262,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129759379</v>
+        <v>129759381</v>
       </c>
       <c r="B8" t="n">
-        <v>57733</v>
+        <v>80090</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583930</v>
+        <v>583783</v>
       </c>
       <c r="R8" t="n">
-        <v>6911711</v>
+        <v>6911895</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1333,11 +1338,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>1 ex, födosökande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1364,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129759436</v>
+        <v>129759413</v>
       </c>
       <c r="B9" t="n">
-        <v>80221</v>
+        <v>98774</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583792</v>
+        <v>583755</v>
       </c>
       <c r="R9" t="n">
-        <v>6911886</v>
+        <v>6911734</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1435,6 +1435,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1461,34 +1466,30 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129759413</v>
+        <v>129759430</v>
       </c>
       <c r="B10" t="n">
-        <v>98774</v>
+        <v>91613</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1496,10 +1497,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583755</v>
+        <v>584005</v>
       </c>
       <c r="R10" t="n">
-        <v>6911734</v>
+        <v>6911803</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1532,11 +1533,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>45 ex</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1563,30 +1559,34 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129759430</v>
+        <v>129759436</v>
       </c>
       <c r="B11" t="n">
-        <v>91613</v>
+        <v>80221</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1594,10 +1594,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584005</v>
+        <v>583792</v>
       </c>
       <c r="R11" t="n">
-        <v>6911803</v>
+        <v>6911886</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,32 +1753,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129759392</v>
+        <v>129759397</v>
       </c>
       <c r="B13" t="n">
-        <v>91891</v>
+        <v>80214</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>6461</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583799</v>
+        <v>583679</v>
       </c>
       <c r="R13" t="n">
-        <v>6911903</v>
+        <v>6911975</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1850,32 +1850,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129759397</v>
+        <v>129759392</v>
       </c>
       <c r="B14" t="n">
-        <v>80214</v>
+        <v>91891</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6461</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>583679</v>
+        <v>583799</v>
       </c>
       <c r="R14" t="n">
-        <v>6911975</v>
+        <v>6911903</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,32 +2044,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129759427</v>
+        <v>129759424</v>
       </c>
       <c r="B16" t="n">
-        <v>105840</v>
+        <v>98774</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584003</v>
+        <v>583956</v>
       </c>
       <c r="R16" t="n">
-        <v>6911804</v>
+        <v>6911817</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2115,6 +2115,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>90 ex runt en tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2141,32 +2146,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129759424</v>
+        <v>129759427</v>
       </c>
       <c r="B17" t="n">
-        <v>98774</v>
+        <v>105840</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2176,10 +2181,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583956</v>
+        <v>584003</v>
       </c>
       <c r="R17" t="n">
-        <v>6911817</v>
+        <v>6911804</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2212,11 +2217,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>90 ex runt en tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2340,32 +2340,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129759437</v>
+        <v>129759425</v>
       </c>
       <c r="B19" t="n">
-        <v>100963</v>
+        <v>98774</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583826</v>
+        <v>583999</v>
       </c>
       <c r="R19" t="n">
-        <v>6911855</v>
+        <v>6911781</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2411,6 +2411,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2437,7 +2442,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129759425</v>
+        <v>129759423</v>
       </c>
       <c r="B20" t="n">
         <v>98774</v>
@@ -2472,10 +2477,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583999</v>
+        <v>583836</v>
       </c>
       <c r="R20" t="n">
-        <v>6911781</v>
+        <v>6911810</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2512,7 +2517,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>15 ex</t>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2539,32 +2544,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129759423</v>
+        <v>129759437</v>
       </c>
       <c r="B21" t="n">
-        <v>98774</v>
+        <v>100963</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2574,10 +2579,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583836</v>
+        <v>583826</v>
       </c>
       <c r="R21" t="n">
-        <v>6911810</v>
+        <v>6911855</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2610,11 +2615,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>10 ex</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2641,32 +2641,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129759406</v>
+        <v>129759384</v>
       </c>
       <c r="B22" t="n">
-        <v>80146</v>
+        <v>92046</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229497</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>583688</v>
+        <v>584021</v>
       </c>
       <c r="R22" t="n">
-        <v>6911990</v>
+        <v>6911731</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2835,32 +2835,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129759384</v>
+        <v>129759380</v>
       </c>
       <c r="B24" t="n">
-        <v>92046</v>
+        <v>57733</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584021</v>
+        <v>583963</v>
       </c>
       <c r="R24" t="n">
-        <v>6911731</v>
+        <v>6911801</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2906,6 +2906,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska hackspår i liggande gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2932,10 +2937,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129759380</v>
+        <v>129759404</v>
       </c>
       <c r="B25" t="n">
-        <v>57733</v>
+        <v>92012</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2943,34 +2948,32 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stor-Oxögeberget, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583963</v>
+        <v>583819</v>
       </c>
       <c r="R25" t="n">
-        <v>6911801</v>
+        <v>6911717</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3005,17 +3008,13 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska hackspår i liggande gran</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3034,43 +3033,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129759404</v>
+        <v>129759406</v>
       </c>
       <c r="B26" t="n">
-        <v>92012</v>
+        <v>80146</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6040186</v>
+        <v>229497</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stor-Oxögeberget, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583819</v>
+        <v>583688</v>
       </c>
       <c r="R26" t="n">
-        <v>6911717</v>
+        <v>6911990</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3111,7 +3112,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3334,32 +3334,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129759388</v>
+        <v>129759385</v>
       </c>
       <c r="B29" t="n">
-        <v>91891</v>
+        <v>92046</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584025</v>
+        <v>583791</v>
       </c>
       <c r="R29" t="n">
-        <v>6911728</v>
+        <v>6911899</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3431,10 +3431,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129759385</v>
+        <v>129759422</v>
       </c>
       <c r="B30" t="n">
-        <v>92046</v>
+        <v>98774</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3442,21 +3442,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>583791</v>
+        <v>583932</v>
       </c>
       <c r="R30" t="n">
-        <v>6911899</v>
+        <v>6911706</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3502,6 +3502,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>6 ex</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3528,32 +3533,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129759422</v>
+        <v>129759388</v>
       </c>
       <c r="B31" t="n">
-        <v>98774</v>
+        <v>91891</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3563,10 +3568,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>583932</v>
+        <v>584025</v>
       </c>
       <c r="R31" t="n">
-        <v>6911706</v>
+        <v>6911728</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3599,11 +3604,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>6 ex</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3727,10 +3727,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129759343</v>
+        <v>129759393</v>
       </c>
       <c r="B33" t="n">
-        <v>91593</v>
+        <v>91891</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3738,21 +3738,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3762,10 +3762,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>583805</v>
+        <v>583944</v>
       </c>
       <c r="R33" t="n">
-        <v>6911905</v>
+        <v>6911825</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3824,10 +3824,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129759393</v>
+        <v>129759343</v>
       </c>
       <c r="B34" t="n">
-        <v>91891</v>
+        <v>91593</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3835,21 +3835,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3859,10 +3859,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>583944</v>
+        <v>583805</v>
       </c>
       <c r="R34" t="n">
-        <v>6911825</v>
+        <v>6911905</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3921,7 +3921,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129759407</v>
+        <v>129759409</v>
       </c>
       <c r="B35" t="n">
         <v>80146</v>
@@ -3956,10 +3956,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>583767</v>
+        <v>583771</v>
       </c>
       <c r="R35" t="n">
-        <v>6911956</v>
+        <v>6911948</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4018,7 +4018,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129759409</v>
+        <v>129759407</v>
       </c>
       <c r="B36" t="n">
         <v>80146</v>
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>583771</v>
+        <v>583767</v>
       </c>
       <c r="R36" t="n">
-        <v>6911948</v>
+        <v>6911956</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4115,32 +4115,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129759421</v>
+        <v>129759389</v>
       </c>
       <c r="B37" t="n">
-        <v>98774</v>
+        <v>91891</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>583940</v>
+        <v>583704</v>
       </c>
       <c r="R37" t="n">
-        <v>6911780</v>
+        <v>6911854</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4186,11 +4186,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>7 ex</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4217,7 +4212,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129759414</v>
+        <v>129759421</v>
       </c>
       <c r="B38" t="n">
         <v>98774</v>
@@ -4252,10 +4247,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>583765</v>
+        <v>583940</v>
       </c>
       <c r="R38" t="n">
-        <v>6911752</v>
+        <v>6911780</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4292,7 +4287,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>15 ex</t>
+          <t>7 ex</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4319,32 +4314,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129759389</v>
+        <v>129759414</v>
       </c>
       <c r="B39" t="n">
-        <v>91891</v>
+        <v>98774</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4354,10 +4349,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>583704</v>
+        <v>583765</v>
       </c>
       <c r="R39" t="n">
-        <v>6911854</v>
+        <v>6911752</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4390,6 +4385,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4513,10 +4513,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129759428</v>
+        <v>129759345</v>
       </c>
       <c r="B41" t="n">
-        <v>91607</v>
+        <v>91593</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4524,21 +4524,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4548,10 +4548,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>583782</v>
+        <v>584070</v>
       </c>
       <c r="R41" t="n">
-        <v>6911933</v>
+        <v>6911921</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4610,10 +4610,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129759345</v>
+        <v>129759400</v>
       </c>
       <c r="B42" t="n">
-        <v>91593</v>
+        <v>80186</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4621,21 +4621,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4645,10 +4645,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>584070</v>
+        <v>583551</v>
       </c>
       <c r="R42" t="n">
-        <v>6911921</v>
+        <v>6911946</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4681,6 +4681,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4707,32 +4712,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129759400</v>
+        <v>129759435</v>
       </c>
       <c r="B43" t="n">
-        <v>80186</v>
+        <v>80221</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4742,10 +4747,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>583551</v>
+        <v>583790</v>
       </c>
       <c r="R43" t="n">
-        <v>6911946</v>
+        <v>6911897</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4778,11 +4783,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4809,10 +4809,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129759435</v>
+        <v>129759396</v>
       </c>
       <c r="B44" t="n">
-        <v>80221</v>
+        <v>97645</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4820,21 +4820,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6463</v>
+        <v>221945</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4844,10 +4844,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>583790</v>
+        <v>583804</v>
       </c>
       <c r="R44" t="n">
-        <v>6911897</v>
+        <v>6911895</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4906,32 +4906,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129759396</v>
+        <v>129759428</v>
       </c>
       <c r="B45" t="n">
-        <v>97645</v>
+        <v>91607</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221945</v>
+        <v>1204</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>583804</v>
+        <v>583782</v>
       </c>
       <c r="R45" t="n">
-        <v>6911895</v>
+        <v>6911933</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5794,10 +5794,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129759391</v>
+        <v>129759431</v>
       </c>
       <c r="B54" t="n">
-        <v>91891</v>
+        <v>79081</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5805,21 +5805,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5829,10 +5829,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>583565</v>
+        <v>583549</v>
       </c>
       <c r="R54" t="n">
-        <v>6911984</v>
+        <v>6911806</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5891,32 +5891,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129759377</v>
+        <v>129759391</v>
       </c>
       <c r="B55" t="n">
-        <v>80215</v>
+        <v>91891</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5926,10 +5926,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>583809</v>
+        <v>583565</v>
       </c>
       <c r="R55" t="n">
-        <v>6911875</v>
+        <v>6911984</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5988,32 +5988,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129759431</v>
+        <v>129759377</v>
       </c>
       <c r="B56" t="n">
-        <v>79081</v>
+        <v>80215</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6023,10 +6023,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>583549</v>
+        <v>583809</v>
       </c>
       <c r="R56" t="n">
-        <v>6911806</v>
+        <v>6911875</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6279,32 +6279,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129759433</v>
+        <v>129759418</v>
       </c>
       <c r="B59" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6314,10 +6314,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>583652</v>
+        <v>583629</v>
       </c>
       <c r="R59" t="n">
-        <v>6911949</v>
+        <v>6911831</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6350,6 +6350,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6376,7 +6381,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129759418</v>
+        <v>129759416</v>
       </c>
       <c r="B60" t="n">
         <v>98774</v>
@@ -6411,10 +6416,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>583629</v>
+        <v>583627</v>
       </c>
       <c r="R60" t="n">
-        <v>6911831</v>
+        <v>6911841</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6451,7 +6456,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>35 ex</t>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6478,32 +6483,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129759416</v>
+        <v>129759433</v>
       </c>
       <c r="B61" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6513,10 +6518,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>583627</v>
+        <v>583652</v>
       </c>
       <c r="R61" t="n">
-        <v>6911841</v>
+        <v>6911949</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6549,11 +6554,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>45 ex</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 48568-2023 artfynd.xlsx
+++ b/artfynd/A 48568-2023 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129759415</v>
+        <v>129759398</v>
       </c>
       <c r="B3" t="n">
-        <v>98774</v>
+        <v>80214</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583723</v>
+        <v>583824</v>
       </c>
       <c r="R3" t="n">
-        <v>6911832</v>
+        <v>6911829</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129759398</v>
+        <v>129759415</v>
       </c>
       <c r="B4" t="n">
-        <v>80214</v>
+        <v>98774</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583824</v>
+        <v>583723</v>
       </c>
       <c r="R4" t="n">
-        <v>6911829</v>
+        <v>6911832</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129759379</v>
+        <v>129759381</v>
       </c>
       <c r="B7" t="n">
-        <v>57733</v>
+        <v>80090</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583930</v>
+        <v>583783</v>
       </c>
       <c r="R7" t="n">
-        <v>6911711</v>
+        <v>6911895</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,11 +1236,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>1 ex, födosökande</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129759381</v>
+        <v>129759379</v>
       </c>
       <c r="B8" t="n">
-        <v>80090</v>
+        <v>57733</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583783</v>
+        <v>583930</v>
       </c>
       <c r="R8" t="n">
-        <v>6911895</v>
+        <v>6911711</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1338,6 +1333,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1 ex, födosökande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1364,34 +1364,30 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129759413</v>
+        <v>129759430</v>
       </c>
       <c r="B9" t="n">
-        <v>98774</v>
+        <v>91613</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1399,10 +1395,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583755</v>
+        <v>584005</v>
       </c>
       <c r="R9" t="n">
-        <v>6911734</v>
+        <v>6911803</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1435,11 +1431,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>45 ex</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1466,30 +1457,34 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129759430</v>
+        <v>129759436</v>
       </c>
       <c r="B10" t="n">
-        <v>91613</v>
+        <v>80221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1497,10 +1492,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584005</v>
+        <v>583792</v>
       </c>
       <c r="R10" t="n">
-        <v>6911803</v>
+        <v>6911886</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1559,32 +1554,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129759436</v>
+        <v>129759413</v>
       </c>
       <c r="B11" t="n">
-        <v>80221</v>
+        <v>98774</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1594,10 +1589,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583792</v>
+        <v>583755</v>
       </c>
       <c r="R11" t="n">
-        <v>6911886</v>
+        <v>6911734</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1630,6 +1625,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1656,10 +1656,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129759429</v>
+        <v>129759392</v>
       </c>
       <c r="B12" t="n">
-        <v>91607</v>
+        <v>91891</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1667,21 +1667,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583810</v>
+        <v>583799</v>
       </c>
       <c r="R12" t="n">
-        <v>6911860</v>
+        <v>6911903</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1753,32 +1753,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129759397</v>
+        <v>129759429</v>
       </c>
       <c r="B13" t="n">
-        <v>80214</v>
+        <v>91607</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6461</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583679</v>
+        <v>583810</v>
       </c>
       <c r="R13" t="n">
-        <v>6911975</v>
+        <v>6911860</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1850,32 +1850,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129759392</v>
+        <v>129759397</v>
       </c>
       <c r="B14" t="n">
-        <v>91891</v>
+        <v>80214</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>6461</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>583799</v>
+        <v>583679</v>
       </c>
       <c r="R14" t="n">
-        <v>6911903</v>
+        <v>6911975</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2243,32 +2243,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129759432</v>
+        <v>129759425</v>
       </c>
       <c r="B18" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583940</v>
+        <v>583999</v>
       </c>
       <c r="R18" t="n">
-        <v>6911767</v>
+        <v>6911781</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2314,6 +2314,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2340,7 +2345,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129759425</v>
+        <v>129759423</v>
       </c>
       <c r="B19" t="n">
         <v>98774</v>
@@ -2375,10 +2380,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583999</v>
+        <v>583836</v>
       </c>
       <c r="R19" t="n">
-        <v>6911781</v>
+        <v>6911810</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2415,7 +2420,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>15 ex</t>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2442,32 +2447,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129759423</v>
+        <v>129759437</v>
       </c>
       <c r="B20" t="n">
-        <v>98774</v>
+        <v>100963</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2477,10 +2482,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583836</v>
+        <v>583826</v>
       </c>
       <c r="R20" t="n">
-        <v>6911810</v>
+        <v>6911855</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2513,11 +2518,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>10 ex</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2544,32 +2544,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129759437</v>
+        <v>129759432</v>
       </c>
       <c r="B21" t="n">
-        <v>100963</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583826</v>
+        <v>583940</v>
       </c>
       <c r="R21" t="n">
-        <v>6911855</v>
+        <v>6911767</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2641,32 +2641,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129759384</v>
+        <v>129759339</v>
       </c>
       <c r="B22" t="n">
-        <v>92046</v>
+        <v>91593</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584021</v>
+        <v>584025</v>
       </c>
       <c r="R22" t="n">
-        <v>6911731</v>
+        <v>6911724</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2738,32 +2738,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129759339</v>
+        <v>129759384</v>
       </c>
       <c r="B23" t="n">
-        <v>91593</v>
+        <v>92046</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584025</v>
+        <v>584021</v>
       </c>
       <c r="R23" t="n">
-        <v>6911724</v>
+        <v>6911731</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2835,32 +2835,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129759380</v>
+        <v>129759406</v>
       </c>
       <c r="B24" t="n">
-        <v>57733</v>
+        <v>80146</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>229497</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583963</v>
+        <v>583688</v>
       </c>
       <c r="R24" t="n">
-        <v>6911801</v>
+        <v>6911990</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2906,11 +2906,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska hackspår i liggande gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3033,32 +3028,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129759406</v>
+        <v>129759380</v>
       </c>
       <c r="B26" t="n">
-        <v>80146</v>
+        <v>57733</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229497</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3068,10 +3063,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583688</v>
+        <v>583963</v>
       </c>
       <c r="R26" t="n">
-        <v>6911990</v>
+        <v>6911801</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3104,6 +3099,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska hackspår i liggande gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3431,32 +3431,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129759422</v>
+        <v>129759388</v>
       </c>
       <c r="B30" t="n">
-        <v>98774</v>
+        <v>91891</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>583932</v>
+        <v>584025</v>
       </c>
       <c r="R30" t="n">
-        <v>6911706</v>
+        <v>6911728</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3502,11 +3502,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>6 ex</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3533,32 +3528,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129759388</v>
+        <v>129759422</v>
       </c>
       <c r="B31" t="n">
-        <v>91891</v>
+        <v>98774</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3568,10 +3563,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584025</v>
+        <v>583932</v>
       </c>
       <c r="R31" t="n">
-        <v>6911728</v>
+        <v>6911706</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3604,6 +3599,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>6 ex</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3727,10 +3727,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129759393</v>
+        <v>129759343</v>
       </c>
       <c r="B33" t="n">
-        <v>91891</v>
+        <v>91593</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3738,21 +3738,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3762,10 +3762,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>583944</v>
+        <v>583805</v>
       </c>
       <c r="R33" t="n">
-        <v>6911825</v>
+        <v>6911905</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3824,10 +3824,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129759343</v>
+        <v>129759393</v>
       </c>
       <c r="B34" t="n">
-        <v>91593</v>
+        <v>91891</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3835,21 +3835,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3859,10 +3859,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>583805</v>
+        <v>583944</v>
       </c>
       <c r="R34" t="n">
-        <v>6911905</v>
+        <v>6911825</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4513,10 +4513,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129759345</v>
+        <v>129759428</v>
       </c>
       <c r="B41" t="n">
-        <v>91593</v>
+        <v>91607</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4524,21 +4524,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4548,10 +4548,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584070</v>
+        <v>583782</v>
       </c>
       <c r="R41" t="n">
-        <v>6911921</v>
+        <v>6911933</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4610,32 +4610,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129759400</v>
+        <v>129759396</v>
       </c>
       <c r="B42" t="n">
-        <v>80186</v>
+        <v>97645</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4645,10 +4645,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>583551</v>
+        <v>583804</v>
       </c>
       <c r="R42" t="n">
-        <v>6911946</v>
+        <v>6911895</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4681,11 +4681,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4712,32 +4707,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129759435</v>
+        <v>129759400</v>
       </c>
       <c r="B43" t="n">
-        <v>80221</v>
+        <v>80186</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4747,10 +4742,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>583790</v>
+        <v>583551</v>
       </c>
       <c r="R43" t="n">
-        <v>6911897</v>
+        <v>6911946</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4783,6 +4778,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4809,10 +4809,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129759396</v>
+        <v>129759435</v>
       </c>
       <c r="B44" t="n">
-        <v>97645</v>
+        <v>80221</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4820,21 +4820,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221945</v>
+        <v>6463</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4844,10 +4844,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>583804</v>
+        <v>583790</v>
       </c>
       <c r="R44" t="n">
-        <v>6911895</v>
+        <v>6911897</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4906,10 +4906,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129759428</v>
+        <v>129759345</v>
       </c>
       <c r="B45" t="n">
-        <v>91607</v>
+        <v>91593</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4917,21 +4917,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>583782</v>
+        <v>584070</v>
       </c>
       <c r="R45" t="n">
-        <v>6911933</v>
+        <v>6911921</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6085,32 +6085,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129759383</v>
+        <v>129759433</v>
       </c>
       <c r="B57" t="n">
-        <v>80090</v>
+        <v>79081</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6120,10 +6120,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>584065</v>
+        <v>583652</v>
       </c>
       <c r="R57" t="n">
-        <v>6911889</v>
+        <v>6911949</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6182,10 +6182,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129759376</v>
+        <v>129759383</v>
       </c>
       <c r="B58" t="n">
-        <v>80215</v>
+        <v>80090</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6193,21 +6193,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6217,10 +6217,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>583790</v>
+        <v>584065</v>
       </c>
       <c r="R58" t="n">
-        <v>6911899</v>
+        <v>6911889</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6279,32 +6279,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129759418</v>
+        <v>129759376</v>
       </c>
       <c r="B59" t="n">
-        <v>98774</v>
+        <v>80215</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6314,10 +6314,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>583629</v>
+        <v>583790</v>
       </c>
       <c r="R59" t="n">
-        <v>6911831</v>
+        <v>6911899</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6350,11 +6350,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>35 ex</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6381,7 +6376,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129759416</v>
+        <v>129759418</v>
       </c>
       <c r="B60" t="n">
         <v>98774</v>
@@ -6416,10 +6411,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>583627</v>
+        <v>583629</v>
       </c>
       <c r="R60" t="n">
-        <v>6911841</v>
+        <v>6911831</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6456,7 +6451,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>45 ex</t>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6483,32 +6478,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129759433</v>
+        <v>129759416</v>
       </c>
       <c r="B61" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6518,10 +6513,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>583652</v>
+        <v>583627</v>
       </c>
       <c r="R61" t="n">
-        <v>6911949</v>
+        <v>6911841</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6554,6 +6549,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 48568-2023 artfynd.xlsx
+++ b/artfynd/A 48568-2023 artfynd.xlsx
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129759401</v>
+        <v>129759399</v>
       </c>
       <c r="B5" t="n">
-        <v>80186</v>
+        <v>75117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>229651</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lunglavsknapp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Plectocarpon lichenum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583559</v>
+        <v>583550</v>
       </c>
       <c r="R5" t="n">
-        <v>6911967</v>
+        <v>6911932</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129759399</v>
+        <v>129759401</v>
       </c>
       <c r="B6" t="n">
-        <v>75117</v>
+        <v>80186</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229651</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglavsknapp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Plectocarpon lichenum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Sommerf.) D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583550</v>
+        <v>583559</v>
       </c>
       <c r="R6" t="n">
-        <v>6911932</v>
+        <v>6911967</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129759381</v>
+        <v>129759379</v>
       </c>
       <c r="B7" t="n">
-        <v>80090</v>
+        <v>57733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583783</v>
+        <v>583930</v>
       </c>
       <c r="R7" t="n">
-        <v>6911895</v>
+        <v>6911711</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,6 +1236,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>1 ex, födosökande</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1262,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129759379</v>
+        <v>129759381</v>
       </c>
       <c r="B8" t="n">
-        <v>57733</v>
+        <v>80090</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583930</v>
+        <v>583783</v>
       </c>
       <c r="R8" t="n">
-        <v>6911711</v>
+        <v>6911895</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1333,11 +1338,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>1 ex, födosökande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1947,32 +1947,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129759434</v>
+        <v>129759424</v>
       </c>
       <c r="B15" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1982,10 +1982,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583999</v>
+        <v>583956</v>
       </c>
       <c r="R15" t="n">
-        <v>6911809</v>
+        <v>6911817</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2018,6 +2018,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>90 ex runt en tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2044,32 +2049,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129759424</v>
+        <v>129759434</v>
       </c>
       <c r="B16" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2079,10 +2084,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583956</v>
+        <v>583999</v>
       </c>
       <c r="R16" t="n">
-        <v>6911817</v>
+        <v>6911809</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2115,11 +2120,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>90 ex runt en tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2243,32 +2243,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129759425</v>
+        <v>129759432</v>
       </c>
       <c r="B18" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583999</v>
+        <v>583940</v>
       </c>
       <c r="R18" t="n">
-        <v>6911781</v>
+        <v>6911767</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2314,11 +2314,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>15 ex</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2345,7 +2340,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129759423</v>
+        <v>129759425</v>
       </c>
       <c r="B19" t="n">
         <v>98774</v>
@@ -2380,10 +2375,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583836</v>
+        <v>583999</v>
       </c>
       <c r="R19" t="n">
-        <v>6911810</v>
+        <v>6911781</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2420,7 +2415,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>10 ex</t>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2447,32 +2442,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129759437</v>
+        <v>129759423</v>
       </c>
       <c r="B20" t="n">
-        <v>100963</v>
+        <v>98774</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2482,10 +2477,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583826</v>
+        <v>583836</v>
       </c>
       <c r="R20" t="n">
-        <v>6911855</v>
+        <v>6911810</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2518,6 +2513,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2544,32 +2544,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129759432</v>
+        <v>129759437</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>100963</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583940</v>
+        <v>583826</v>
       </c>
       <c r="R21" t="n">
-        <v>6911767</v>
+        <v>6911855</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2738,32 +2738,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129759384</v>
+        <v>129759380</v>
       </c>
       <c r="B23" t="n">
-        <v>92046</v>
+        <v>57733</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584021</v>
+        <v>583963</v>
       </c>
       <c r="R23" t="n">
-        <v>6911731</v>
+        <v>6911801</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2809,6 +2809,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska hackspår i liggande gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2835,45 +2840,43 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129759406</v>
+        <v>129759404</v>
       </c>
       <c r="B24" t="n">
-        <v>80146</v>
+        <v>92012</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229497</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Korallblylav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stor-Oxögeberget, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583688</v>
+        <v>583819</v>
       </c>
       <c r="R24" t="n">
-        <v>6911990</v>
+        <v>6911717</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2914,6 +2917,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2932,43 +2936,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129759404</v>
+        <v>129759384</v>
       </c>
       <c r="B25" t="n">
-        <v>92012</v>
+        <v>92046</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6040186</v>
+        <v>1209</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stor-Oxögeberget, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583819</v>
+        <v>584021</v>
       </c>
       <c r="R25" t="n">
-        <v>6911717</v>
+        <v>6911731</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3009,7 +3015,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3028,32 +3033,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129759380</v>
+        <v>129759406</v>
       </c>
       <c r="B26" t="n">
-        <v>57733</v>
+        <v>80146</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>229497</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3063,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583963</v>
+        <v>583688</v>
       </c>
       <c r="R26" t="n">
-        <v>6911801</v>
+        <v>6911990</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3099,11 +3104,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färska hackspår i liggande gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3334,32 +3334,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129759385</v>
+        <v>129759388</v>
       </c>
       <c r="B29" t="n">
-        <v>92046</v>
+        <v>91891</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>583791</v>
+        <v>584025</v>
       </c>
       <c r="R29" t="n">
-        <v>6911899</v>
+        <v>6911728</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3431,32 +3431,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129759388</v>
+        <v>129759385</v>
       </c>
       <c r="B30" t="n">
-        <v>91891</v>
+        <v>92046</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584025</v>
+        <v>583791</v>
       </c>
       <c r="R30" t="n">
-        <v>6911728</v>
+        <v>6911899</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3727,10 +3727,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129759343</v>
+        <v>129759393</v>
       </c>
       <c r="B33" t="n">
-        <v>91593</v>
+        <v>91891</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3738,21 +3738,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3762,10 +3762,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>583805</v>
+        <v>583944</v>
       </c>
       <c r="R33" t="n">
-        <v>6911905</v>
+        <v>6911825</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3824,10 +3824,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129759393</v>
+        <v>129759343</v>
       </c>
       <c r="B34" t="n">
-        <v>91891</v>
+        <v>91593</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3835,21 +3835,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3859,10 +3859,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>583944</v>
+        <v>583805</v>
       </c>
       <c r="R34" t="n">
-        <v>6911825</v>
+        <v>6911905</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4416,10 +4416,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129759395</v>
+        <v>129759428</v>
       </c>
       <c r="B40" t="n">
-        <v>91891</v>
+        <v>91607</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4427,21 +4427,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4451,10 +4451,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584070</v>
+        <v>583782</v>
       </c>
       <c r="R40" t="n">
-        <v>6911923</v>
+        <v>6911933</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4513,32 +4513,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129759428</v>
+        <v>129759396</v>
       </c>
       <c r="B41" t="n">
-        <v>91607</v>
+        <v>97645</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1204</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4548,10 +4548,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>583782</v>
+        <v>583804</v>
       </c>
       <c r="R41" t="n">
-        <v>6911933</v>
+        <v>6911895</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4610,32 +4610,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129759396</v>
+        <v>129759395</v>
       </c>
       <c r="B42" t="n">
-        <v>97645</v>
+        <v>91891</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4645,10 +4645,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>583804</v>
+        <v>584070</v>
       </c>
       <c r="R42" t="n">
-        <v>6911895</v>
+        <v>6911923</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5003,10 +5003,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129759378</v>
+        <v>129759405</v>
       </c>
       <c r="B46" t="n">
-        <v>80215</v>
+        <v>80146</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5014,21 +5014,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>229497</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5038,10 +5038,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>583791</v>
+        <v>583549</v>
       </c>
       <c r="R46" t="n">
-        <v>6911883</v>
+        <v>6911932</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5100,32 +5100,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129759402</v>
+        <v>129759378</v>
       </c>
       <c r="B47" t="n">
-        <v>80186</v>
+        <v>80215</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>583797</v>
+        <v>583791</v>
       </c>
       <c r="R47" t="n">
-        <v>6911899</v>
+        <v>6911883</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5197,32 +5197,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129759382</v>
+        <v>129759402</v>
       </c>
       <c r="B48" t="n">
-        <v>80090</v>
+        <v>80186</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5232,10 +5232,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>583791</v>
+        <v>583797</v>
       </c>
       <c r="R48" t="n">
-        <v>6911884</v>
+        <v>6911899</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5294,10 +5294,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129759403</v>
+        <v>129759382</v>
       </c>
       <c r="B49" t="n">
-        <v>80222</v>
+        <v>80090</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5305,21 +5305,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6464</v>
+        <v>6456</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5329,10 +5329,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>583755</v>
+        <v>583791</v>
       </c>
       <c r="R49" t="n">
-        <v>6911971</v>
+        <v>6911884</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5391,10 +5391,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129759405</v>
+        <v>129759403</v>
       </c>
       <c r="B50" t="n">
-        <v>80146</v>
+        <v>80222</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5402,21 +5402,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229497</v>
+        <v>6464</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5426,10 +5426,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>583549</v>
+        <v>583755</v>
       </c>
       <c r="R50" t="n">
-        <v>6911932</v>
+        <v>6911971</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5794,10 +5794,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129759431</v>
+        <v>129759391</v>
       </c>
       <c r="B54" t="n">
-        <v>79081</v>
+        <v>91891</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5805,21 +5805,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5829,10 +5829,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>583549</v>
+        <v>583565</v>
       </c>
       <c r="R54" t="n">
-        <v>6911806</v>
+        <v>6911984</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5891,32 +5891,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129759391</v>
+        <v>129759377</v>
       </c>
       <c r="B55" t="n">
-        <v>91891</v>
+        <v>80215</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5926,10 +5926,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>583565</v>
+        <v>583809</v>
       </c>
       <c r="R55" t="n">
-        <v>6911984</v>
+        <v>6911875</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5988,32 +5988,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129759377</v>
+        <v>129759431</v>
       </c>
       <c r="B56" t="n">
-        <v>80215</v>
+        <v>79081</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6023,10 +6023,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>583809</v>
+        <v>583549</v>
       </c>
       <c r="R56" t="n">
-        <v>6911875</v>
+        <v>6911806</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6085,10 +6085,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129759433</v>
+        <v>129759394</v>
       </c>
       <c r="B57" t="n">
-        <v>79081</v>
+        <v>91891</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6096,21 +6096,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6120,10 +6120,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>583652</v>
+        <v>584057</v>
       </c>
       <c r="R57" t="n">
-        <v>6911949</v>
+        <v>6911892</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6182,32 +6182,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129759383</v>
+        <v>129759418</v>
       </c>
       <c r="B58" t="n">
-        <v>80090</v>
+        <v>98774</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6217,10 +6217,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>584065</v>
+        <v>583629</v>
       </c>
       <c r="R58" t="n">
-        <v>6911889</v>
+        <v>6911831</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6253,6 +6253,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6279,32 +6284,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129759376</v>
+        <v>129759416</v>
       </c>
       <c r="B59" t="n">
-        <v>80215</v>
+        <v>98774</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6314,10 +6319,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>583790</v>
+        <v>583627</v>
       </c>
       <c r="R59" t="n">
-        <v>6911899</v>
+        <v>6911841</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6350,6 +6355,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6376,32 +6386,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129759418</v>
+        <v>129759383</v>
       </c>
       <c r="B60" t="n">
-        <v>98774</v>
+        <v>80090</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6411,10 +6421,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>583629</v>
+        <v>584065</v>
       </c>
       <c r="R60" t="n">
-        <v>6911831</v>
+        <v>6911889</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6447,11 +6457,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>35 ex</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6478,32 +6483,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129759416</v>
+        <v>129759376</v>
       </c>
       <c r="B61" t="n">
-        <v>98774</v>
+        <v>80215</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6513,10 +6518,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>583627</v>
+        <v>583790</v>
       </c>
       <c r="R61" t="n">
-        <v>6911841</v>
+        <v>6911899</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6549,11 +6554,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>45 ex</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6580,10 +6580,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129759394</v>
+        <v>129759433</v>
       </c>
       <c r="B62" t="n">
-        <v>91891</v>
+        <v>79081</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6591,21 +6591,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>584057</v>
+        <v>583652</v>
       </c>
       <c r="R62" t="n">
-        <v>6911892</v>
+        <v>6911949</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>

--- a/artfynd/A 48568-2023 artfynd.xlsx
+++ b/artfynd/A 48568-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129759341</v>
       </c>
       <c r="B2" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129759415</v>
       </c>
       <c r="B4" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129759399</v>
+        <v>129759401</v>
       </c>
       <c r="B5" t="n">
-        <v>75117</v>
+        <v>80186</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229651</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglavsknapp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Plectocarpon lichenum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Sommerf.) D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583550</v>
+        <v>583559</v>
       </c>
       <c r="R5" t="n">
-        <v>6911932</v>
+        <v>6911967</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129759401</v>
+        <v>129759399</v>
       </c>
       <c r="B6" t="n">
-        <v>80186</v>
+        <v>75117</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>229651</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lunglavsknapp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Plectocarpon lichenum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583559</v>
+        <v>583550</v>
       </c>
       <c r="R6" t="n">
-        <v>6911967</v>
+        <v>6911932</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129759379</v>
+        <v>129759381</v>
       </c>
       <c r="B7" t="n">
-        <v>57733</v>
+        <v>80090</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583930</v>
+        <v>583783</v>
       </c>
       <c r="R7" t="n">
-        <v>6911711</v>
+        <v>6911895</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,11 +1236,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>1 ex, födosökande</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129759381</v>
+        <v>129759379</v>
       </c>
       <c r="B8" t="n">
-        <v>80090</v>
+        <v>57733</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583783</v>
+        <v>583930</v>
       </c>
       <c r="R8" t="n">
-        <v>6911895</v>
+        <v>6911711</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1338,6 +1333,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1 ex, födosökande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1367,7 +1367,7 @@
         <v>129759430</v>
       </c>
       <c r="B9" t="n">
-        <v>91613</v>
+        <v>91617</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1457,32 +1457,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129759436</v>
+        <v>129759413</v>
       </c>
       <c r="B10" t="n">
-        <v>80221</v>
+        <v>98778</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583792</v>
+        <v>583755</v>
       </c>
       <c r="R10" t="n">
-        <v>6911886</v>
+        <v>6911734</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1528,6 +1528,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1554,32 +1559,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129759413</v>
+        <v>129759436</v>
       </c>
       <c r="B11" t="n">
-        <v>98774</v>
+        <v>80221</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1589,10 +1594,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583755</v>
+        <v>583792</v>
       </c>
       <c r="R11" t="n">
-        <v>6911734</v>
+        <v>6911886</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1625,11 +1630,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>45 ex</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1659,7 +1659,7 @@
         <v>129759392</v>
       </c>
       <c r="B12" t="n">
-        <v>91891</v>
+        <v>91895</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>129759429</v>
       </c>
       <c r="B13" t="n">
-        <v>91607</v>
+        <v>91611</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,32 +1947,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129759424</v>
+        <v>129759427</v>
       </c>
       <c r="B15" t="n">
-        <v>98774</v>
+        <v>105844</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1982,10 +1982,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583956</v>
+        <v>584003</v>
       </c>
       <c r="R15" t="n">
-        <v>6911817</v>
+        <v>6911804</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2018,11 +2018,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>90 ex runt en tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2049,32 +2044,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129759434</v>
+        <v>129759424</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>98778</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2084,10 +2079,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583999</v>
+        <v>583956</v>
       </c>
       <c r="R16" t="n">
-        <v>6911809</v>
+        <v>6911817</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2120,6 +2115,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>90 ex runt en tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2146,32 +2146,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129759427</v>
+        <v>129759434</v>
       </c>
       <c r="B17" t="n">
-        <v>105840</v>
+        <v>79081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584003</v>
+        <v>583999</v>
       </c>
       <c r="R17" t="n">
-        <v>6911804</v>
+        <v>6911809</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2243,32 +2243,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129759432</v>
+        <v>129759437</v>
       </c>
       <c r="B18" t="n">
-        <v>79081</v>
+        <v>100967</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583940</v>
+        <v>583826</v>
       </c>
       <c r="R18" t="n">
-        <v>6911767</v>
+        <v>6911855</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2340,32 +2340,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129759425</v>
+        <v>129759432</v>
       </c>
       <c r="B19" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583999</v>
+        <v>583940</v>
       </c>
       <c r="R19" t="n">
-        <v>6911781</v>
+        <v>6911767</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2411,11 +2411,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>15 ex</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2442,10 +2437,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129759423</v>
+        <v>129759425</v>
       </c>
       <c r="B20" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2477,10 +2472,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583836</v>
+        <v>583999</v>
       </c>
       <c r="R20" t="n">
-        <v>6911810</v>
+        <v>6911781</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2517,7 +2512,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>10 ex</t>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2544,32 +2539,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129759437</v>
+        <v>129759423</v>
       </c>
       <c r="B21" t="n">
-        <v>100963</v>
+        <v>98778</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2579,10 +2574,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583826</v>
+        <v>583836</v>
       </c>
       <c r="R21" t="n">
-        <v>6911855</v>
+        <v>6911810</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2615,6 +2610,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2644,7 +2644,7 @@
         <v>129759339</v>
       </c>
       <c r="B22" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2738,32 +2738,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129759380</v>
+        <v>129759384</v>
       </c>
       <c r="B23" t="n">
-        <v>57733</v>
+        <v>92050</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583963</v>
+        <v>584021</v>
       </c>
       <c r="R23" t="n">
-        <v>6911801</v>
+        <v>6911731</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2809,11 +2809,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska hackspår i liggande gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2840,10 +2835,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129759404</v>
+        <v>129759380</v>
       </c>
       <c r="B24" t="n">
-        <v>92012</v>
+        <v>57733</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2851,32 +2846,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6040186</v>
+        <v>100049</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stor-Oxögeberget, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583819</v>
+        <v>583963</v>
       </c>
       <c r="R24" t="n">
-        <v>6911717</v>
+        <v>6911801</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2911,13 +2908,17 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska hackspår i liggande gran</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2936,45 +2937,43 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129759384</v>
+        <v>129759404</v>
       </c>
       <c r="B25" t="n">
-        <v>92046</v>
+        <v>92016</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stor-Oxögeberget, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584021</v>
+        <v>583819</v>
       </c>
       <c r="R25" t="n">
-        <v>6911731</v>
+        <v>6911717</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3015,6 +3014,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3130,32 +3130,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129759375</v>
+        <v>129759411</v>
       </c>
       <c r="B27" t="n">
-        <v>57896</v>
+        <v>98778</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>583977</v>
+        <v>583966</v>
       </c>
       <c r="R27" t="n">
-        <v>6911791</v>
+        <v>6911716</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Flera hördes varna</t>
+          <t>29 ex</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3232,32 +3232,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129759411</v>
+        <v>129759375</v>
       </c>
       <c r="B28" t="n">
-        <v>98774</v>
+        <v>57896</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3267,10 +3267,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>583966</v>
+        <v>583977</v>
       </c>
       <c r="R28" t="n">
-        <v>6911716</v>
+        <v>6911791</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>29 ex</t>
+          <t>Flera hördes varna</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3334,32 +3334,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129759388</v>
+        <v>129759385</v>
       </c>
       <c r="B29" t="n">
-        <v>91891</v>
+        <v>92050</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584025</v>
+        <v>583791</v>
       </c>
       <c r="R29" t="n">
-        <v>6911728</v>
+        <v>6911899</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3431,32 +3431,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129759385</v>
+        <v>129759410</v>
       </c>
       <c r="B30" t="n">
-        <v>92046</v>
+        <v>80146</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>229497</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>583791</v>
+        <v>583794</v>
       </c>
       <c r="R30" t="n">
-        <v>6911899</v>
+        <v>6911885</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3528,32 +3528,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129759422</v>
+        <v>129759388</v>
       </c>
       <c r="B31" t="n">
-        <v>98774</v>
+        <v>91895</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3563,10 +3563,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>583932</v>
+        <v>584025</v>
       </c>
       <c r="R31" t="n">
-        <v>6911706</v>
+        <v>6911728</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3599,11 +3599,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>6 ex</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3630,32 +3625,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129759410</v>
+        <v>129759422</v>
       </c>
       <c r="B32" t="n">
-        <v>80146</v>
+        <v>98778</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3665,10 +3660,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>583794</v>
+        <v>583932</v>
       </c>
       <c r="R32" t="n">
-        <v>6911885</v>
+        <v>6911706</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3701,6 +3696,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>6 ex</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3730,7 +3730,7 @@
         <v>129759393</v>
       </c>
       <c r="B33" t="n">
-        <v>91891</v>
+        <v>91895</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>129759343</v>
       </c>
       <c r="B34" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>129759389</v>
       </c>
       <c r="B37" t="n">
-        <v>91891</v>
+        <v>91895</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>129759421</v>
       </c>
       <c r="B38" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>129759414</v>
       </c>
       <c r="B39" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4416,10 +4416,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129759428</v>
+        <v>129759395</v>
       </c>
       <c r="B40" t="n">
-        <v>91607</v>
+        <v>91895</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4427,21 +4427,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4451,10 +4451,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>583782</v>
+        <v>584070</v>
       </c>
       <c r="R40" t="n">
-        <v>6911933</v>
+        <v>6911923</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4513,32 +4513,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129759396</v>
+        <v>129759400</v>
       </c>
       <c r="B41" t="n">
-        <v>97645</v>
+        <v>80186</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4548,10 +4548,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>583804</v>
+        <v>583551</v>
       </c>
       <c r="R41" t="n">
-        <v>6911895</v>
+        <v>6911946</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4584,6 +4584,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4610,32 +4615,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129759395</v>
+        <v>129759435</v>
       </c>
       <c r="B42" t="n">
-        <v>91891</v>
+        <v>80221</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4645,10 +4650,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>584070</v>
+        <v>583790</v>
       </c>
       <c r="R42" t="n">
-        <v>6911923</v>
+        <v>6911897</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4707,10 +4712,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129759400</v>
+        <v>129759428</v>
       </c>
       <c r="B43" t="n">
-        <v>80186</v>
+        <v>91611</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4718,21 +4723,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4742,10 +4747,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>583551</v>
+        <v>583782</v>
       </c>
       <c r="R43" t="n">
-        <v>6911946</v>
+        <v>6911933</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4778,11 +4783,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4809,32 +4809,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129759435</v>
+        <v>129759345</v>
       </c>
       <c r="B44" t="n">
-        <v>80221</v>
+        <v>91597</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4844,10 +4844,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>583790</v>
+        <v>584070</v>
       </c>
       <c r="R44" t="n">
-        <v>6911897</v>
+        <v>6911921</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4906,32 +4906,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129759345</v>
+        <v>129759396</v>
       </c>
       <c r="B45" t="n">
-        <v>91593</v>
+        <v>97649</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584070</v>
+        <v>583804</v>
       </c>
       <c r="R45" t="n">
-        <v>6911921</v>
+        <v>6911895</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5003,32 +5003,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129759405</v>
+        <v>129759402</v>
       </c>
       <c r="B46" t="n">
-        <v>80146</v>
+        <v>80186</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5038,10 +5038,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>583549</v>
+        <v>583797</v>
       </c>
       <c r="R46" t="n">
-        <v>6911932</v>
+        <v>6911899</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5100,10 +5100,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129759378</v>
+        <v>129759382</v>
       </c>
       <c r="B47" t="n">
-        <v>80215</v>
+        <v>80090</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5111,21 +5111,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5138,7 +5138,7 @@
         <v>583791</v>
       </c>
       <c r="R47" t="n">
-        <v>6911883</v>
+        <v>6911884</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5197,32 +5197,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129759402</v>
+        <v>129759403</v>
       </c>
       <c r="B48" t="n">
-        <v>80186</v>
+        <v>80222</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5232,10 +5232,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>583797</v>
+        <v>583755</v>
       </c>
       <c r="R48" t="n">
-        <v>6911899</v>
+        <v>6911971</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5294,10 +5294,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129759382</v>
+        <v>129759378</v>
       </c>
       <c r="B49" t="n">
-        <v>80090</v>
+        <v>80215</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5305,21 +5305,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5332,7 +5332,7 @@
         <v>583791</v>
       </c>
       <c r="R49" t="n">
-        <v>6911884</v>
+        <v>6911883</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5391,10 +5391,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129759403</v>
+        <v>129759405</v>
       </c>
       <c r="B50" t="n">
-        <v>80222</v>
+        <v>80146</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5402,21 +5402,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6464</v>
+        <v>229497</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5426,10 +5426,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>583755</v>
+        <v>583549</v>
       </c>
       <c r="R50" t="n">
-        <v>6911971</v>
+        <v>6911932</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5491,7 +5491,7 @@
         <v>129759419</v>
       </c>
       <c r="B51" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>129759412</v>
       </c>
       <c r="B52" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>129759420</v>
       </c>
       <c r="B53" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>129759391</v>
       </c>
       <c r="B54" t="n">
-        <v>91891</v>
+        <v>91895</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6085,32 +6085,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129759394</v>
+        <v>129759383</v>
       </c>
       <c r="B57" t="n">
-        <v>91891</v>
+        <v>80090</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6120,10 +6120,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>584057</v>
+        <v>584065</v>
       </c>
       <c r="R57" t="n">
-        <v>6911892</v>
+        <v>6911889</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6182,32 +6182,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129759418</v>
+        <v>129759376</v>
       </c>
       <c r="B58" t="n">
-        <v>98774</v>
+        <v>80215</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6217,10 +6217,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>583629</v>
+        <v>583790</v>
       </c>
       <c r="R58" t="n">
-        <v>6911831</v>
+        <v>6911899</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6253,11 +6253,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>35 ex</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6284,32 +6279,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129759416</v>
+        <v>129759433</v>
       </c>
       <c r="B59" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6319,10 +6314,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>583627</v>
+        <v>583652</v>
       </c>
       <c r="R59" t="n">
-        <v>6911841</v>
+        <v>6911949</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6355,11 +6350,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>45 ex</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6386,32 +6376,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129759383</v>
+        <v>129759394</v>
       </c>
       <c r="B60" t="n">
-        <v>80090</v>
+        <v>91895</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6421,10 +6411,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>584065</v>
+        <v>584057</v>
       </c>
       <c r="R60" t="n">
-        <v>6911889</v>
+        <v>6911892</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6483,32 +6473,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129759376</v>
+        <v>129759418</v>
       </c>
       <c r="B61" t="n">
-        <v>80215</v>
+        <v>98778</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6518,10 +6508,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>583790</v>
+        <v>583629</v>
       </c>
       <c r="R61" t="n">
-        <v>6911899</v>
+        <v>6911831</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6554,6 +6544,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6580,32 +6575,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129759433</v>
+        <v>129759416</v>
       </c>
       <c r="B62" t="n">
-        <v>79081</v>
+        <v>98778</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6615,10 +6610,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>583652</v>
+        <v>583627</v>
       </c>
       <c r="R62" t="n">
-        <v>6911949</v>
+        <v>6911841</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6651,6 +6646,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6680,7 +6680,7 @@
         <v>129759387</v>
       </c>
       <c r="B63" t="n">
-        <v>91891</v>
+        <v>91895</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129759370</v>
+        <v>129759357</v>
       </c>
       <c r="B71" t="n">
         <v>57736</v>
@@ -7523,10 +7523,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>584063</v>
+        <v>583586</v>
       </c>
       <c r="R71" t="n">
-        <v>6911870</v>
+        <v>6911868</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7563,7 +7563,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7590,7 +7590,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129759357</v>
+        <v>129759370</v>
       </c>
       <c r="B72" t="n">
         <v>57736</v>
@@ -7625,10 +7625,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>583586</v>
+        <v>584063</v>
       </c>
       <c r="R72" t="n">
-        <v>6911868</v>
+        <v>6911870</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7665,7 +7665,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7998,7 +7998,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129759364</v>
+        <v>129759358</v>
       </c>
       <c r="B76" t="n">
         <v>57736</v>
@@ -8033,10 +8033,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>583922</v>
+        <v>583672</v>
       </c>
       <c r="R76" t="n">
-        <v>6911801</v>
+        <v>6911978</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8100,7 +8100,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129759358</v>
+        <v>129759364</v>
       </c>
       <c r="B77" t="n">
         <v>57736</v>
@@ -8135,10 +8135,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>583672</v>
+        <v>583922</v>
       </c>
       <c r="R77" t="n">
-        <v>6911978</v>
+        <v>6911801</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8304,7 +8304,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129759353</v>
+        <v>129759362</v>
       </c>
       <c r="B79" t="n">
         <v>57736</v>
@@ -8339,10 +8339,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>583756</v>
+        <v>583925</v>
       </c>
       <c r="R79" t="n">
-        <v>6911811</v>
+        <v>6911784</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8406,7 +8406,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129759362</v>
+        <v>129759353</v>
       </c>
       <c r="B80" t="n">
         <v>57736</v>
@@ -8441,10 +8441,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>583925</v>
+        <v>583756</v>
       </c>
       <c r="R80" t="n">
-        <v>6911784</v>
+        <v>6911811</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>

--- a/artfynd/A 48568-2023 artfynd.xlsx
+++ b/artfynd/A 48568-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129759341</v>
       </c>
       <c r="B2" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129759415</v>
       </c>
       <c r="B4" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129759381</v>
+        <v>129759379</v>
       </c>
       <c r="B7" t="n">
-        <v>80090</v>
+        <v>57733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583783</v>
+        <v>583930</v>
       </c>
       <c r="R7" t="n">
-        <v>6911895</v>
+        <v>6911711</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,6 +1236,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>1 ex, födosökande</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1262,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129759379</v>
+        <v>129759381</v>
       </c>
       <c r="B8" t="n">
-        <v>57733</v>
+        <v>80090</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583930</v>
+        <v>583783</v>
       </c>
       <c r="R8" t="n">
-        <v>6911711</v>
+        <v>6911895</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1333,11 +1338,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>1 ex, födosökande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1367,7 +1367,7 @@
         <v>129759430</v>
       </c>
       <c r="B9" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1457,32 +1457,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129759413</v>
+        <v>129759436</v>
       </c>
       <c r="B10" t="n">
-        <v>98778</v>
+        <v>80221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583755</v>
+        <v>583792</v>
       </c>
       <c r="R10" t="n">
-        <v>6911734</v>
+        <v>6911886</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1528,11 +1528,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>45 ex</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1559,32 +1554,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129759436</v>
+        <v>129759413</v>
       </c>
       <c r="B11" t="n">
-        <v>80221</v>
+        <v>98780</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1594,10 +1589,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583792</v>
+        <v>583755</v>
       </c>
       <c r="R11" t="n">
-        <v>6911886</v>
+        <v>6911734</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1630,6 +1625,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1656,32 +1656,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129759392</v>
+        <v>129759397</v>
       </c>
       <c r="B12" t="n">
-        <v>91895</v>
+        <v>80214</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>6461</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583799</v>
+        <v>583679</v>
       </c>
       <c r="R12" t="n">
-        <v>6911903</v>
+        <v>6911975</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129759429</v>
+        <v>129759392</v>
       </c>
       <c r="B13" t="n">
-        <v>91611</v>
+        <v>91897</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1764,21 +1764,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583810</v>
+        <v>583799</v>
       </c>
       <c r="R13" t="n">
-        <v>6911860</v>
+        <v>6911903</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1850,32 +1850,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129759397</v>
+        <v>129759429</v>
       </c>
       <c r="B14" t="n">
-        <v>80214</v>
+        <v>91613</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6461</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>583679</v>
+        <v>583810</v>
       </c>
       <c r="R14" t="n">
-        <v>6911975</v>
+        <v>6911860</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1947,32 +1947,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129759427</v>
+        <v>129759434</v>
       </c>
       <c r="B15" t="n">
-        <v>105844</v>
+        <v>79081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1982,10 +1982,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584003</v>
+        <v>583999</v>
       </c>
       <c r="R15" t="n">
-        <v>6911804</v>
+        <v>6911809</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2044,32 +2044,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129759424</v>
+        <v>129759427</v>
       </c>
       <c r="B16" t="n">
-        <v>98778</v>
+        <v>105846</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583956</v>
+        <v>584003</v>
       </c>
       <c r="R16" t="n">
-        <v>6911817</v>
+        <v>6911804</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2115,11 +2115,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>90 ex runt en tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2146,32 +2141,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129759434</v>
+        <v>129759424</v>
       </c>
       <c r="B17" t="n">
-        <v>79081</v>
+        <v>98780</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2181,10 +2176,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583999</v>
+        <v>583956</v>
       </c>
       <c r="R17" t="n">
-        <v>6911809</v>
+        <v>6911817</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2217,6 +2212,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>90 ex runt en tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2243,32 +2243,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129759437</v>
+        <v>129759432</v>
       </c>
       <c r="B18" t="n">
-        <v>100967</v>
+        <v>79081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583826</v>
+        <v>583940</v>
       </c>
       <c r="R18" t="n">
-        <v>6911855</v>
+        <v>6911767</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2340,32 +2340,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129759432</v>
+        <v>129759425</v>
       </c>
       <c r="B19" t="n">
-        <v>79081</v>
+        <v>98780</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583940</v>
+        <v>583999</v>
       </c>
       <c r="R19" t="n">
-        <v>6911767</v>
+        <v>6911781</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2411,6 +2411,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2437,10 +2442,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129759425</v>
+        <v>129759423</v>
       </c>
       <c r="B20" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2472,10 +2477,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583999</v>
+        <v>583836</v>
       </c>
       <c r="R20" t="n">
-        <v>6911781</v>
+        <v>6911810</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2512,7 +2517,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>15 ex</t>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2539,32 +2544,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129759423</v>
+        <v>129759437</v>
       </c>
       <c r="B21" t="n">
-        <v>98778</v>
+        <v>100969</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2574,10 +2579,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583836</v>
+        <v>583826</v>
       </c>
       <c r="R21" t="n">
-        <v>6911810</v>
+        <v>6911855</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2610,11 +2615,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>10 ex</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2641,32 +2641,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129759339</v>
+        <v>129759384</v>
       </c>
       <c r="B22" t="n">
-        <v>91597</v>
+        <v>92052</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584025</v>
+        <v>584021</v>
       </c>
       <c r="R22" t="n">
-        <v>6911724</v>
+        <v>6911731</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2738,32 +2738,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129759384</v>
+        <v>129759406</v>
       </c>
       <c r="B23" t="n">
-        <v>92050</v>
+        <v>80146</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1209</v>
+        <v>229497</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584021</v>
+        <v>583688</v>
       </c>
       <c r="R23" t="n">
-        <v>6911731</v>
+        <v>6911990</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2937,10 +2937,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129759404</v>
+        <v>129759339</v>
       </c>
       <c r="B25" t="n">
-        <v>92016</v>
+        <v>91599</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2948,32 +2948,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stor-Oxögeberget, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583819</v>
+        <v>584025</v>
       </c>
       <c r="R25" t="n">
-        <v>6911717</v>
+        <v>6911724</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3014,7 +3016,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3033,45 +3034,43 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129759406</v>
+        <v>129759404</v>
       </c>
       <c r="B26" t="n">
-        <v>80146</v>
+        <v>92018</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229497</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Korallblylav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stor-Oxögeberget, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583688</v>
+        <v>583819</v>
       </c>
       <c r="R26" t="n">
-        <v>6911990</v>
+        <v>6911717</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3112,6 +3111,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3130,32 +3130,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129759411</v>
+        <v>129759375</v>
       </c>
       <c r="B27" t="n">
-        <v>98778</v>
+        <v>57896</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>583966</v>
+        <v>583977</v>
       </c>
       <c r="R27" t="n">
-        <v>6911716</v>
+        <v>6911791</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>29 ex</t>
+          <t>Flera hördes varna</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3232,32 +3232,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129759375</v>
+        <v>129759411</v>
       </c>
       <c r="B28" t="n">
-        <v>57896</v>
+        <v>98780</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3267,10 +3267,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>583977</v>
+        <v>583966</v>
       </c>
       <c r="R28" t="n">
-        <v>6911791</v>
+        <v>6911716</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Flera hördes varna</t>
+          <t>29 ex</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3334,32 +3334,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129759385</v>
+        <v>129759388</v>
       </c>
       <c r="B29" t="n">
-        <v>92050</v>
+        <v>91897</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>583791</v>
+        <v>584025</v>
       </c>
       <c r="R29" t="n">
-        <v>6911899</v>
+        <v>6911728</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3528,32 +3528,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129759388</v>
+        <v>129759385</v>
       </c>
       <c r="B31" t="n">
-        <v>91895</v>
+        <v>92052</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3563,10 +3563,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584025</v>
+        <v>583791</v>
       </c>
       <c r="R31" t="n">
-        <v>6911728</v>
+        <v>6911899</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3628,7 +3628,7 @@
         <v>129759422</v>
       </c>
       <c r="B32" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3727,10 +3727,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129759393</v>
+        <v>129759343</v>
       </c>
       <c r="B33" t="n">
-        <v>91895</v>
+        <v>91599</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3738,21 +3738,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3762,10 +3762,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>583944</v>
+        <v>583805</v>
       </c>
       <c r="R33" t="n">
-        <v>6911825</v>
+        <v>6911905</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3824,10 +3824,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129759343</v>
+        <v>129759393</v>
       </c>
       <c r="B34" t="n">
-        <v>91597</v>
+        <v>91897</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3835,21 +3835,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3859,10 +3859,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>583805</v>
+        <v>583944</v>
       </c>
       <c r="R34" t="n">
-        <v>6911905</v>
+        <v>6911825</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4118,7 +4118,7 @@
         <v>129759389</v>
       </c>
       <c r="B37" t="n">
-        <v>91895</v>
+        <v>91897</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>129759421</v>
       </c>
       <c r="B38" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>129759414</v>
       </c>
       <c r="B39" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>129759395</v>
       </c>
       <c r="B40" t="n">
-        <v>91895</v>
+        <v>91897</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4513,32 +4513,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129759400</v>
+        <v>129759396</v>
       </c>
       <c r="B41" t="n">
-        <v>80186</v>
+        <v>97651</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4548,10 +4548,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>583551</v>
+        <v>583804</v>
       </c>
       <c r="R41" t="n">
-        <v>6911946</v>
+        <v>6911895</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4584,11 +4584,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4615,32 +4610,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129759435</v>
+        <v>129759428</v>
       </c>
       <c r="B42" t="n">
-        <v>80221</v>
+        <v>91613</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6463</v>
+        <v>1204</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4650,10 +4645,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>583790</v>
+        <v>583782</v>
       </c>
       <c r="R42" t="n">
-        <v>6911897</v>
+        <v>6911933</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4712,10 +4707,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129759428</v>
+        <v>129759345</v>
       </c>
       <c r="B43" t="n">
-        <v>91611</v>
+        <v>91599</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4723,21 +4718,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4747,10 +4742,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>583782</v>
+        <v>584070</v>
       </c>
       <c r="R43" t="n">
-        <v>6911933</v>
+        <v>6911921</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4809,32 +4804,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129759345</v>
+        <v>129759435</v>
       </c>
       <c r="B44" t="n">
-        <v>91597</v>
+        <v>80221</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4844,10 +4839,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584070</v>
+        <v>583790</v>
       </c>
       <c r="R44" t="n">
-        <v>6911921</v>
+        <v>6911897</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4906,32 +4901,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129759396</v>
+        <v>129759400</v>
       </c>
       <c r="B45" t="n">
-        <v>97649</v>
+        <v>80186</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4941,10 +4936,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>583804</v>
+        <v>583551</v>
       </c>
       <c r="R45" t="n">
-        <v>6911895</v>
+        <v>6911946</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4977,6 +4972,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5491,7 +5491,7 @@
         <v>129759419</v>
       </c>
       <c r="B51" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>129759412</v>
       </c>
       <c r="B52" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>129759420</v>
       </c>
       <c r="B53" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>129759391</v>
       </c>
       <c r="B54" t="n">
-        <v>91895</v>
+        <v>91897</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6085,32 +6085,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129759383</v>
+        <v>129759394</v>
       </c>
       <c r="B57" t="n">
-        <v>80090</v>
+        <v>91897</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6120,10 +6120,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>584065</v>
+        <v>584057</v>
       </c>
       <c r="R57" t="n">
-        <v>6911889</v>
+        <v>6911892</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6376,32 +6376,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129759394</v>
+        <v>129759383</v>
       </c>
       <c r="B60" t="n">
-        <v>91895</v>
+        <v>80090</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6411,10 +6411,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>584057</v>
+        <v>584065</v>
       </c>
       <c r="R60" t="n">
-        <v>6911892</v>
+        <v>6911889</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6476,7 +6476,7 @@
         <v>129759418</v>
       </c>
       <c r="B61" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>129759416</v>
       </c>
       <c r="B62" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>129759387</v>
       </c>
       <c r="B63" t="n">
-        <v>91895</v>
+        <v>91897</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129759350</v>
+        <v>129759361</v>
       </c>
       <c r="B64" t="n">
         <v>57736</v>
@@ -6809,10 +6809,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>583877</v>
+        <v>583916</v>
       </c>
       <c r="R64" t="n">
-        <v>6911708</v>
+        <v>6911778</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6876,7 +6876,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129759361</v>
+        <v>129759350</v>
       </c>
       <c r="B65" t="n">
         <v>57736</v>
@@ -6911,10 +6911,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>583916</v>
+        <v>583877</v>
       </c>
       <c r="R65" t="n">
-        <v>6911778</v>
+        <v>6911708</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7488,7 +7488,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129759357</v>
+        <v>129759370</v>
       </c>
       <c r="B71" t="n">
         <v>57736</v>
@@ -7523,10 +7523,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>583586</v>
+        <v>584063</v>
       </c>
       <c r="R71" t="n">
-        <v>6911868</v>
+        <v>6911870</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7563,7 +7563,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7590,7 +7590,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129759370</v>
+        <v>129759357</v>
       </c>
       <c r="B72" t="n">
         <v>57736</v>
@@ -7625,10 +7625,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>584063</v>
+        <v>583586</v>
       </c>
       <c r="R72" t="n">
-        <v>6911870</v>
+        <v>6911868</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7665,7 +7665,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7998,7 +7998,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129759358</v>
+        <v>129759364</v>
       </c>
       <c r="B76" t="n">
         <v>57736</v>
@@ -8033,10 +8033,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>583672</v>
+        <v>583922</v>
       </c>
       <c r="R76" t="n">
-        <v>6911978</v>
+        <v>6911801</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8100,7 +8100,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129759364</v>
+        <v>129759358</v>
       </c>
       <c r="B77" t="n">
         <v>57736</v>
@@ -8135,10 +8135,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>583922</v>
+        <v>583672</v>
       </c>
       <c r="R77" t="n">
-        <v>6911801</v>
+        <v>6911978</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8304,7 +8304,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129759362</v>
+        <v>129759353</v>
       </c>
       <c r="B79" t="n">
         <v>57736</v>
@@ -8339,10 +8339,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>583925</v>
+        <v>583756</v>
       </c>
       <c r="R79" t="n">
-        <v>6911784</v>
+        <v>6911811</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8406,7 +8406,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129759353</v>
+        <v>129759362</v>
       </c>
       <c r="B80" t="n">
         <v>57736</v>
@@ -8441,10 +8441,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>583756</v>
+        <v>583925</v>
       </c>
       <c r="R80" t="n">
-        <v>6911811</v>
+        <v>6911784</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>

--- a/artfynd/A 48568-2023 artfynd.xlsx
+++ b/artfynd/A 48568-2023 artfynd.xlsx
@@ -1457,32 +1457,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129759436</v>
+        <v>129759413</v>
       </c>
       <c r="B10" t="n">
-        <v>80221</v>
+        <v>98780</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583792</v>
+        <v>583755</v>
       </c>
       <c r="R10" t="n">
-        <v>6911886</v>
+        <v>6911734</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1528,6 +1528,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1554,32 +1559,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129759413</v>
+        <v>129759436</v>
       </c>
       <c r="B11" t="n">
-        <v>98780</v>
+        <v>80221</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1589,10 +1594,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583755</v>
+        <v>583792</v>
       </c>
       <c r="R11" t="n">
-        <v>6911734</v>
+        <v>6911886</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1625,11 +1630,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>45 ex</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1656,32 +1656,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129759397</v>
+        <v>129759392</v>
       </c>
       <c r="B12" t="n">
-        <v>80214</v>
+        <v>91897</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583679</v>
+        <v>583799</v>
       </c>
       <c r="R12" t="n">
-        <v>6911975</v>
+        <v>6911903</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129759392</v>
+        <v>129759429</v>
       </c>
       <c r="B13" t="n">
-        <v>91897</v>
+        <v>91613</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1764,21 +1764,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583799</v>
+        <v>583810</v>
       </c>
       <c r="R13" t="n">
-        <v>6911903</v>
+        <v>6911860</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1850,32 +1850,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129759429</v>
+        <v>129759397</v>
       </c>
       <c r="B14" t="n">
-        <v>91613</v>
+        <v>80214</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>6461</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>583810</v>
+        <v>583679</v>
       </c>
       <c r="R14" t="n">
-        <v>6911860</v>
+        <v>6911975</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2641,45 +2641,43 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129759384</v>
+        <v>129759404</v>
       </c>
       <c r="B22" t="n">
-        <v>92052</v>
+        <v>92018</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stor-Oxögeberget, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584021</v>
+        <v>583819</v>
       </c>
       <c r="R22" t="n">
-        <v>6911731</v>
+        <v>6911717</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2720,6 +2718,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2835,10 +2834,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129759380</v>
+        <v>129759339</v>
       </c>
       <c r="B24" t="n">
-        <v>57733</v>
+        <v>91599</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2846,21 +2845,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2870,10 +2869,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583963</v>
+        <v>584025</v>
       </c>
       <c r="R24" t="n">
-        <v>6911801</v>
+        <v>6911724</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2906,11 +2905,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska hackspår i liggande gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2937,32 +2931,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129759339</v>
+        <v>129759384</v>
       </c>
       <c r="B25" t="n">
-        <v>91599</v>
+        <v>92052</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2972,10 +2966,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584025</v>
+        <v>584021</v>
       </c>
       <c r="R25" t="n">
-        <v>6911724</v>
+        <v>6911731</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3034,10 +3028,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129759404</v>
+        <v>129759380</v>
       </c>
       <c r="B26" t="n">
-        <v>92018</v>
+        <v>57733</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3045,32 +3039,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6040186</v>
+        <v>100049</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stor-Oxögeberget, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583819</v>
+        <v>583963</v>
       </c>
       <c r="R26" t="n">
-        <v>6911717</v>
+        <v>6911801</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3105,13 +3101,17 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska hackspår i liggande gran</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3727,10 +3727,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129759343</v>
+        <v>129759393</v>
       </c>
       <c r="B33" t="n">
-        <v>91599</v>
+        <v>91897</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3738,21 +3738,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3762,10 +3762,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>583805</v>
+        <v>583944</v>
       </c>
       <c r="R33" t="n">
-        <v>6911905</v>
+        <v>6911825</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3824,10 +3824,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129759393</v>
+        <v>129759343</v>
       </c>
       <c r="B34" t="n">
-        <v>91897</v>
+        <v>91599</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3835,21 +3835,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3859,10 +3859,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>583944</v>
+        <v>583805</v>
       </c>
       <c r="R34" t="n">
-        <v>6911825</v>
+        <v>6911905</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4115,32 +4115,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129759389</v>
+        <v>129759421</v>
       </c>
       <c r="B37" t="n">
-        <v>91897</v>
+        <v>98780</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>583704</v>
+        <v>583940</v>
       </c>
       <c r="R37" t="n">
-        <v>6911854</v>
+        <v>6911780</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4186,6 +4186,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>7 ex</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4212,7 +4217,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129759421</v>
+        <v>129759414</v>
       </c>
       <c r="B38" t="n">
         <v>98780</v>
@@ -4247,10 +4252,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>583940</v>
+        <v>583765</v>
       </c>
       <c r="R38" t="n">
-        <v>6911780</v>
+        <v>6911752</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4287,7 +4292,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>7 ex</t>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4314,32 +4319,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129759414</v>
+        <v>129759389</v>
       </c>
       <c r="B39" t="n">
-        <v>98780</v>
+        <v>91897</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4349,10 +4354,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>583765</v>
+        <v>583704</v>
       </c>
       <c r="R39" t="n">
-        <v>6911752</v>
+        <v>6911854</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4385,11 +4390,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>15 ex</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5003,32 +5003,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129759402</v>
+        <v>129759405</v>
       </c>
       <c r="B46" t="n">
-        <v>80186</v>
+        <v>80146</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5038,10 +5038,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>583797</v>
+        <v>583549</v>
       </c>
       <c r="R46" t="n">
-        <v>6911899</v>
+        <v>6911932</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5100,32 +5100,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129759382</v>
+        <v>129759402</v>
       </c>
       <c r="B47" t="n">
-        <v>80090</v>
+        <v>80186</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>583791</v>
+        <v>583797</v>
       </c>
       <c r="R47" t="n">
-        <v>6911884</v>
+        <v>6911899</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5197,10 +5197,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129759403</v>
+        <v>129759382</v>
       </c>
       <c r="B48" t="n">
-        <v>80222</v>
+        <v>80090</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5208,21 +5208,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6464</v>
+        <v>6456</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5232,10 +5232,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>583755</v>
+        <v>583791</v>
       </c>
       <c r="R48" t="n">
-        <v>6911971</v>
+        <v>6911884</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5294,10 +5294,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129759378</v>
+        <v>129759403</v>
       </c>
       <c r="B49" t="n">
-        <v>80215</v>
+        <v>80222</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5305,21 +5305,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5329,10 +5329,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>583791</v>
+        <v>583755</v>
       </c>
       <c r="R49" t="n">
-        <v>6911883</v>
+        <v>6911971</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5391,10 +5391,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129759405</v>
+        <v>129759378</v>
       </c>
       <c r="B50" t="n">
-        <v>80146</v>
+        <v>80215</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5402,21 +5402,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5426,10 +5426,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>583549</v>
+        <v>583791</v>
       </c>
       <c r="R50" t="n">
-        <v>6911932</v>
+        <v>6911883</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5794,32 +5794,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129759391</v>
+        <v>129759377</v>
       </c>
       <c r="B54" t="n">
-        <v>91897</v>
+        <v>80215</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5829,10 +5829,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>583565</v>
+        <v>583809</v>
       </c>
       <c r="R54" t="n">
-        <v>6911984</v>
+        <v>6911875</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5891,32 +5891,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129759377</v>
+        <v>129759431</v>
       </c>
       <c r="B55" t="n">
-        <v>80215</v>
+        <v>79081</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5926,10 +5926,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>583809</v>
+        <v>583549</v>
       </c>
       <c r="R55" t="n">
-        <v>6911875</v>
+        <v>6911806</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5988,10 +5988,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129759431</v>
+        <v>129759391</v>
       </c>
       <c r="B56" t="n">
-        <v>79081</v>
+        <v>91897</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5999,21 +5999,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6023,10 +6023,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>583549</v>
+        <v>583565</v>
       </c>
       <c r="R56" t="n">
-        <v>6911806</v>
+        <v>6911984</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>

--- a/artfynd/A 48568-2023 artfynd.xlsx
+++ b/artfynd/A 48568-2023 artfynd.xlsx
@@ -1656,32 +1656,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129759392</v>
+        <v>129759397</v>
       </c>
       <c r="B12" t="n">
-        <v>91897</v>
+        <v>80214</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>6461</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583799</v>
+        <v>583679</v>
       </c>
       <c r="R12" t="n">
-        <v>6911903</v>
+        <v>6911975</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129759429</v>
+        <v>129759392</v>
       </c>
       <c r="B13" t="n">
-        <v>91613</v>
+        <v>91897</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1764,21 +1764,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583810</v>
+        <v>583799</v>
       </c>
       <c r="R13" t="n">
-        <v>6911860</v>
+        <v>6911903</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1850,32 +1850,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129759397</v>
+        <v>129759429</v>
       </c>
       <c r="B14" t="n">
-        <v>80214</v>
+        <v>91613</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6461</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>583679</v>
+        <v>583810</v>
       </c>
       <c r="R14" t="n">
-        <v>6911975</v>
+        <v>6911860</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2641,43 +2641,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129759404</v>
+        <v>129759384</v>
       </c>
       <c r="B22" t="n">
-        <v>92018</v>
+        <v>92052</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6040186</v>
+        <v>1209</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stor-Oxögeberget, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>583819</v>
+        <v>584021</v>
       </c>
       <c r="R22" t="n">
-        <v>6911717</v>
+        <v>6911731</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2718,7 +2720,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2834,10 +2835,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129759339</v>
+        <v>129759380</v>
       </c>
       <c r="B24" t="n">
-        <v>91599</v>
+        <v>57733</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2845,21 +2846,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2869,10 +2870,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584025</v>
+        <v>583963</v>
       </c>
       <c r="R24" t="n">
-        <v>6911724</v>
+        <v>6911801</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2905,6 +2906,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska hackspår i liggande gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2931,32 +2937,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129759384</v>
+        <v>129759339</v>
       </c>
       <c r="B25" t="n">
-        <v>92052</v>
+        <v>91599</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2966,10 +2972,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584021</v>
+        <v>584025</v>
       </c>
       <c r="R25" t="n">
-        <v>6911731</v>
+        <v>6911724</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3028,10 +3034,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129759380</v>
+        <v>129759404</v>
       </c>
       <c r="B26" t="n">
-        <v>57733</v>
+        <v>92018</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3039,34 +3045,32 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stor-Oxögeberget, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583963</v>
+        <v>583819</v>
       </c>
       <c r="R26" t="n">
-        <v>6911801</v>
+        <v>6911717</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3101,17 +3105,13 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färska hackspår i liggande gran</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -4416,32 +4416,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129759395</v>
+        <v>129759435</v>
       </c>
       <c r="B40" t="n">
-        <v>91897</v>
+        <v>80221</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4451,10 +4451,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584070</v>
+        <v>583790</v>
       </c>
       <c r="R40" t="n">
-        <v>6911923</v>
+        <v>6911897</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4513,32 +4513,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129759396</v>
+        <v>129759400</v>
       </c>
       <c r="B41" t="n">
-        <v>97651</v>
+        <v>80186</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4548,10 +4548,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>583804</v>
+        <v>583551</v>
       </c>
       <c r="R41" t="n">
-        <v>6911895</v>
+        <v>6911946</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4584,6 +4584,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4804,32 +4809,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129759435</v>
+        <v>129759395</v>
       </c>
       <c r="B44" t="n">
-        <v>80221</v>
+        <v>91897</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4839,10 +4844,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>583790</v>
+        <v>584070</v>
       </c>
       <c r="R44" t="n">
-        <v>6911897</v>
+        <v>6911923</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4901,32 +4906,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129759400</v>
+        <v>129759396</v>
       </c>
       <c r="B45" t="n">
-        <v>80186</v>
+        <v>97651</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4936,10 +4941,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>583551</v>
+        <v>583804</v>
       </c>
       <c r="R45" t="n">
-        <v>6911946</v>
+        <v>6911895</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4972,11 +4977,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5794,32 +5794,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129759377</v>
+        <v>129759431</v>
       </c>
       <c r="B54" t="n">
-        <v>80215</v>
+        <v>79081</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5829,10 +5829,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>583809</v>
+        <v>583549</v>
       </c>
       <c r="R54" t="n">
-        <v>6911875</v>
+        <v>6911806</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5891,10 +5891,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129759431</v>
+        <v>129759391</v>
       </c>
       <c r="B55" t="n">
-        <v>79081</v>
+        <v>91897</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5902,21 +5902,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5926,10 +5926,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>583549</v>
+        <v>583565</v>
       </c>
       <c r="R55" t="n">
-        <v>6911806</v>
+        <v>6911984</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5988,32 +5988,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129759391</v>
+        <v>129759377</v>
       </c>
       <c r="B56" t="n">
-        <v>91897</v>
+        <v>80215</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6023,10 +6023,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>583565</v>
+        <v>583809</v>
       </c>
       <c r="R56" t="n">
-        <v>6911984</v>
+        <v>6911875</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>

--- a/artfynd/A 48568-2023 artfynd.xlsx
+++ b/artfynd/A 48568-2023 artfynd.xlsx
@@ -2641,45 +2641,43 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129759384</v>
+        <v>129759404</v>
       </c>
       <c r="B22" t="n">
-        <v>92052</v>
+        <v>92018</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stor-Oxögeberget, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584021</v>
+        <v>583819</v>
       </c>
       <c r="R22" t="n">
-        <v>6911731</v>
+        <v>6911717</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2720,6 +2718,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2835,10 +2834,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129759380</v>
+        <v>129759339</v>
       </c>
       <c r="B24" t="n">
-        <v>57733</v>
+        <v>91599</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2846,21 +2845,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2870,10 +2869,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583963</v>
+        <v>584025</v>
       </c>
       <c r="R24" t="n">
-        <v>6911801</v>
+        <v>6911724</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2906,11 +2905,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska hackspår i liggande gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2937,32 +2931,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129759339</v>
+        <v>129759384</v>
       </c>
       <c r="B25" t="n">
-        <v>91599</v>
+        <v>92052</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2972,10 +2966,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584025</v>
+        <v>584021</v>
       </c>
       <c r="R25" t="n">
-        <v>6911724</v>
+        <v>6911731</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3034,10 +3028,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129759404</v>
+        <v>129759380</v>
       </c>
       <c r="B26" t="n">
-        <v>92018</v>
+        <v>57733</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3045,32 +3039,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6040186</v>
+        <v>100049</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stor-Oxögeberget, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583819</v>
+        <v>583963</v>
       </c>
       <c r="R26" t="n">
-        <v>6911717</v>
+        <v>6911801</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3105,13 +3101,17 @@
           <t>2025-11-19</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska hackspår i liggande gran</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -4416,32 +4416,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129759435</v>
+        <v>129759395</v>
       </c>
       <c r="B40" t="n">
-        <v>80221</v>
+        <v>91897</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4451,10 +4451,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>583790</v>
+        <v>584070</v>
       </c>
       <c r="R40" t="n">
-        <v>6911897</v>
+        <v>6911923</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4513,32 +4513,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129759400</v>
+        <v>129759396</v>
       </c>
       <c r="B41" t="n">
-        <v>80186</v>
+        <v>97651</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4548,10 +4548,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>583551</v>
+        <v>583804</v>
       </c>
       <c r="R41" t="n">
-        <v>6911946</v>
+        <v>6911895</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4584,11 +4584,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4809,32 +4804,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129759395</v>
+        <v>129759435</v>
       </c>
       <c r="B44" t="n">
-        <v>91897</v>
+        <v>80221</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4844,10 +4839,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584070</v>
+        <v>583790</v>
       </c>
       <c r="R44" t="n">
-        <v>6911923</v>
+        <v>6911897</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4906,32 +4901,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129759396</v>
+        <v>129759400</v>
       </c>
       <c r="B45" t="n">
-        <v>97651</v>
+        <v>80186</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4941,10 +4936,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>583804</v>
+        <v>583551</v>
       </c>
       <c r="R45" t="n">
-        <v>6911895</v>
+        <v>6911946</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4977,6 +4972,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 48568-2023 artfynd.xlsx
+++ b/artfynd/A 48568-2023 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129759398</v>
+        <v>129759415</v>
       </c>
       <c r="B3" t="n">
-        <v>80214</v>
+        <v>98790</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583824</v>
+        <v>583723</v>
       </c>
       <c r="R3" t="n">
-        <v>6911829</v>
+        <v>6911832</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129759415</v>
+        <v>129759398</v>
       </c>
       <c r="B4" t="n">
-        <v>98780</v>
+        <v>80214</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583723</v>
+        <v>583824</v>
       </c>
       <c r="R4" t="n">
-        <v>6911832</v>
+        <v>6911829</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129759379</v>
+        <v>129759381</v>
       </c>
       <c r="B7" t="n">
-        <v>57733</v>
+        <v>80090</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583930</v>
+        <v>583783</v>
       </c>
       <c r="R7" t="n">
-        <v>6911711</v>
+        <v>6911895</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,11 +1236,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>1 ex, födosökande</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129759381</v>
+        <v>129759379</v>
       </c>
       <c r="B8" t="n">
-        <v>80090</v>
+        <v>57733</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583783</v>
+        <v>583930</v>
       </c>
       <c r="R8" t="n">
-        <v>6911895</v>
+        <v>6911711</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1338,6 +1333,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1 ex, födosökande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,32 +1457,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129759413</v>
+        <v>129759436</v>
       </c>
       <c r="B10" t="n">
-        <v>98780</v>
+        <v>80221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583755</v>
+        <v>583792</v>
       </c>
       <c r="R10" t="n">
-        <v>6911734</v>
+        <v>6911886</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1528,11 +1528,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>45 ex</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1559,32 +1554,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129759436</v>
+        <v>129759413</v>
       </c>
       <c r="B11" t="n">
-        <v>80221</v>
+        <v>98790</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1594,10 +1589,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583792</v>
+        <v>583755</v>
       </c>
       <c r="R11" t="n">
-        <v>6911886</v>
+        <v>6911734</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1630,6 +1625,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1656,32 +1656,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129759397</v>
+        <v>129759429</v>
       </c>
       <c r="B12" t="n">
-        <v>80214</v>
+        <v>91613</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583679</v>
+        <v>583810</v>
       </c>
       <c r="R12" t="n">
-        <v>6911975</v>
+        <v>6911860</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,32 +1850,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129759429</v>
+        <v>129759397</v>
       </c>
       <c r="B14" t="n">
-        <v>91613</v>
+        <v>80214</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>6461</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>583810</v>
+        <v>583679</v>
       </c>
       <c r="R14" t="n">
-        <v>6911860</v>
+        <v>6911975</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1947,32 +1947,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129759434</v>
+        <v>129759424</v>
       </c>
       <c r="B15" t="n">
-        <v>79081</v>
+        <v>98790</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1982,10 +1982,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583999</v>
+        <v>583956</v>
       </c>
       <c r="R15" t="n">
-        <v>6911809</v>
+        <v>6911817</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2018,6 +2018,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>90 ex runt en tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2047,7 +2052,7 @@
         <v>129759427</v>
       </c>
       <c r="B16" t="n">
-        <v>105846</v>
+        <v>105856</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2141,32 +2146,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129759424</v>
+        <v>129759434</v>
       </c>
       <c r="B17" t="n">
-        <v>98780</v>
+        <v>79081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2176,10 +2181,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583956</v>
+        <v>583999</v>
       </c>
       <c r="R17" t="n">
-        <v>6911817</v>
+        <v>6911809</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2212,11 +2217,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>90 ex runt en tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2343,7 +2343,7 @@
         <v>129759425</v>
       </c>
       <c r="B19" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>129759423</v>
       </c>
       <c r="B20" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>129759437</v>
       </c>
       <c r="B21" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2641,10 +2641,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129759404</v>
+        <v>129759339</v>
       </c>
       <c r="B22" t="n">
-        <v>92018</v>
+        <v>91599</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2652,32 +2652,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stor-Oxögeberget, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>583819</v>
+        <v>584025</v>
       </c>
       <c r="R22" t="n">
-        <v>6911717</v>
+        <v>6911724</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2718,7 +2720,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2737,32 +2738,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129759406</v>
+        <v>129759384</v>
       </c>
       <c r="B23" t="n">
-        <v>80146</v>
+        <v>92052</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2772,10 +2773,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583688</v>
+        <v>584021</v>
       </c>
       <c r="R23" t="n">
-        <v>6911990</v>
+        <v>6911731</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2834,10 +2835,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129759339</v>
+        <v>129759380</v>
       </c>
       <c r="B24" t="n">
-        <v>91599</v>
+        <v>57733</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2845,21 +2846,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2869,10 +2870,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584025</v>
+        <v>583963</v>
       </c>
       <c r="R24" t="n">
-        <v>6911724</v>
+        <v>6911801</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2905,6 +2906,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska hackspår i liggande gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2931,32 +2937,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129759384</v>
+        <v>129759406</v>
       </c>
       <c r="B25" t="n">
-        <v>92052</v>
+        <v>80146</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>229497</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2966,10 +2972,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584021</v>
+        <v>583688</v>
       </c>
       <c r="R25" t="n">
-        <v>6911731</v>
+        <v>6911990</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3028,10 +3034,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129759380</v>
+        <v>129759404</v>
       </c>
       <c r="B26" t="n">
-        <v>57733</v>
+        <v>92018</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3039,34 +3045,32 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stor-Oxögeberget, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583963</v>
+        <v>583819</v>
       </c>
       <c r="R26" t="n">
-        <v>6911801</v>
+        <v>6911717</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3101,17 +3105,13 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färska hackspår i liggande gran</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3235,7 +3235,7 @@
         <v>129759411</v>
       </c>
       <c r="B28" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3431,32 +3431,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129759410</v>
+        <v>129759385</v>
       </c>
       <c r="B30" t="n">
-        <v>80146</v>
+        <v>92052</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229497</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>583794</v>
+        <v>583791</v>
       </c>
       <c r="R30" t="n">
-        <v>6911885</v>
+        <v>6911899</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3528,32 +3528,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129759385</v>
+        <v>129759410</v>
       </c>
       <c r="B31" t="n">
-        <v>92052</v>
+        <v>80146</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>229497</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3563,10 +3563,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>583791</v>
+        <v>583794</v>
       </c>
       <c r="R31" t="n">
-        <v>6911899</v>
+        <v>6911885</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3628,7 +3628,7 @@
         <v>129759422</v>
       </c>
       <c r="B32" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3727,10 +3727,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129759393</v>
+        <v>129759343</v>
       </c>
       <c r="B33" t="n">
-        <v>91897</v>
+        <v>91599</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3738,21 +3738,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3762,10 +3762,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>583944</v>
+        <v>583805</v>
       </c>
       <c r="R33" t="n">
-        <v>6911825</v>
+        <v>6911905</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3824,10 +3824,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129759343</v>
+        <v>129759393</v>
       </c>
       <c r="B34" t="n">
-        <v>91599</v>
+        <v>91897</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3835,21 +3835,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3859,10 +3859,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>583805</v>
+        <v>583944</v>
       </c>
       <c r="R34" t="n">
-        <v>6911905</v>
+        <v>6911825</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4118,7 +4118,7 @@
         <v>129759421</v>
       </c>
       <c r="B37" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         <v>129759414</v>
       </c>
       <c r="B38" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4416,32 +4416,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129759395</v>
+        <v>129759396</v>
       </c>
       <c r="B40" t="n">
-        <v>91897</v>
+        <v>97661</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4451,10 +4451,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584070</v>
+        <v>583804</v>
       </c>
       <c r="R40" t="n">
-        <v>6911923</v>
+        <v>6911895</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4513,32 +4513,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129759396</v>
+        <v>129759395</v>
       </c>
       <c r="B41" t="n">
-        <v>97651</v>
+        <v>91897</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4548,10 +4548,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>583804</v>
+        <v>584070</v>
       </c>
       <c r="R41" t="n">
-        <v>6911895</v>
+        <v>6911923</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5003,32 +5003,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129759405</v>
+        <v>129759402</v>
       </c>
       <c r="B46" t="n">
-        <v>80146</v>
+        <v>80186</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5038,10 +5038,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>583549</v>
+        <v>583797</v>
       </c>
       <c r="R46" t="n">
-        <v>6911932</v>
+        <v>6911899</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5100,32 +5100,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129759402</v>
+        <v>129759382</v>
       </c>
       <c r="B47" t="n">
-        <v>80186</v>
+        <v>80090</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>583797</v>
+        <v>583791</v>
       </c>
       <c r="R47" t="n">
-        <v>6911899</v>
+        <v>6911884</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5197,10 +5197,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129759382</v>
+        <v>129759403</v>
       </c>
       <c r="B48" t="n">
-        <v>80090</v>
+        <v>80222</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5208,21 +5208,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6456</v>
+        <v>6464</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5232,10 +5232,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>583791</v>
+        <v>583755</v>
       </c>
       <c r="R48" t="n">
-        <v>6911884</v>
+        <v>6911971</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5294,10 +5294,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129759403</v>
+        <v>129759378</v>
       </c>
       <c r="B49" t="n">
-        <v>80222</v>
+        <v>80215</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5305,21 +5305,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5329,10 +5329,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>583755</v>
+        <v>583791</v>
       </c>
       <c r="R49" t="n">
-        <v>6911971</v>
+        <v>6911883</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5391,10 +5391,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129759378</v>
+        <v>129759405</v>
       </c>
       <c r="B50" t="n">
-        <v>80215</v>
+        <v>80146</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5402,21 +5402,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6462</v>
+        <v>229497</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5426,10 +5426,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>583791</v>
+        <v>583549</v>
       </c>
       <c r="R50" t="n">
-        <v>6911883</v>
+        <v>6911932</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5491,7 +5491,7 @@
         <v>129759419</v>
       </c>
       <c r="B51" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>129759412</v>
       </c>
       <c r="B52" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>129759420</v>
       </c>
       <c r="B53" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5794,10 +5794,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129759431</v>
+        <v>129759391</v>
       </c>
       <c r="B54" t="n">
-        <v>79081</v>
+        <v>91897</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5805,21 +5805,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5829,10 +5829,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>583549</v>
+        <v>583565</v>
       </c>
       <c r="R54" t="n">
-        <v>6911806</v>
+        <v>6911984</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5891,10 +5891,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129759391</v>
+        <v>129759431</v>
       </c>
       <c r="B55" t="n">
-        <v>91897</v>
+        <v>79081</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5902,21 +5902,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5926,10 +5926,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>583565</v>
+        <v>583549</v>
       </c>
       <c r="R55" t="n">
-        <v>6911984</v>
+        <v>6911806</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6182,32 +6182,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129759376</v>
+        <v>129759433</v>
       </c>
       <c r="B58" t="n">
-        <v>80215</v>
+        <v>79081</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6217,10 +6217,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>583790</v>
+        <v>583652</v>
       </c>
       <c r="R58" t="n">
-        <v>6911899</v>
+        <v>6911949</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6279,32 +6279,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129759433</v>
+        <v>129759376</v>
       </c>
       <c r="B59" t="n">
-        <v>79081</v>
+        <v>80215</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6314,10 +6314,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>583652</v>
+        <v>583790</v>
       </c>
       <c r="R59" t="n">
-        <v>6911949</v>
+        <v>6911899</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6476,7 +6476,7 @@
         <v>129759418</v>
       </c>
       <c r="B61" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>129759416</v>
       </c>
       <c r="B62" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129759361</v>
+        <v>129759350</v>
       </c>
       <c r="B64" t="n">
         <v>57736</v>
@@ -6809,10 +6809,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>583916</v>
+        <v>583877</v>
       </c>
       <c r="R64" t="n">
-        <v>6911778</v>
+        <v>6911708</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6876,7 +6876,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129759350</v>
+        <v>129759361</v>
       </c>
       <c r="B65" t="n">
         <v>57736</v>
@@ -6911,10 +6911,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>583877</v>
+        <v>583916</v>
       </c>
       <c r="R65" t="n">
-        <v>6911708</v>
+        <v>6911778</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>

--- a/artfynd/A 48568-2023 artfynd.xlsx
+++ b/artfynd/A 48568-2023 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129759415</v>
+        <v>129759398</v>
       </c>
       <c r="B3" t="n">
-        <v>98790</v>
+        <v>80214</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583723</v>
+        <v>583824</v>
       </c>
       <c r="R3" t="n">
-        <v>6911832</v>
+        <v>6911829</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129759398</v>
+        <v>129759415</v>
       </c>
       <c r="B4" t="n">
-        <v>80214</v>
+        <v>98790</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583824</v>
+        <v>583723</v>
       </c>
       <c r="R4" t="n">
-        <v>6911829</v>
+        <v>6911832</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -2937,45 +2937,43 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129759406</v>
+        <v>129759404</v>
       </c>
       <c r="B25" t="n">
-        <v>80146</v>
+        <v>92018</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229497</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Korallblylav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stor-Oxögeberget, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583688</v>
+        <v>583819</v>
       </c>
       <c r="R25" t="n">
-        <v>6911990</v>
+        <v>6911717</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3016,6 +3014,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3034,43 +3033,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129759404</v>
+        <v>129759406</v>
       </c>
       <c r="B26" t="n">
-        <v>92018</v>
+        <v>80146</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6040186</v>
+        <v>229497</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stor-Oxögeberget, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583819</v>
+        <v>583688</v>
       </c>
       <c r="R26" t="n">
-        <v>6911717</v>
+        <v>6911990</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3111,7 +3112,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3334,32 +3334,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129759388</v>
+        <v>129759385</v>
       </c>
       <c r="B29" t="n">
-        <v>91897</v>
+        <v>92052</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584025</v>
+        <v>583791</v>
       </c>
       <c r="R29" t="n">
-        <v>6911728</v>
+        <v>6911899</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3431,10 +3431,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129759385</v>
+        <v>129759422</v>
       </c>
       <c r="B30" t="n">
-        <v>92052</v>
+        <v>98790</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3442,21 +3442,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>583791</v>
+        <v>583932</v>
       </c>
       <c r="R30" t="n">
-        <v>6911899</v>
+        <v>6911706</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3502,6 +3502,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>6 ex</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3625,32 +3630,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129759422</v>
+        <v>129759388</v>
       </c>
       <c r="B32" t="n">
-        <v>98790</v>
+        <v>91897</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3660,10 +3665,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>583932</v>
+        <v>584025</v>
       </c>
       <c r="R32" t="n">
-        <v>6911706</v>
+        <v>6911728</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3696,11 +3701,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>6 ex</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4416,32 +4416,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129759396</v>
+        <v>129759395</v>
       </c>
       <c r="B40" t="n">
-        <v>97661</v>
+        <v>91897</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4451,10 +4451,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>583804</v>
+        <v>584070</v>
       </c>
       <c r="R40" t="n">
-        <v>6911895</v>
+        <v>6911923</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4513,32 +4513,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129759395</v>
+        <v>129759396</v>
       </c>
       <c r="B41" t="n">
-        <v>91897</v>
+        <v>97661</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4548,10 +4548,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584070</v>
+        <v>583804</v>
       </c>
       <c r="R41" t="n">
-        <v>6911923</v>
+        <v>6911895</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5003,32 +5003,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129759402</v>
+        <v>129759405</v>
       </c>
       <c r="B46" t="n">
-        <v>80186</v>
+        <v>80146</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5038,10 +5038,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>583797</v>
+        <v>583549</v>
       </c>
       <c r="R46" t="n">
-        <v>6911899</v>
+        <v>6911932</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5100,32 +5100,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129759382</v>
+        <v>129759402</v>
       </c>
       <c r="B47" t="n">
-        <v>80090</v>
+        <v>80186</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>583791</v>
+        <v>583797</v>
       </c>
       <c r="R47" t="n">
-        <v>6911884</v>
+        <v>6911899</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5197,10 +5197,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129759403</v>
+        <v>129759382</v>
       </c>
       <c r="B48" t="n">
-        <v>80222</v>
+        <v>80090</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5208,21 +5208,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6464</v>
+        <v>6456</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5232,10 +5232,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>583755</v>
+        <v>583791</v>
       </c>
       <c r="R48" t="n">
-        <v>6911971</v>
+        <v>6911884</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5294,10 +5294,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129759378</v>
+        <v>129759403</v>
       </c>
       <c r="B49" t="n">
-        <v>80215</v>
+        <v>80222</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5305,21 +5305,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5329,10 +5329,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>583791</v>
+        <v>583755</v>
       </c>
       <c r="R49" t="n">
-        <v>6911883</v>
+        <v>6911971</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5391,10 +5391,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129759405</v>
+        <v>129759378</v>
       </c>
       <c r="B50" t="n">
-        <v>80146</v>
+        <v>80215</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5402,21 +5402,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5426,10 +5426,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>583549</v>
+        <v>583791</v>
       </c>
       <c r="R50" t="n">
-        <v>6911932</v>
+        <v>6911883</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6085,32 +6085,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129759394</v>
+        <v>129759418</v>
       </c>
       <c r="B57" t="n">
-        <v>91897</v>
+        <v>98790</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6120,10 +6120,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>584057</v>
+        <v>583629</v>
       </c>
       <c r="R57" t="n">
-        <v>6911892</v>
+        <v>6911831</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6156,6 +6156,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6182,32 +6187,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129759433</v>
+        <v>129759416</v>
       </c>
       <c r="B58" t="n">
-        <v>79081</v>
+        <v>98790</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6217,10 +6222,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>583652</v>
+        <v>583627</v>
       </c>
       <c r="R58" t="n">
-        <v>6911949</v>
+        <v>6911841</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6253,6 +6258,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6279,32 +6289,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129759376</v>
+        <v>129759433</v>
       </c>
       <c r="B59" t="n">
-        <v>80215</v>
+        <v>79081</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6314,10 +6324,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>583790</v>
+        <v>583652</v>
       </c>
       <c r="R59" t="n">
-        <v>6911899</v>
+        <v>6911949</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6376,10 +6386,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129759383</v>
+        <v>129759376</v>
       </c>
       <c r="B60" t="n">
-        <v>80090</v>
+        <v>80215</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6387,21 +6397,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6411,10 +6421,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>584065</v>
+        <v>583790</v>
       </c>
       <c r="R60" t="n">
-        <v>6911889</v>
+        <v>6911899</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6473,32 +6483,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129759418</v>
+        <v>129759383</v>
       </c>
       <c r="B61" t="n">
-        <v>98790</v>
+        <v>80090</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6508,10 +6518,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>583629</v>
+        <v>584065</v>
       </c>
       <c r="R61" t="n">
-        <v>6911831</v>
+        <v>6911889</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6544,11 +6554,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>35 ex</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6575,32 +6580,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129759416</v>
+        <v>129759394</v>
       </c>
       <c r="B62" t="n">
-        <v>98790</v>
+        <v>91897</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6610,10 +6615,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>583627</v>
+        <v>584057</v>
       </c>
       <c r="R62" t="n">
-        <v>6911841</v>
+        <v>6911892</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6646,11 +6651,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>45 ex</t>
         </is>
       </c>
       <c r="AD62" t="b">

--- a/artfynd/A 48568-2023 artfynd.xlsx
+++ b/artfynd/A 48568-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129759341</v>
       </c>
       <c r="B2" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129759398</v>
       </c>
       <c r="B3" t="n">
-        <v>80214</v>
+        <v>80217</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129759415</v>
       </c>
       <c r="B4" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>129759401</v>
       </c>
       <c r="B5" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>129759399</v>
       </c>
       <c r="B6" t="n">
-        <v>75117</v>
+        <v>75120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>129759381</v>
       </c>
       <c r="B7" t="n">
-        <v>80090</v>
+        <v>80093</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>129759379</v>
       </c>
       <c r="B8" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1364,30 +1364,34 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129759430</v>
+        <v>129759413</v>
       </c>
       <c r="B9" t="n">
-        <v>91619</v>
+        <v>98794</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1395,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584005</v>
+        <v>583755</v>
       </c>
       <c r="R9" t="n">
-        <v>6911803</v>
+        <v>6911734</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1431,6 +1435,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1460,7 +1469,7 @@
         <v>129759436</v>
       </c>
       <c r="B10" t="n">
-        <v>80221</v>
+        <v>80224</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1554,34 +1563,30 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129759413</v>
+        <v>129759430</v>
       </c>
       <c r="B11" t="n">
-        <v>98790</v>
+        <v>91622</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1589,10 +1594,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583755</v>
+        <v>584005</v>
       </c>
       <c r="R11" t="n">
-        <v>6911734</v>
+        <v>6911803</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1625,11 +1630,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>45 ex</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1656,10 +1656,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129759429</v>
+        <v>129759392</v>
       </c>
       <c r="B12" t="n">
-        <v>91613</v>
+        <v>91900</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1667,21 +1667,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583810</v>
+        <v>583799</v>
       </c>
       <c r="R12" t="n">
-        <v>6911860</v>
+        <v>6911903</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129759392</v>
+        <v>129759429</v>
       </c>
       <c r="B13" t="n">
-        <v>91897</v>
+        <v>91616</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1764,21 +1764,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583799</v>
+        <v>583810</v>
       </c>
       <c r="R13" t="n">
-        <v>6911903</v>
+        <v>6911860</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1853,7 +1853,7 @@
         <v>129759397</v>
       </c>
       <c r="B14" t="n">
-        <v>80214</v>
+        <v>80217</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1947,32 +1947,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129759424</v>
+        <v>129759427</v>
       </c>
       <c r="B15" t="n">
-        <v>98790</v>
+        <v>105860</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1982,10 +1982,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583956</v>
+        <v>584003</v>
       </c>
       <c r="R15" t="n">
-        <v>6911817</v>
+        <v>6911804</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2018,11 +2018,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>90 ex runt en tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2049,32 +2044,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129759427</v>
+        <v>129759424</v>
       </c>
       <c r="B16" t="n">
-        <v>105856</v>
+        <v>98794</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2084,10 +2079,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584003</v>
+        <v>583956</v>
       </c>
       <c r="R16" t="n">
-        <v>6911804</v>
+        <v>6911817</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2120,6 +2115,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>90 ex runt en tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2149,7 +2149,7 @@
         <v>129759434</v>
       </c>
       <c r="B17" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2243,32 +2243,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129759432</v>
+        <v>129759425</v>
       </c>
       <c r="B18" t="n">
-        <v>79081</v>
+        <v>98794</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583940</v>
+        <v>583999</v>
       </c>
       <c r="R18" t="n">
-        <v>6911767</v>
+        <v>6911781</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2314,6 +2314,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2340,10 +2345,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129759425</v>
+        <v>129759423</v>
       </c>
       <c r="B19" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2375,10 +2380,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583999</v>
+        <v>583836</v>
       </c>
       <c r="R19" t="n">
-        <v>6911781</v>
+        <v>6911810</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2415,7 +2420,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>15 ex</t>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2442,32 +2447,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129759423</v>
+        <v>129759432</v>
       </c>
       <c r="B20" t="n">
-        <v>98790</v>
+        <v>79084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2477,10 +2482,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583836</v>
+        <v>583940</v>
       </c>
       <c r="R20" t="n">
-        <v>6911810</v>
+        <v>6911767</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2513,11 +2518,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>10 ex</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2547,7 +2547,7 @@
         <v>129759437</v>
       </c>
       <c r="B21" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2641,10 +2641,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129759339</v>
+        <v>129759380</v>
       </c>
       <c r="B22" t="n">
-        <v>91599</v>
+        <v>57734</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2652,21 +2652,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584025</v>
+        <v>583963</v>
       </c>
       <c r="R22" t="n">
-        <v>6911724</v>
+        <v>6911801</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2712,6 +2712,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska hackspår i liggande gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2738,45 +2743,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129759384</v>
+        <v>129759404</v>
       </c>
       <c r="B23" t="n">
-        <v>92052</v>
+        <v>92021</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1209</v>
+        <v>6040186</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stor-Oxögeberget, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584021</v>
+        <v>583819</v>
       </c>
       <c r="R23" t="n">
-        <v>6911731</v>
+        <v>6911717</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2817,6 +2825,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2835,32 +2844,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129759380</v>
+        <v>129759406</v>
       </c>
       <c r="B24" t="n">
-        <v>57733</v>
+        <v>80149</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>229497</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2870,10 +2879,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583963</v>
+        <v>583688</v>
       </c>
       <c r="R24" t="n">
-        <v>6911801</v>
+        <v>6911990</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2906,11 +2915,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska hackspår i liggande gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2937,10 +2941,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129759404</v>
+        <v>129759339</v>
       </c>
       <c r="B25" t="n">
-        <v>92018</v>
+        <v>91602</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2948,32 +2952,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stor-Oxögeberget, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583819</v>
+        <v>584025</v>
       </c>
       <c r="R25" t="n">
-        <v>6911717</v>
+        <v>6911724</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3014,7 +3020,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3033,32 +3038,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129759406</v>
+        <v>129759384</v>
       </c>
       <c r="B26" t="n">
-        <v>80146</v>
+        <v>92055</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229497</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3068,10 +3073,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583688</v>
+        <v>584021</v>
       </c>
       <c r="R26" t="n">
-        <v>6911990</v>
+        <v>6911731</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3133,7 +3138,7 @@
         <v>129759375</v>
       </c>
       <c r="B27" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3235,7 +3240,7 @@
         <v>129759411</v>
       </c>
       <c r="B28" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3334,10 +3339,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129759385</v>
+        <v>129759422</v>
       </c>
       <c r="B29" t="n">
-        <v>92052</v>
+        <v>98794</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3345,21 +3350,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3369,10 +3374,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>583791</v>
+        <v>583932</v>
       </c>
       <c r="R29" t="n">
-        <v>6911899</v>
+        <v>6911706</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3405,6 +3410,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>6 ex</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3431,32 +3441,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129759422</v>
+        <v>129759388</v>
       </c>
       <c r="B30" t="n">
-        <v>98790</v>
+        <v>91900</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3466,10 +3476,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>583932</v>
+        <v>584025</v>
       </c>
       <c r="R30" t="n">
-        <v>6911706</v>
+        <v>6911728</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3502,11 +3512,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>6 ex</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3533,32 +3538,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129759410</v>
+        <v>129759385</v>
       </c>
       <c r="B31" t="n">
-        <v>80146</v>
+        <v>92055</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229497</v>
+        <v>1209</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3568,10 +3573,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>583794</v>
+        <v>583791</v>
       </c>
       <c r="R31" t="n">
-        <v>6911885</v>
+        <v>6911899</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3630,32 +3635,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129759388</v>
+        <v>129759410</v>
       </c>
       <c r="B32" t="n">
-        <v>91897</v>
+        <v>80149</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>229497</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3665,10 +3670,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584025</v>
+        <v>583794</v>
       </c>
       <c r="R32" t="n">
-        <v>6911728</v>
+        <v>6911885</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3730,7 +3735,7 @@
         <v>129759343</v>
       </c>
       <c r="B33" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3827,7 +3832,7 @@
         <v>129759393</v>
       </c>
       <c r="B34" t="n">
-        <v>91897</v>
+        <v>91900</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3924,7 +3929,7 @@
         <v>129759409</v>
       </c>
       <c r="B35" t="n">
-        <v>80146</v>
+        <v>80149</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4021,7 +4026,7 @@
         <v>129759407</v>
       </c>
       <c r="B36" t="n">
-        <v>80146</v>
+        <v>80149</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4115,32 +4120,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129759421</v>
+        <v>129759389</v>
       </c>
       <c r="B37" t="n">
-        <v>98790</v>
+        <v>91900</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4150,10 +4155,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>583940</v>
+        <v>583704</v>
       </c>
       <c r="R37" t="n">
-        <v>6911780</v>
+        <v>6911854</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4186,11 +4191,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>7 ex</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4217,10 +4217,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129759414</v>
+        <v>129759421</v>
       </c>
       <c r="B38" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4252,10 +4252,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>583765</v>
+        <v>583940</v>
       </c>
       <c r="R38" t="n">
-        <v>6911752</v>
+        <v>6911780</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4292,7 +4292,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>15 ex</t>
+          <t>7 ex</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4319,32 +4319,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129759389</v>
+        <v>129759414</v>
       </c>
       <c r="B39" t="n">
-        <v>91897</v>
+        <v>98794</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4354,10 +4354,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>583704</v>
+        <v>583765</v>
       </c>
       <c r="R39" t="n">
-        <v>6911854</v>
+        <v>6911752</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4390,6 +4390,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4419,7 +4424,7 @@
         <v>129759395</v>
       </c>
       <c r="B40" t="n">
-        <v>91897</v>
+        <v>91900</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4513,32 +4518,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129759396</v>
+        <v>129759428</v>
       </c>
       <c r="B41" t="n">
-        <v>97661</v>
+        <v>91616</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>1204</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4548,10 +4553,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>583804</v>
+        <v>583782</v>
       </c>
       <c r="R41" t="n">
-        <v>6911895</v>
+        <v>6911933</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4610,10 +4615,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129759428</v>
+        <v>129759345</v>
       </c>
       <c r="B42" t="n">
-        <v>91613</v>
+        <v>91602</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4621,21 +4626,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4645,10 +4650,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>583782</v>
+        <v>584070</v>
       </c>
       <c r="R42" t="n">
-        <v>6911933</v>
+        <v>6911921</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4707,10 +4712,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129759345</v>
+        <v>129759400</v>
       </c>
       <c r="B43" t="n">
-        <v>91599</v>
+        <v>80189</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4718,21 +4723,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4742,10 +4747,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584070</v>
+        <v>583551</v>
       </c>
       <c r="R43" t="n">
-        <v>6911921</v>
+        <v>6911946</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4778,6 +4783,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4807,7 +4817,7 @@
         <v>129759435</v>
       </c>
       <c r="B44" t="n">
-        <v>80221</v>
+        <v>80224</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4901,32 +4911,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129759400</v>
+        <v>129759396</v>
       </c>
       <c r="B45" t="n">
-        <v>80186</v>
+        <v>97665</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4936,10 +4946,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>583551</v>
+        <v>583804</v>
       </c>
       <c r="R45" t="n">
-        <v>6911946</v>
+        <v>6911895</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4972,11 +4982,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5003,10 +5008,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129759405</v>
+        <v>129759378</v>
       </c>
       <c r="B46" t="n">
-        <v>80146</v>
+        <v>80218</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5014,21 +5019,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5038,10 +5043,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>583549</v>
+        <v>583791</v>
       </c>
       <c r="R46" t="n">
-        <v>6911932</v>
+        <v>6911883</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5103,7 +5108,7 @@
         <v>129759402</v>
       </c>
       <c r="B47" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5200,7 +5205,7 @@
         <v>129759382</v>
       </c>
       <c r="B48" t="n">
-        <v>80090</v>
+        <v>80093</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5297,7 +5302,7 @@
         <v>129759403</v>
       </c>
       <c r="B49" t="n">
-        <v>80222</v>
+        <v>80225</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5391,10 +5396,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129759378</v>
+        <v>129759405</v>
       </c>
       <c r="B50" t="n">
-        <v>80215</v>
+        <v>80149</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5402,21 +5407,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6462</v>
+        <v>229497</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5426,10 +5431,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>583791</v>
+        <v>583549</v>
       </c>
       <c r="R50" t="n">
-        <v>6911883</v>
+        <v>6911932</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5488,10 +5493,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129759419</v>
+        <v>129759420</v>
       </c>
       <c r="B51" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5523,10 +5528,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>583745</v>
+        <v>583927</v>
       </c>
       <c r="R51" t="n">
-        <v>6911935</v>
+        <v>6911779</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5563,7 +5568,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>100 ex</t>
+          <t>22 ex</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5590,10 +5595,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129759412</v>
+        <v>129759419</v>
       </c>
       <c r="B52" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5625,10 +5630,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>583781</v>
+        <v>583745</v>
       </c>
       <c r="R52" t="n">
-        <v>6911695</v>
+        <v>6911935</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5665,7 +5670,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>70 ex</t>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5692,10 +5697,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129759420</v>
+        <v>129759412</v>
       </c>
       <c r="B53" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5727,10 +5732,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>583927</v>
+        <v>583781</v>
       </c>
       <c r="R53" t="n">
-        <v>6911779</v>
+        <v>6911695</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5767,7 +5772,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>22 ex</t>
+          <t>70 ex</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5797,7 +5802,7 @@
         <v>129759391</v>
       </c>
       <c r="B54" t="n">
-        <v>91897</v>
+        <v>91900</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5891,32 +5896,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129759431</v>
+        <v>129759377</v>
       </c>
       <c r="B55" t="n">
-        <v>79081</v>
+        <v>80218</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5926,10 +5931,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>583549</v>
+        <v>583809</v>
       </c>
       <c r="R55" t="n">
-        <v>6911806</v>
+        <v>6911875</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5988,32 +5993,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129759377</v>
+        <v>129759431</v>
       </c>
       <c r="B56" t="n">
-        <v>80215</v>
+        <v>79084</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6023,10 +6028,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>583809</v>
+        <v>583549</v>
       </c>
       <c r="R56" t="n">
-        <v>6911875</v>
+        <v>6911806</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6085,32 +6090,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129759418</v>
+        <v>129759433</v>
       </c>
       <c r="B57" t="n">
-        <v>98790</v>
+        <v>79084</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6120,10 +6125,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>583629</v>
+        <v>583652</v>
       </c>
       <c r="R57" t="n">
-        <v>6911831</v>
+        <v>6911949</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6156,11 +6161,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>35 ex</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6187,32 +6187,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129759416</v>
+        <v>129759394</v>
       </c>
       <c r="B58" t="n">
-        <v>98790</v>
+        <v>91900</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6222,10 +6222,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>583627</v>
+        <v>584057</v>
       </c>
       <c r="R58" t="n">
-        <v>6911841</v>
+        <v>6911892</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6258,11 +6258,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>45 ex</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6289,32 +6284,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129759433</v>
+        <v>129759383</v>
       </c>
       <c r="B59" t="n">
-        <v>79081</v>
+        <v>80093</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6324,10 +6319,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>583652</v>
+        <v>584065</v>
       </c>
       <c r="R59" t="n">
-        <v>6911949</v>
+        <v>6911889</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6389,7 +6384,7 @@
         <v>129759376</v>
       </c>
       <c r="B60" t="n">
-        <v>80215</v>
+        <v>80218</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6483,32 +6478,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129759383</v>
+        <v>129759418</v>
       </c>
       <c r="B61" t="n">
-        <v>80090</v>
+        <v>98794</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6518,10 +6513,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>584065</v>
+        <v>583629</v>
       </c>
       <c r="R61" t="n">
-        <v>6911889</v>
+        <v>6911831</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6554,6 +6549,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6580,32 +6580,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129759394</v>
+        <v>129759416</v>
       </c>
       <c r="B62" t="n">
-        <v>91897</v>
+        <v>98794</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>584057</v>
+        <v>583627</v>
       </c>
       <c r="R62" t="n">
-        <v>6911892</v>
+        <v>6911841</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6651,6 +6651,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6680,7 +6685,7 @@
         <v>129759387</v>
       </c>
       <c r="B63" t="n">
-        <v>91897</v>
+        <v>91900</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6777,7 +6782,7 @@
         <v>129759350</v>
       </c>
       <c r="B64" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6879,7 +6884,7 @@
         <v>129759361</v>
       </c>
       <c r="B65" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6981,7 +6986,7 @@
         <v>129759359</v>
       </c>
       <c r="B66" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7083,7 +7088,7 @@
         <v>129759352</v>
       </c>
       <c r="B67" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7185,7 +7190,7 @@
         <v>129759354</v>
       </c>
       <c r="B68" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7287,7 +7292,7 @@
         <v>129759348</v>
       </c>
       <c r="B69" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7389,7 +7394,7 @@
         <v>129759363</v>
       </c>
       <c r="B70" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7491,7 +7496,7 @@
         <v>129759370</v>
       </c>
       <c r="B71" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7593,7 +7598,7 @@
         <v>129759357</v>
       </c>
       <c r="B72" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7695,7 +7700,7 @@
         <v>129759372</v>
       </c>
       <c r="B73" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7797,7 +7802,7 @@
         <v>129759367</v>
       </c>
       <c r="B74" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7899,7 +7904,7 @@
         <v>129759366</v>
       </c>
       <c r="B75" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8001,7 +8006,7 @@
         <v>129759364</v>
       </c>
       <c r="B76" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8103,7 +8108,7 @@
         <v>129759358</v>
       </c>
       <c r="B77" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8205,7 +8210,7 @@
         <v>129759355</v>
       </c>
       <c r="B78" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8307,7 +8312,7 @@
         <v>129759353</v>
       </c>
       <c r="B79" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8409,7 +8414,7 @@
         <v>129759362</v>
       </c>
       <c r="B80" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8511,7 +8516,7 @@
         <v>129759349</v>
       </c>
       <c r="B81" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8613,7 +8618,7 @@
         <v>129759365</v>
       </c>
       <c r="B82" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8715,7 +8720,7 @@
         <v>129759360</v>
       </c>
       <c r="B83" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8817,7 +8822,7 @@
         <v>129759351</v>
       </c>
       <c r="B84" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8919,7 +8924,7 @@
         <v>129759369</v>
       </c>
       <c r="B85" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9021,7 +9026,7 @@
         <v>129759356</v>
       </c>
       <c r="B86" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 48568-2023 artfynd.xlsx
+++ b/artfynd/A 48568-2023 artfynd.xlsx
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129759401</v>
+        <v>129759399</v>
       </c>
       <c r="B5" t="n">
-        <v>80189</v>
+        <v>75120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>229651</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lunglavsknapp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Plectocarpon lichenum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583559</v>
+        <v>583550</v>
       </c>
       <c r="R5" t="n">
-        <v>6911967</v>
+        <v>6911932</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129759399</v>
+        <v>129759401</v>
       </c>
       <c r="B6" t="n">
-        <v>75120</v>
+        <v>80189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229651</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglavsknapp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Plectocarpon lichenum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Sommerf.) D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583550</v>
+        <v>583559</v>
       </c>
       <c r="R6" t="n">
-        <v>6911932</v>
+        <v>6911967</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1364,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129759413</v>
+        <v>129759436</v>
       </c>
       <c r="B9" t="n">
-        <v>98794</v>
+        <v>80224</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583755</v>
+        <v>583792</v>
       </c>
       <c r="R9" t="n">
-        <v>6911734</v>
+        <v>6911886</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1435,11 +1435,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>45 ex</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1466,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129759436</v>
+        <v>129759413</v>
       </c>
       <c r="B10" t="n">
-        <v>80224</v>
+        <v>98794</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1501,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583792</v>
+        <v>583755</v>
       </c>
       <c r="R10" t="n">
-        <v>6911886</v>
+        <v>6911734</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1537,6 +1532,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,10 +1656,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129759392</v>
+        <v>129759429</v>
       </c>
       <c r="B12" t="n">
-        <v>91900</v>
+        <v>91616</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1667,21 +1667,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583799</v>
+        <v>583810</v>
       </c>
       <c r="R12" t="n">
-        <v>6911903</v>
+        <v>6911860</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129759429</v>
+        <v>129759392</v>
       </c>
       <c r="B13" t="n">
-        <v>91616</v>
+        <v>91900</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1764,21 +1764,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583810</v>
+        <v>583799</v>
       </c>
       <c r="R13" t="n">
-        <v>6911860</v>
+        <v>6911903</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,32 +1947,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129759427</v>
+        <v>129759434</v>
       </c>
       <c r="B15" t="n">
-        <v>105860</v>
+        <v>79084</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1982,10 +1982,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584003</v>
+        <v>583999</v>
       </c>
       <c r="R15" t="n">
-        <v>6911804</v>
+        <v>6911809</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,32 +2146,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129759434</v>
+        <v>129759427</v>
       </c>
       <c r="B17" t="n">
-        <v>79084</v>
+        <v>105860</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583999</v>
+        <v>584003</v>
       </c>
       <c r="R17" t="n">
-        <v>6911809</v>
+        <v>6911804</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2243,32 +2243,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129759425</v>
+        <v>129759437</v>
       </c>
       <c r="B18" t="n">
-        <v>98794</v>
+        <v>100983</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583999</v>
+        <v>583826</v>
       </c>
       <c r="R18" t="n">
-        <v>6911781</v>
+        <v>6911855</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2314,11 +2314,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>15 ex</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2345,32 +2340,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129759423</v>
+        <v>129759432</v>
       </c>
       <c r="B19" t="n">
-        <v>98794</v>
+        <v>79084</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2380,10 +2375,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583836</v>
+        <v>583940</v>
       </c>
       <c r="R19" t="n">
-        <v>6911810</v>
+        <v>6911767</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2416,11 +2411,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>10 ex</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2447,32 +2437,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129759432</v>
+        <v>129759425</v>
       </c>
       <c r="B20" t="n">
-        <v>79084</v>
+        <v>98794</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2482,10 +2472,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583940</v>
+        <v>583999</v>
       </c>
       <c r="R20" t="n">
-        <v>6911767</v>
+        <v>6911781</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2518,6 +2508,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2544,32 +2539,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129759437</v>
+        <v>129759423</v>
       </c>
       <c r="B21" t="n">
-        <v>100983</v>
+        <v>98794</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2579,10 +2574,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583826</v>
+        <v>583836</v>
       </c>
       <c r="R21" t="n">
-        <v>6911855</v>
+        <v>6911810</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2615,6 +2610,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2743,10 +2743,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129759404</v>
+        <v>129759339</v>
       </c>
       <c r="B23" t="n">
-        <v>92021</v>
+        <v>91602</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2754,37 +2754,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6040186</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stor-Oxögeberget, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583819</v>
+        <v>584025</v>
       </c>
       <c r="R23" t="n">
-        <v>6911717</v>
+        <v>6911724</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2825,7 +2822,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2844,32 +2840,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129759406</v>
+        <v>129759384</v>
       </c>
       <c r="B24" t="n">
-        <v>80149</v>
+        <v>92055</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229497</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2879,10 +2875,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583688</v>
+        <v>584021</v>
       </c>
       <c r="R24" t="n">
-        <v>6911990</v>
+        <v>6911731</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2941,32 +2937,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129759339</v>
+        <v>129759406</v>
       </c>
       <c r="B25" t="n">
-        <v>91602</v>
+        <v>80149</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2976,10 +2972,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584025</v>
+        <v>583688</v>
       </c>
       <c r="R25" t="n">
-        <v>6911724</v>
+        <v>6911990</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3038,45 +3034,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129759384</v>
+        <v>129759404</v>
       </c>
       <c r="B26" t="n">
-        <v>92055</v>
+        <v>92021</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>6040186</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stor-Oxögeberget, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584021</v>
+        <v>583819</v>
       </c>
       <c r="R26" t="n">
-        <v>6911731</v>
+        <v>6911717</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3117,6 +3116,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3339,32 +3339,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129759422</v>
+        <v>129759388</v>
       </c>
       <c r="B29" t="n">
-        <v>98794</v>
+        <v>91900</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3374,10 +3374,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>583932</v>
+        <v>584025</v>
       </c>
       <c r="R29" t="n">
-        <v>6911706</v>
+        <v>6911728</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3410,11 +3410,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>6 ex</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3441,32 +3436,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129759388</v>
+        <v>129759385</v>
       </c>
       <c r="B30" t="n">
-        <v>91900</v>
+        <v>92055</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3476,10 +3471,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584025</v>
+        <v>583791</v>
       </c>
       <c r="R30" t="n">
-        <v>6911728</v>
+        <v>6911899</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3538,10 +3533,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129759385</v>
+        <v>129759422</v>
       </c>
       <c r="B31" t="n">
-        <v>92055</v>
+        <v>98794</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3549,21 +3544,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3573,10 +3568,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>583791</v>
+        <v>583932</v>
       </c>
       <c r="R31" t="n">
-        <v>6911899</v>
+        <v>6911706</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3609,6 +3604,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>6 ex</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4712,32 +4712,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129759400</v>
+        <v>129759435</v>
       </c>
       <c r="B43" t="n">
-        <v>80189</v>
+        <v>80224</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4747,10 +4747,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>583551</v>
+        <v>583790</v>
       </c>
       <c r="R43" t="n">
-        <v>6911946</v>
+        <v>6911897</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4783,11 +4783,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4814,32 +4809,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129759435</v>
+        <v>129759400</v>
       </c>
       <c r="B44" t="n">
-        <v>80224</v>
+        <v>80189</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4849,10 +4844,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>583790</v>
+        <v>583551</v>
       </c>
       <c r="R44" t="n">
-        <v>6911897</v>
+        <v>6911946</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4885,6 +4880,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5008,10 +5008,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129759378</v>
+        <v>129759405</v>
       </c>
       <c r="B46" t="n">
-        <v>80218</v>
+        <v>80149</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5019,21 +5019,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>229497</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5043,10 +5043,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>583791</v>
+        <v>583549</v>
       </c>
       <c r="R46" t="n">
-        <v>6911883</v>
+        <v>6911932</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5396,10 +5396,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129759405</v>
+        <v>129759378</v>
       </c>
       <c r="B50" t="n">
-        <v>80149</v>
+        <v>80218</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5407,21 +5407,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5431,10 +5431,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>583549</v>
+        <v>583791</v>
       </c>
       <c r="R50" t="n">
-        <v>6911932</v>
+        <v>6911883</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5493,7 +5493,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129759420</v>
+        <v>129759419</v>
       </c>
       <c r="B51" t="n">
         <v>98794</v>
@@ -5528,10 +5528,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>583927</v>
+        <v>583745</v>
       </c>
       <c r="R51" t="n">
-        <v>6911779</v>
+        <v>6911935</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>22 ex</t>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5595,7 +5595,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129759419</v>
+        <v>129759412</v>
       </c>
       <c r="B52" t="n">
         <v>98794</v>
@@ -5630,10 +5630,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>583745</v>
+        <v>583781</v>
       </c>
       <c r="R52" t="n">
-        <v>6911935</v>
+        <v>6911695</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5670,7 +5670,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>100 ex</t>
+          <t>70 ex</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5697,7 +5697,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129759412</v>
+        <v>129759420</v>
       </c>
       <c r="B53" t="n">
         <v>98794</v>
@@ -5732,10 +5732,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>583781</v>
+        <v>583927</v>
       </c>
       <c r="R53" t="n">
-        <v>6911695</v>
+        <v>6911779</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5772,7 +5772,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>70 ex</t>
+          <t>22 ex</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5799,10 +5799,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129759391</v>
+        <v>129759431</v>
       </c>
       <c r="B54" t="n">
-        <v>91900</v>
+        <v>79084</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5810,21 +5810,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>583565</v>
+        <v>583549</v>
       </c>
       <c r="R54" t="n">
-        <v>6911984</v>
+        <v>6911806</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5993,10 +5993,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129759431</v>
+        <v>129759391</v>
       </c>
       <c r="B56" t="n">
-        <v>79084</v>
+        <v>91900</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6004,21 +6004,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>583549</v>
+        <v>583565</v>
       </c>
       <c r="R56" t="n">
-        <v>6911806</v>
+        <v>6911984</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6090,32 +6090,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129759433</v>
+        <v>129759418</v>
       </c>
       <c r="B57" t="n">
-        <v>79084</v>
+        <v>98794</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6125,10 +6125,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>583652</v>
+        <v>583629</v>
       </c>
       <c r="R57" t="n">
-        <v>6911949</v>
+        <v>6911831</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6161,6 +6161,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6187,10 +6192,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129759394</v>
+        <v>129759433</v>
       </c>
       <c r="B58" t="n">
-        <v>91900</v>
+        <v>79084</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6198,21 +6203,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6222,10 +6227,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>584057</v>
+        <v>583652</v>
       </c>
       <c r="R58" t="n">
-        <v>6911892</v>
+        <v>6911949</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6284,32 +6289,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129759383</v>
+        <v>129759394</v>
       </c>
       <c r="B59" t="n">
-        <v>80093</v>
+        <v>91900</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6319,10 +6324,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>584065</v>
+        <v>584057</v>
       </c>
       <c r="R59" t="n">
-        <v>6911889</v>
+        <v>6911892</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6478,32 +6483,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129759418</v>
+        <v>129759383</v>
       </c>
       <c r="B61" t="n">
-        <v>98794</v>
+        <v>80093</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6513,10 +6518,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>583629</v>
+        <v>584065</v>
       </c>
       <c r="R61" t="n">
-        <v>6911831</v>
+        <v>6911889</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6549,11 +6554,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>35 ex</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7493,7 +7493,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129759370</v>
+        <v>129759357</v>
       </c>
       <c r="B71" t="n">
         <v>57737</v>
@@ -7528,10 +7528,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>584063</v>
+        <v>583586</v>
       </c>
       <c r="R71" t="n">
-        <v>6911870</v>
+        <v>6911868</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7568,7 +7568,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7595,7 +7595,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129759357</v>
+        <v>129759370</v>
       </c>
       <c r="B72" t="n">
         <v>57737</v>
@@ -7630,10 +7630,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>583586</v>
+        <v>584063</v>
       </c>
       <c r="R72" t="n">
-        <v>6911868</v>
+        <v>6911870</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8003,7 +8003,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129759364</v>
+        <v>129759358</v>
       </c>
       <c r="B76" t="n">
         <v>57737</v>
@@ -8038,10 +8038,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>583922</v>
+        <v>583672</v>
       </c>
       <c r="R76" t="n">
-        <v>6911801</v>
+        <v>6911978</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8105,7 +8105,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129759358</v>
+        <v>129759364</v>
       </c>
       <c r="B77" t="n">
         <v>57737</v>
@@ -8140,10 +8140,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>583672</v>
+        <v>583922</v>
       </c>
       <c r="R77" t="n">
-        <v>6911978</v>
+        <v>6911801</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>

--- a/artfynd/A 48568-2023 artfynd.xlsx
+++ b/artfynd/A 48568-2023 artfynd.xlsx
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129759381</v>
+        <v>129759379</v>
       </c>
       <c r="B7" t="n">
-        <v>80093</v>
+        <v>57734</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583783</v>
+        <v>583930</v>
       </c>
       <c r="R7" t="n">
-        <v>6911895</v>
+        <v>6911711</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,6 +1236,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>1 ex, födosökande</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1262,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129759379</v>
+        <v>129759381</v>
       </c>
       <c r="B8" t="n">
-        <v>57734</v>
+        <v>80093</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583930</v>
+        <v>583783</v>
       </c>
       <c r="R8" t="n">
-        <v>6911711</v>
+        <v>6911895</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1333,11 +1338,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>1 ex, födosökande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1364,34 +1364,30 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129759436</v>
+        <v>129759430</v>
       </c>
       <c r="B9" t="n">
-        <v>80224</v>
+        <v>91622</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1399,10 +1395,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583792</v>
+        <v>584005</v>
       </c>
       <c r="R9" t="n">
-        <v>6911886</v>
+        <v>6911803</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,32 +1457,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129759413</v>
+        <v>129759436</v>
       </c>
       <c r="B10" t="n">
-        <v>98794</v>
+        <v>80224</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1492,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583755</v>
+        <v>583792</v>
       </c>
       <c r="R10" t="n">
-        <v>6911734</v>
+        <v>6911886</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1532,11 +1528,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>45 ex</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1563,30 +1554,34 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129759430</v>
+        <v>129759413</v>
       </c>
       <c r="B11" t="n">
-        <v>91622</v>
+        <v>98794</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1594,10 +1589,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584005</v>
+        <v>583755</v>
       </c>
       <c r="R11" t="n">
-        <v>6911803</v>
+        <v>6911734</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1630,6 +1625,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -4421,10 +4421,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129759395</v>
+        <v>129759428</v>
       </c>
       <c r="B40" t="n">
-        <v>91900</v>
+        <v>91616</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4432,21 +4432,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4456,10 +4456,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584070</v>
+        <v>583782</v>
       </c>
       <c r="R40" t="n">
-        <v>6911923</v>
+        <v>6911933</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4518,32 +4518,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129759428</v>
+        <v>129759396</v>
       </c>
       <c r="B41" t="n">
-        <v>91616</v>
+        <v>97665</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1204</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4553,10 +4553,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>583782</v>
+        <v>583804</v>
       </c>
       <c r="R41" t="n">
-        <v>6911933</v>
+        <v>6911895</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4615,10 +4615,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129759345</v>
+        <v>129759395</v>
       </c>
       <c r="B42" t="n">
-        <v>91602</v>
+        <v>91900</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4626,21 +4626,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4653,7 +4653,7 @@
         <v>584070</v>
       </c>
       <c r="R42" t="n">
-        <v>6911921</v>
+        <v>6911923</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4712,32 +4712,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129759435</v>
+        <v>129759345</v>
       </c>
       <c r="B43" t="n">
-        <v>80224</v>
+        <v>91602</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4747,10 +4747,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>583790</v>
+        <v>584070</v>
       </c>
       <c r="R43" t="n">
-        <v>6911897</v>
+        <v>6911921</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4809,32 +4809,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129759400</v>
+        <v>129759435</v>
       </c>
       <c r="B44" t="n">
-        <v>80189</v>
+        <v>80224</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4844,10 +4844,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>583551</v>
+        <v>583790</v>
       </c>
       <c r="R44" t="n">
-        <v>6911946</v>
+        <v>6911897</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4880,11 +4880,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4911,32 +4906,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129759396</v>
+        <v>129759400</v>
       </c>
       <c r="B45" t="n">
-        <v>97665</v>
+        <v>80189</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4946,10 +4941,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>583804</v>
+        <v>583551</v>
       </c>
       <c r="R45" t="n">
-        <v>6911895</v>
+        <v>6911946</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4982,6 +4977,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 48568-2023 artfynd.xlsx
+++ b/artfynd/A 48568-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY86"/>
+  <dimension ref="A1:AY87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129759341</v>
+        <v>129759386</v>
       </c>
       <c r="B2" t="n">
-        <v>91639</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583643</v>
+        <v>584061</v>
       </c>
       <c r="R2" t="n">
-        <v>6911972</v>
+        <v>6911791</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129759415</v>
+        <v>129759387</v>
       </c>
       <c r="B3" t="n">
-        <v>98831</v>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583723</v>
+        <v>584029</v>
       </c>
       <c r="R3" t="n">
-        <v>6911832</v>
+        <v>6911718</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129759398</v>
+        <v>129759388</v>
       </c>
       <c r="B4" t="n">
-        <v>80228</v>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6461</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583824</v>
+        <v>584025</v>
       </c>
       <c r="R4" t="n">
-        <v>6911829</v>
+        <v>6911728</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129759399</v>
+        <v>129759389</v>
       </c>
       <c r="B5" t="n">
-        <v>75125</v>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229651</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglavsknapp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Plectocarpon lichenum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Sommerf.) D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583550</v>
+        <v>583704</v>
       </c>
       <c r="R5" t="n">
-        <v>6911932</v>
+        <v>6911854</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129759401</v>
+        <v>129759391</v>
       </c>
       <c r="B6" t="n">
-        <v>80200</v>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583559</v>
+        <v>583565</v>
       </c>
       <c r="R6" t="n">
-        <v>6911967</v>
+        <v>6911984</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129759381</v>
+        <v>129759392</v>
       </c>
       <c r="B7" t="n">
-        <v>80104</v>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583783</v>
+        <v>583799</v>
       </c>
       <c r="R7" t="n">
-        <v>6911895</v>
+        <v>6911903</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129759379</v>
+        <v>129759393</v>
       </c>
       <c r="B8" t="n">
-        <v>57738</v>
+        <v>92208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583930</v>
+        <v>583944</v>
       </c>
       <c r="R8" t="n">
-        <v>6911711</v>
+        <v>6911825</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1333,11 +1328,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>1 ex, födosökande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1364,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129759436</v>
+        <v>129759394</v>
       </c>
       <c r="B9" t="n">
-        <v>80235</v>
+        <v>92208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583792</v>
+        <v>584057</v>
       </c>
       <c r="R9" t="n">
-        <v>6911886</v>
+        <v>6911892</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129759430</v>
+        <v>129759395</v>
       </c>
       <c r="B10" t="n">
-        <v>91659</v>
+        <v>92208</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,19 +1462,23 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1492,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584005</v>
+        <v>584070</v>
       </c>
       <c r="R10" t="n">
-        <v>6911803</v>
+        <v>6911923</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1554,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129759413</v>
+        <v>129759339</v>
       </c>
       <c r="B11" t="n">
-        <v>98831</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1589,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583755</v>
+        <v>584025</v>
       </c>
       <c r="R11" t="n">
-        <v>6911734</v>
+        <v>6911724</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1625,11 +1619,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>45 ex</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1656,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129759397</v>
+        <v>129759341</v>
       </c>
       <c r="B12" t="n">
-        <v>80228</v>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1691,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583679</v>
+        <v>583643</v>
       </c>
       <c r="R12" t="n">
-        <v>6911975</v>
+        <v>6911972</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1753,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129759429</v>
+        <v>129759343</v>
       </c>
       <c r="B13" t="n">
-        <v>91653</v>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1764,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1788,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583810</v>
+        <v>583805</v>
       </c>
       <c r="R13" t="n">
-        <v>6911860</v>
+        <v>6911905</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1850,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129759392</v>
+        <v>129759345</v>
       </c>
       <c r="B14" t="n">
-        <v>91937</v>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1861,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1885,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>583799</v>
+        <v>584070</v>
       </c>
       <c r="R14" t="n">
-        <v>6911903</v>
+        <v>6911921</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1947,32 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129759434</v>
+        <v>129759428</v>
       </c>
       <c r="B15" t="n">
-        <v>79095</v>
+        <v>91923</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1982,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583999</v>
+        <v>583782</v>
       </c>
       <c r="R15" t="n">
-        <v>6911809</v>
+        <v>6911933</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2044,32 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129759427</v>
+        <v>129759429</v>
       </c>
       <c r="B16" t="n">
-        <v>105897</v>
+        <v>91923</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2079,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584003</v>
+        <v>583810</v>
       </c>
       <c r="R16" t="n">
-        <v>6911804</v>
+        <v>6911860</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2141,32 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129759424</v>
+        <v>129759384</v>
       </c>
       <c r="B17" t="n">
-        <v>98831</v>
+        <v>92369</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2176,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583956</v>
+        <v>584021</v>
       </c>
       <c r="R17" t="n">
-        <v>6911817</v>
+        <v>6911731</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2212,11 +2201,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>90 ex runt en tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2243,32 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129759425</v>
+        <v>129759385</v>
       </c>
       <c r="B18" t="n">
-        <v>98831</v>
+        <v>92369</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2278,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583999</v>
+        <v>583791</v>
       </c>
       <c r="R18" t="n">
-        <v>6911781</v>
+        <v>6911899</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2314,11 +2298,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>15 ex</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2345,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129759423</v>
+        <v>129759431</v>
       </c>
       <c r="B19" t="n">
-        <v>98831</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2356,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2380,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583836</v>
+        <v>583549</v>
       </c>
       <c r="R19" t="n">
-        <v>6911810</v>
+        <v>6911806</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2416,11 +2395,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>10 ex</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2447,32 +2421,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129759437</v>
+        <v>129759432</v>
       </c>
       <c r="B20" t="n">
-        <v>101020</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2482,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583826</v>
+        <v>583940</v>
       </c>
       <c r="R20" t="n">
-        <v>6911855</v>
+        <v>6911767</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2544,14 +2518,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129759432</v>
+        <v>129759433</v>
       </c>
       <c r="B21" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2579,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583940</v>
+        <v>583652</v>
       </c>
       <c r="R21" t="n">
-        <v>6911767</v>
+        <v>6911949</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2641,32 +2615,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129759406</v>
+        <v>129759434</v>
       </c>
       <c r="B22" t="n">
-        <v>80160</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2676,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>583688</v>
+        <v>583999</v>
       </c>
       <c r="R22" t="n">
-        <v>6911990</v>
+        <v>6911809</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2738,48 +2712,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129759404</v>
+        <v>129759381</v>
       </c>
       <c r="B23" t="n">
-        <v>92058</v>
+        <v>80336</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6040186</v>
+        <v>6456</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stor-Oxögeberget, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583819</v>
+        <v>583783</v>
       </c>
       <c r="R23" t="n">
-        <v>6911717</v>
+        <v>6911895</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2820,7 +2791,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2839,32 +2809,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129759339</v>
+        <v>129759382</v>
       </c>
       <c r="B24" t="n">
-        <v>91639</v>
+        <v>80336</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2874,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584025</v>
+        <v>583791</v>
       </c>
       <c r="R24" t="n">
-        <v>6911724</v>
+        <v>6911884</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2936,32 +2906,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129759384</v>
+        <v>129759383</v>
       </c>
       <c r="B25" t="n">
-        <v>92092</v>
+        <v>80336</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>6456</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2971,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584021</v>
+        <v>584065</v>
       </c>
       <c r="R25" t="n">
-        <v>6911731</v>
+        <v>6911889</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3033,10 +3003,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129759380</v>
+        <v>129759400</v>
       </c>
       <c r="B26" t="n">
-        <v>57738</v>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3044,21 +3014,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3068,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583963</v>
+        <v>583551</v>
       </c>
       <c r="R26" t="n">
-        <v>6911801</v>
+        <v>6911946</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3108,7 +3078,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Färska hackspår i liggande gran</t>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3135,32 +3105,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129759411</v>
+        <v>129759401</v>
       </c>
       <c r="B27" t="n">
-        <v>98831</v>
+        <v>80432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3170,10 +3140,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>583966</v>
+        <v>583559</v>
       </c>
       <c r="R27" t="n">
-        <v>6911716</v>
+        <v>6911967</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3206,11 +3176,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>29 ex</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3237,10 +3202,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129759375</v>
+        <v>129759402</v>
       </c>
       <c r="B28" t="n">
-        <v>57900</v>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3248,21 +3213,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3272,10 +3237,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>583977</v>
+        <v>583797</v>
       </c>
       <c r="R28" t="n">
-        <v>6911791</v>
+        <v>6911899</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3308,11 +3273,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Flera hördes varna</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3339,32 +3299,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129759388</v>
+        <v>129759397</v>
       </c>
       <c r="B29" t="n">
-        <v>91937</v>
+        <v>80460</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>6461</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3374,10 +3334,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584025</v>
+        <v>583679</v>
       </c>
       <c r="R29" t="n">
-        <v>6911728</v>
+        <v>6911975</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3436,32 +3396,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129759385</v>
+        <v>129759398</v>
       </c>
       <c r="B30" t="n">
-        <v>92092</v>
+        <v>80460</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>6461</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3471,10 +3431,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>583791</v>
+        <v>583824</v>
       </c>
       <c r="R30" t="n">
-        <v>6911899</v>
+        <v>6911829</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3533,32 +3493,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129759422</v>
+        <v>129759376</v>
       </c>
       <c r="B31" t="n">
-        <v>98831</v>
+        <v>80461</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3568,10 +3528,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>583932</v>
+        <v>583790</v>
       </c>
       <c r="R31" t="n">
-        <v>6911706</v>
+        <v>6911899</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3604,11 +3564,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>6 ex</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3635,10 +3590,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129759410</v>
+        <v>129759377</v>
       </c>
       <c r="B32" t="n">
-        <v>80160</v>
+        <v>80461</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3646,21 +3601,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3670,10 +3625,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>583794</v>
+        <v>583809</v>
       </c>
       <c r="R32" t="n">
-        <v>6911885</v>
+        <v>6911875</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3732,32 +3687,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129759343</v>
+        <v>129759378</v>
       </c>
       <c r="B33" t="n">
-        <v>91639</v>
+        <v>80461</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3767,10 +3722,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>583805</v>
+        <v>583791</v>
       </c>
       <c r="R33" t="n">
-        <v>6911905</v>
+        <v>6911883</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3829,32 +3784,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129759393</v>
+        <v>129759435</v>
       </c>
       <c r="B34" t="n">
-        <v>91937</v>
+        <v>80467</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3864,10 +3819,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>583944</v>
+        <v>583790</v>
       </c>
       <c r="R34" t="n">
-        <v>6911825</v>
+        <v>6911897</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3926,10 +3881,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129759409</v>
+        <v>129759436</v>
       </c>
       <c r="B35" t="n">
-        <v>80160</v>
+        <v>80467</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3937,21 +3892,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229497</v>
+        <v>6463</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3961,10 +3916,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>583771</v>
+        <v>583792</v>
       </c>
       <c r="R35" t="n">
-        <v>6911948</v>
+        <v>6911886</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4023,10 +3978,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129759407</v>
+        <v>129759403</v>
       </c>
       <c r="B36" t="n">
-        <v>80160</v>
+        <v>80468</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4034,21 +3989,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229497</v>
+        <v>6464</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4058,10 +4013,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>583767</v>
+        <v>583755</v>
       </c>
       <c r="R36" t="n">
-        <v>6911956</v>
+        <v>6911971</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4120,32 +4075,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129759389</v>
+        <v>129759379</v>
       </c>
       <c r="B37" t="n">
-        <v>91937</v>
+        <v>57950</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4155,10 +4110,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>583704</v>
+        <v>583930</v>
       </c>
       <c r="R37" t="n">
-        <v>6911854</v>
+        <v>6911711</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4191,6 +4146,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>1 ex, födosökande</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4217,32 +4177,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129759421</v>
+        <v>129759380</v>
       </c>
       <c r="B38" t="n">
-        <v>98831</v>
+        <v>57950</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4252,10 +4212,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>583940</v>
+        <v>583963</v>
       </c>
       <c r="R38" t="n">
-        <v>6911780</v>
+        <v>6911801</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4292,7 +4252,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>7 ex</t>
+          <t>Färska hackspår i liggande gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4319,32 +4279,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129759414</v>
+        <v>129759348</v>
       </c>
       <c r="B39" t="n">
-        <v>98831</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4354,10 +4314,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>583765</v>
+        <v>584041</v>
       </c>
       <c r="R39" t="n">
-        <v>6911752</v>
+        <v>6911763</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4394,7 +4354,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>15 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4421,10 +4381,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129759395</v>
+        <v>129759349</v>
       </c>
       <c r="B40" t="n">
-        <v>91937</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4432,21 +4392,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4456,10 +4416,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584070</v>
+        <v>583883</v>
       </c>
       <c r="R40" t="n">
-        <v>6911923</v>
+        <v>6911711</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4492,6 +4452,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4518,10 +4483,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129759428</v>
+        <v>129759350</v>
       </c>
       <c r="B41" t="n">
-        <v>91653</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4529,21 +4494,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4553,10 +4518,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>583782</v>
+        <v>583877</v>
       </c>
       <c r="R41" t="n">
-        <v>6911933</v>
+        <v>6911708</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4589,6 +4554,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4615,10 +4585,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129759345</v>
+        <v>129759351</v>
       </c>
       <c r="B42" t="n">
-        <v>91639</v>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4626,21 +4596,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4650,10 +4620,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>584070</v>
+        <v>583868</v>
       </c>
       <c r="R42" t="n">
-        <v>6911921</v>
+        <v>6911718</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4686,6 +4656,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4712,10 +4687,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129759400</v>
+        <v>129759352</v>
       </c>
       <c r="B43" t="n">
-        <v>80200</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4723,21 +4698,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4747,10 +4722,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>583551</v>
+        <v>583778</v>
       </c>
       <c r="R43" t="n">
-        <v>6911946</v>
+        <v>6911699</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4787,7 +4762,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Med apothecier</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4814,32 +4789,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129759435</v>
+        <v>129759353</v>
       </c>
       <c r="B44" t="n">
-        <v>80235</v>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4849,10 +4824,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>583790</v>
+        <v>583756</v>
       </c>
       <c r="R44" t="n">
-        <v>6911897</v>
+        <v>6911811</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4885,6 +4860,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4911,32 +4891,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129759396</v>
+        <v>129759354</v>
       </c>
       <c r="B45" t="n">
-        <v>97702</v>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4946,10 +4926,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>583804</v>
+        <v>583724</v>
       </c>
       <c r="R45" t="n">
-        <v>6911895</v>
+        <v>6911836</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4982,6 +4962,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5008,32 +4993,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129759405</v>
+        <v>129759355</v>
       </c>
       <c r="B46" t="n">
-        <v>80160</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5043,10 +5028,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>583549</v>
+        <v>583717</v>
       </c>
       <c r="R46" t="n">
-        <v>6911932</v>
+        <v>6911847</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5079,6 +5064,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>1 ex, födosökande</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5105,32 +5095,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129759378</v>
+        <v>129759356</v>
       </c>
       <c r="B47" t="n">
-        <v>80229</v>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5140,10 +5130,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>583791</v>
+        <v>583544</v>
       </c>
       <c r="R47" t="n">
-        <v>6911883</v>
+        <v>6911898</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5176,6 +5166,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>1 hona, födosökande</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5202,10 +5197,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129759402</v>
+        <v>129759357</v>
       </c>
       <c r="B48" t="n">
-        <v>80200</v>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5213,21 +5208,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5237,10 +5232,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>583797</v>
+        <v>583586</v>
       </c>
       <c r="R48" t="n">
-        <v>6911899</v>
+        <v>6911868</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5273,6 +5268,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5299,32 +5299,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129759382</v>
+        <v>129759358</v>
       </c>
       <c r="B49" t="n">
-        <v>80104</v>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5334,10 +5334,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>583791</v>
+        <v>583672</v>
       </c>
       <c r="R49" t="n">
-        <v>6911884</v>
+        <v>6911978</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5370,6 +5370,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5396,32 +5401,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129759403</v>
+        <v>129759359</v>
       </c>
       <c r="B50" t="n">
-        <v>80236</v>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5431,10 +5436,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>583755</v>
+        <v>583686</v>
       </c>
       <c r="R50" t="n">
-        <v>6911971</v>
+        <v>6911969</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5467,6 +5472,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5493,32 +5503,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129759419</v>
+        <v>129759360</v>
       </c>
       <c r="B51" t="n">
-        <v>98831</v>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5528,10 +5538,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>583745</v>
+        <v>583915</v>
       </c>
       <c r="R51" t="n">
-        <v>6911935</v>
+        <v>6911784</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5568,7 +5578,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>100 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5595,32 +5605,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129759412</v>
+        <v>129759361</v>
       </c>
       <c r="B52" t="n">
-        <v>98831</v>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5630,10 +5640,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>583781</v>
+        <v>583916</v>
       </c>
       <c r="R52" t="n">
-        <v>6911695</v>
+        <v>6911778</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5670,7 +5680,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>70 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5697,32 +5707,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129759420</v>
+        <v>129759362</v>
       </c>
       <c r="B53" t="n">
-        <v>98831</v>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5732,10 +5742,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>583927</v>
+        <v>583925</v>
       </c>
       <c r="R53" t="n">
-        <v>6911779</v>
+        <v>6911784</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5772,7 +5782,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>22 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5799,10 +5809,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129759391</v>
+        <v>129759363</v>
       </c>
       <c r="B54" t="n">
-        <v>91937</v>
+        <v>57953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5810,21 +5820,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5834,10 +5844,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>583565</v>
+        <v>583939</v>
       </c>
       <c r="R54" t="n">
-        <v>6911984</v>
+        <v>6911760</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5870,6 +5880,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5896,10 +5911,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129759431</v>
+        <v>129759364</v>
       </c>
       <c r="B55" t="n">
-        <v>79095</v>
+        <v>57953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5907,21 +5922,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5931,10 +5946,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>583549</v>
+        <v>583922</v>
       </c>
       <c r="R55" t="n">
-        <v>6911806</v>
+        <v>6911801</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5967,6 +5982,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -5993,32 +6013,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129759377</v>
+        <v>129759365</v>
       </c>
       <c r="B56" t="n">
-        <v>80229</v>
+        <v>57953</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6028,10 +6048,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>583809</v>
+        <v>583989</v>
       </c>
       <c r="R56" t="n">
-        <v>6911875</v>
+        <v>6911806</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6064,6 +6084,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>1 ex födosökande</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6090,32 +6115,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129759418</v>
+        <v>129759366</v>
       </c>
       <c r="B57" t="n">
-        <v>98831</v>
+        <v>57953</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6125,10 +6150,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>583629</v>
+        <v>583996</v>
       </c>
       <c r="R57" t="n">
-        <v>6911831</v>
+        <v>6911823</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6165,7 +6190,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>35 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6192,32 +6217,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129759416</v>
+        <v>129759367</v>
       </c>
       <c r="B58" t="n">
-        <v>98831</v>
+        <v>57953</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6227,10 +6252,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>583627</v>
+        <v>584025</v>
       </c>
       <c r="R58" t="n">
-        <v>6911841</v>
+        <v>6911875</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6267,7 +6292,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>45 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6294,10 +6319,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129759394</v>
+        <v>129759369</v>
       </c>
       <c r="B59" t="n">
-        <v>91937</v>
+        <v>57953</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6305,21 +6330,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6329,10 +6354,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>584057</v>
+        <v>584039</v>
       </c>
       <c r="R59" t="n">
-        <v>6911892</v>
+        <v>6911888</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6365,6 +6390,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6391,10 +6421,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129759433</v>
+        <v>129759370</v>
       </c>
       <c r="B60" t="n">
-        <v>79095</v>
+        <v>57953</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6402,21 +6432,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6426,10 +6456,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>583652</v>
+        <v>584063</v>
       </c>
       <c r="R60" t="n">
-        <v>6911949</v>
+        <v>6911870</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6462,6 +6492,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6488,32 +6523,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129759383</v>
+        <v>129759372</v>
       </c>
       <c r="B61" t="n">
-        <v>80104</v>
+        <v>57953</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6526,7 +6561,7 @@
         <v>584065</v>
       </c>
       <c r="R61" t="n">
-        <v>6911889</v>
+        <v>6911918</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6559,6 +6594,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6585,32 +6625,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129759376</v>
+        <v>129759373</v>
       </c>
       <c r="B62" t="n">
-        <v>80229</v>
+        <v>57953</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6620,10 +6660,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>583790</v>
+        <v>584106</v>
       </c>
       <c r="R62" t="n">
-        <v>6911899</v>
+        <v>6911946</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6656,6 +6696,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6682,10 +6727,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129759387</v>
+        <v>129759375</v>
       </c>
       <c r="B63" t="n">
-        <v>91937</v>
+        <v>58114</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6693,21 +6738,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6717,10 +6762,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>584029</v>
+        <v>583977</v>
       </c>
       <c r="R63" t="n">
-        <v>6911718</v>
+        <v>6911791</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6753,6 +6798,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Flera hördes varna</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6779,32 +6829,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129759350</v>
+        <v>129759411</v>
       </c>
       <c r="B64" t="n">
-        <v>57741</v>
+        <v>99118</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6814,10 +6864,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>583877</v>
+        <v>583966</v>
       </c>
       <c r="R64" t="n">
-        <v>6911708</v>
+        <v>6911716</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6854,7 +6904,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>29 ex</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6881,32 +6931,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129759361</v>
+        <v>129759412</v>
       </c>
       <c r="B65" t="n">
-        <v>57741</v>
+        <v>99118</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6916,10 +6966,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>583916</v>
+        <v>583781</v>
       </c>
       <c r="R65" t="n">
-        <v>6911778</v>
+        <v>6911695</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6956,7 +7006,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>70 ex</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -6983,32 +7033,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129759359</v>
+        <v>129759413</v>
       </c>
       <c r="B66" t="n">
-        <v>57741</v>
+        <v>99118</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7018,10 +7068,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>583686</v>
+        <v>583755</v>
       </c>
       <c r="R66" t="n">
-        <v>6911969</v>
+        <v>6911734</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7058,7 +7108,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7085,32 +7135,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129759352</v>
+        <v>129759414</v>
       </c>
       <c r="B67" t="n">
-        <v>57741</v>
+        <v>99118</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7120,10 +7170,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>583778</v>
+        <v>583765</v>
       </c>
       <c r="R67" t="n">
-        <v>6911699</v>
+        <v>6911752</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7160,7 +7210,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7187,32 +7237,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129759354</v>
+        <v>129759415</v>
       </c>
       <c r="B68" t="n">
-        <v>57741</v>
+        <v>99118</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7222,10 +7272,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>583724</v>
+        <v>583723</v>
       </c>
       <c r="R68" t="n">
-        <v>6911836</v>
+        <v>6911832</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7262,7 +7312,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7289,32 +7339,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129759348</v>
+        <v>129759416</v>
       </c>
       <c r="B69" t="n">
-        <v>57741</v>
+        <v>99118</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7324,10 +7374,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>584041</v>
+        <v>583627</v>
       </c>
       <c r="R69" t="n">
-        <v>6911763</v>
+        <v>6911841</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7364,7 +7414,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>45 ex</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7391,32 +7441,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129759363</v>
+        <v>129759418</v>
       </c>
       <c r="B70" t="n">
-        <v>57741</v>
+        <v>99118</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7426,10 +7476,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>583939</v>
+        <v>583629</v>
       </c>
       <c r="R70" t="n">
-        <v>6911760</v>
+        <v>6911831</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7466,7 +7516,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7493,32 +7543,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129759370</v>
+        <v>129759419</v>
       </c>
       <c r="B71" t="n">
-        <v>57741</v>
+        <v>99118</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7528,10 +7578,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>584063</v>
+        <v>583745</v>
       </c>
       <c r="R71" t="n">
-        <v>6911870</v>
+        <v>6911935</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7568,7 +7618,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7595,32 +7645,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129759357</v>
+        <v>129759420</v>
       </c>
       <c r="B72" t="n">
-        <v>57741</v>
+        <v>99118</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7630,10 +7680,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>583586</v>
+        <v>583927</v>
       </c>
       <c r="R72" t="n">
-        <v>6911868</v>
+        <v>6911779</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7670,7 +7720,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>22 ex</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7697,32 +7747,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129759372</v>
+        <v>129759421</v>
       </c>
       <c r="B73" t="n">
-        <v>57741</v>
+        <v>99118</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7732,10 +7782,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>584065</v>
+        <v>583940</v>
       </c>
       <c r="R73" t="n">
-        <v>6911918</v>
+        <v>6911780</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7772,7 +7822,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>7 ex</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7799,32 +7849,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129759367</v>
+        <v>129759422</v>
       </c>
       <c r="B74" t="n">
-        <v>57741</v>
+        <v>99118</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7834,10 +7884,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>584025</v>
+        <v>583932</v>
       </c>
       <c r="R74" t="n">
-        <v>6911875</v>
+        <v>6911706</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7874,7 +7924,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>6 ex</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7901,32 +7951,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129759366</v>
+        <v>129759423</v>
       </c>
       <c r="B75" t="n">
-        <v>57741</v>
+        <v>99118</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7936,10 +7986,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>583996</v>
+        <v>583836</v>
       </c>
       <c r="R75" t="n">
-        <v>6911823</v>
+        <v>6911810</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7976,7 +8026,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8003,32 +8053,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129759364</v>
+        <v>129759424</v>
       </c>
       <c r="B76" t="n">
-        <v>57741</v>
+        <v>99118</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8038,10 +8088,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>583922</v>
+        <v>583956</v>
       </c>
       <c r="R76" t="n">
-        <v>6911801</v>
+        <v>6911817</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8078,7 +8128,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>90 ex runt en tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8105,32 +8155,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129759358</v>
+        <v>129759425</v>
       </c>
       <c r="B77" t="n">
-        <v>57741</v>
+        <v>99118</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8140,10 +8190,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>583672</v>
+        <v>583999</v>
       </c>
       <c r="R77" t="n">
-        <v>6911978</v>
+        <v>6911781</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8180,7 +8230,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8207,32 +8257,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129759355</v>
+        <v>129759427</v>
       </c>
       <c r="B78" t="n">
-        <v>57741</v>
+        <v>106243</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8242,10 +8292,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>583717</v>
+        <v>584003</v>
       </c>
       <c r="R78" t="n">
-        <v>6911847</v>
+        <v>6911804</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8278,11 +8328,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>1 ex, födosökande</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8309,32 +8354,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129759353</v>
+        <v>129759396</v>
       </c>
       <c r="B79" t="n">
-        <v>57741</v>
+        <v>97983</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8344,10 +8389,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>583756</v>
+        <v>583804</v>
       </c>
       <c r="R79" t="n">
-        <v>6911811</v>
+        <v>6911895</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8380,11 +8425,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8411,32 +8451,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129759362</v>
+        <v>129759437</v>
       </c>
       <c r="B80" t="n">
-        <v>57741</v>
+        <v>101325</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8446,10 +8486,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>583925</v>
+        <v>583826</v>
       </c>
       <c r="R80" t="n">
-        <v>6911784</v>
+        <v>6911855</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8482,11 +8522,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8513,32 +8548,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129759349</v>
+        <v>129759405</v>
       </c>
       <c r="B81" t="n">
-        <v>57741</v>
+        <v>80392</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8548,10 +8583,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>583883</v>
+        <v>583549</v>
       </c>
       <c r="R81" t="n">
-        <v>6911711</v>
+        <v>6911932</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8584,11 +8619,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8615,32 +8645,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129759365</v>
+        <v>129759406</v>
       </c>
       <c r="B82" t="n">
-        <v>57741</v>
+        <v>80392</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8650,10 +8680,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>583989</v>
+        <v>583688</v>
       </c>
       <c r="R82" t="n">
-        <v>6911806</v>
+        <v>6911990</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8686,11 +8716,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>1 ex födosökande</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8717,32 +8742,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129759360</v>
+        <v>129759407</v>
       </c>
       <c r="B83" t="n">
-        <v>57741</v>
+        <v>80392</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8752,10 +8777,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>583915</v>
+        <v>583767</v>
       </c>
       <c r="R83" t="n">
-        <v>6911784</v>
+        <v>6911956</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8788,11 +8813,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8819,32 +8839,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129759351</v>
+        <v>129759409</v>
       </c>
       <c r="B84" t="n">
-        <v>57741</v>
+        <v>80392</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8854,10 +8874,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>583868</v>
+        <v>583771</v>
       </c>
       <c r="R84" t="n">
-        <v>6911718</v>
+        <v>6911948</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8890,11 +8910,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8921,32 +8936,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129759369</v>
+        <v>129759410</v>
       </c>
       <c r="B85" t="n">
-        <v>57741</v>
+        <v>80392</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8956,10 +8971,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>584039</v>
+        <v>583794</v>
       </c>
       <c r="R85" t="n">
-        <v>6911888</v>
+        <v>6911885</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8992,11 +9007,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9023,32 +9033,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129759356</v>
+        <v>129759399</v>
       </c>
       <c r="B86" t="n">
-        <v>57741</v>
+        <v>75352</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>229651</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglavsknapp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Plectocarpon lichenum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) D.Hawksw.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9058,10 +9068,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>583544</v>
+        <v>583550</v>
       </c>
       <c r="R86" t="n">
-        <v>6911898</v>
+        <v>6911932</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9096,11 +9106,6 @@
           <t>2025-11-19</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>1 hona, födosökande</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -9122,6 +9127,107 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>129759404</v>
+      </c>
+      <c r="B87" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Stor-Oxögeberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>583819</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6911717</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
